--- a/public/pds/PDS2025.xlsx
+++ b/public/pds/PDS2025.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="3804" windowHeight="216" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="3804" windowHeight="216"/>
   </bookViews>
   <sheets>
     <sheet name="C1" sheetId="1" r:id="rId1"/>
@@ -1435,7 +1435,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0_);\(0.0\)"/>
     <numFmt numFmtId="167" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
-    <numFmt numFmtId="170" formatCode="[$-14809]d/m/yyyy;@"/>
+    <numFmt numFmtId="168" formatCode="[$-14809]d/m/yyyy;@"/>
   </numFmts>
   <fonts count="56" x14ac:knownFonts="1">
     <font>
@@ -2723,7 +2723,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="757">
+  <cellXfs count="754">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
@@ -3122,12 +3122,6 @@
     <xf numFmtId="49" fontId="10" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3174,9 +3168,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3562,6 +3553,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="41" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -3582,6 +3583,18 @@
     </xf>
     <xf numFmtId="49" fontId="17" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3832,10 +3845,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3843,7 +3856,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3947,19 +3960,13 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4075,9 +4082,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4102,28 +4106,23 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4134,17 +4133,8 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4381,6 +4371,12 @@
     <xf numFmtId="49" fontId="17" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="39" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4391,6 +4387,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="48" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4598,71 +4597,6 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4719,12 +4653,6 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4779,6 +4707,10 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -4813,35 +4745,54 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4962,6 +4913,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -4993,36 +4947,6 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5030,26 +4954,28 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5059,6 +4985,81 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -10147,38 +10148,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="331"/>
-      <c r="B1" s="332"/>
-      <c r="C1" s="332"/>
-      <c r="D1" s="332"/>
-      <c r="E1" s="332"/>
-      <c r="F1" s="332"/>
-      <c r="G1" s="332"/>
-      <c r="H1" s="332"/>
-      <c r="I1" s="332"/>
-      <c r="J1" s="332"/>
-      <c r="K1" s="332"/>
-      <c r="L1" s="332"/>
-      <c r="M1" s="332"/>
-      <c r="N1" s="333"/>
+      <c r="A1" s="335"/>
+      <c r="B1" s="336"/>
+      <c r="C1" s="336"/>
+      <c r="D1" s="336"/>
+      <c r="E1" s="336"/>
+      <c r="F1" s="336"/>
+      <c r="G1" s="336"/>
+      <c r="H1" s="336"/>
+      <c r="I1" s="336"/>
+      <c r="J1" s="336"/>
+      <c r="K1" s="336"/>
+      <c r="L1" s="336"/>
+      <c r="M1" s="336"/>
+      <c r="N1" s="337"/>
     </row>
     <row r="2" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144"/>
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
-      <c r="H2" s="145"/>
-      <c r="I2" s="145"/>
-      <c r="J2" s="145"/>
-      <c r="K2" s="145"/>
-      <c r="L2" s="145" t="s">
+      <c r="A2" s="142"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
+      <c r="K2" s="143"/>
+      <c r="L2" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="145"/>
-      <c r="N2" s="146"/>
+      <c r="M2" s="143"/>
+      <c r="N2" s="144"/>
       <c r="O2" s="69" t="s">
         <v>1</v>
       </c>
@@ -10190,80 +10191,80 @@
       </c>
     </row>
     <row r="3" spans="1:21" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="334" t="s">
+      <c r="A3" s="338" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="335"/>
-      <c r="C3" s="335"/>
-      <c r="D3" s="335"/>
-      <c r="E3" s="335"/>
-      <c r="F3" s="335"/>
-      <c r="G3" s="335"/>
-      <c r="H3" s="335"/>
-      <c r="I3" s="335"/>
-      <c r="J3" s="335"/>
-      <c r="K3" s="335"/>
-      <c r="L3" s="335"/>
-      <c r="M3" s="335"/>
-      <c r="N3" s="336"/>
+      <c r="B3" s="339"/>
+      <c r="C3" s="339"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="339"/>
+      <c r="H3" s="339"/>
+      <c r="I3" s="339"/>
+      <c r="J3" s="339"/>
+      <c r="K3" s="339"/>
+      <c r="L3" s="339"/>
+      <c r="M3" s="339"/>
+      <c r="N3" s="340"/>
     </row>
     <row r="4" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="340" t="s">
+      <c r="A4" s="344" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="341"/>
-      <c r="C4" s="341"/>
-      <c r="D4" s="341"/>
-      <c r="E4" s="341"/>
-      <c r="F4" s="341"/>
-      <c r="G4" s="341"/>
-      <c r="H4" s="341"/>
-      <c r="I4" s="341"/>
-      <c r="J4" s="341"/>
-      <c r="K4" s="341"/>
-      <c r="L4" s="341"/>
-      <c r="M4" s="341"/>
-      <c r="N4" s="342"/>
+      <c r="B4" s="345"/>
+      <c r="C4" s="345"/>
+      <c r="D4" s="345"/>
+      <c r="E4" s="345"/>
+      <c r="F4" s="345"/>
+      <c r="G4" s="345"/>
+      <c r="H4" s="345"/>
+      <c r="I4" s="345"/>
+      <c r="J4" s="345"/>
+      <c r="K4" s="345"/>
+      <c r="L4" s="345"/>
+      <c r="M4" s="345"/>
+      <c r="N4" s="346"/>
     </row>
     <row r="5" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="371" t="s">
+      <c r="A5" s="375" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="372"/>
-      <c r="C5" s="372"/>
-      <c r="D5" s="372"/>
-      <c r="E5" s="372"/>
-      <c r="F5" s="372"/>
-      <c r="G5" s="372"/>
-      <c r="H5" s="372"/>
-      <c r="I5" s="372"/>
-      <c r="J5" s="372"/>
-      <c r="K5" s="372"/>
-      <c r="L5" s="372"/>
-      <c r="M5" s="372"/>
-      <c r="N5" s="373"/>
+      <c r="B5" s="376"/>
+      <c r="C5" s="376"/>
+      <c r="D5" s="376"/>
+      <c r="E5" s="376"/>
+      <c r="F5" s="376"/>
+      <c r="G5" s="376"/>
+      <c r="H5" s="376"/>
+      <c r="I5" s="376"/>
+      <c r="J5" s="376"/>
+      <c r="K5" s="376"/>
+      <c r="L5" s="376"/>
+      <c r="M5" s="376"/>
+      <c r="N5" s="377"/>
     </row>
     <row r="6" spans="1:21" ht="3" hidden="1" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A6" s="175"/>
-      <c r="B6" s="235"/>
-      <c r="C6" s="236"/>
-      <c r="D6" s="236"/>
-      <c r="E6" s="236"/>
-      <c r="F6" s="236"/>
-      <c r="G6" s="236"/>
-      <c r="H6" s="236"/>
-      <c r="I6" s="236"/>
-      <c r="J6" s="236"/>
-      <c r="K6" s="236"/>
-      <c r="L6" s="236"/>
-      <c r="M6" s="236"/>
-      <c r="N6" s="176"/>
+      <c r="A6" s="172"/>
+      <c r="B6" s="232"/>
+      <c r="C6" s="233"/>
+      <c r="D6" s="233"/>
+      <c r="E6" s="233"/>
+      <c r="F6" s="233"/>
+      <c r="G6" s="233"/>
+      <c r="H6" s="233"/>
+      <c r="I6" s="233"/>
+      <c r="J6" s="233"/>
+      <c r="K6" s="233"/>
+      <c r="L6" s="233"/>
+      <c r="M6" s="233"/>
+      <c r="N6" s="173"/>
     </row>
     <row r="7" spans="1:21" s="76" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="147" t="s">
+      <c r="A7" s="145" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="191"/>
+      <c r="B7" s="188"/>
       <c r="C7" s="75"/>
       <c r="D7" s="75"/>
       <c r="E7" s="75"/>
@@ -10272,812 +10273,812 @@
       <c r="H7" s="75"/>
       <c r="I7" s="75"/>
       <c r="J7" s="75"/>
-      <c r="K7" s="237"/>
-      <c r="L7" s="237"/>
-      <c r="M7" s="237"/>
-      <c r="N7" s="238"/>
-      <c r="O7" s="240"/>
-      <c r="P7" s="240"/>
-      <c r="Q7" s="240"/>
-      <c r="R7" s="240"/>
-      <c r="S7" s="240"/>
-      <c r="T7" s="240"/>
-      <c r="U7" s="240"/>
+      <c r="K7" s="234"/>
+      <c r="L7" s="234"/>
+      <c r="M7" s="234"/>
+      <c r="N7" s="235"/>
+      <c r="O7" s="237"/>
+      <c r="P7" s="237"/>
+      <c r="Q7" s="237"/>
+      <c r="R7" s="237"/>
+      <c r="S7" s="237"/>
+      <c r="T7" s="237"/>
+      <c r="U7" s="237"/>
     </row>
     <row r="8" spans="1:21" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="239"/>
-      <c r="B8" s="179"/>
-      <c r="C8" s="179"/>
-      <c r="D8" s="179"/>
-      <c r="E8" s="179"/>
-      <c r="F8" s="179"/>
-      <c r="G8" s="179"/>
-      <c r="H8" s="179"/>
-      <c r="I8" s="179"/>
-      <c r="J8" s="179"/>
-      <c r="K8" s="179"/>
-      <c r="L8" s="179"/>
-      <c r="M8" s="179"/>
-      <c r="N8" s="180"/>
-      <c r="O8" s="241"/>
-      <c r="P8" s="241"/>
-      <c r="Q8" s="241"/>
-      <c r="R8" s="241"/>
-      <c r="S8" s="241"/>
-      <c r="T8" s="241"/>
-      <c r="U8" s="241"/>
+      <c r="A8" s="236"/>
+      <c r="B8" s="176"/>
+      <c r="C8" s="176"/>
+      <c r="D8" s="176"/>
+      <c r="E8" s="176"/>
+      <c r="F8" s="176"/>
+      <c r="G8" s="176"/>
+      <c r="H8" s="176"/>
+      <c r="I8" s="176"/>
+      <c r="J8" s="176"/>
+      <c r="K8" s="176"/>
+      <c r="L8" s="176"/>
+      <c r="M8" s="176"/>
+      <c r="N8" s="177"/>
+      <c r="O8" s="238"/>
+      <c r="P8" s="238"/>
+      <c r="Q8" s="238"/>
+      <c r="R8" s="238"/>
+      <c r="S8" s="238"/>
+      <c r="T8" s="238"/>
+      <c r="U8" s="238"/>
     </row>
     <row r="9" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="337" t="s">
+      <c r="A9" s="341" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="338"/>
-      <c r="C9" s="338"/>
-      <c r="D9" s="338"/>
-      <c r="E9" s="338"/>
-      <c r="F9" s="338"/>
-      <c r="G9" s="338"/>
-      <c r="H9" s="338"/>
-      <c r="I9" s="338"/>
-      <c r="J9" s="338"/>
-      <c r="K9" s="338"/>
-      <c r="L9" s="338"/>
-      <c r="M9" s="338"/>
-      <c r="N9" s="339"/>
-      <c r="O9" s="241"/>
-      <c r="P9" s="241"/>
-      <c r="Q9" s="241"/>
-      <c r="R9" s="241"/>
-      <c r="S9" s="241"/>
-      <c r="T9" s="241"/>
-      <c r="U9" s="241"/>
+      <c r="B9" s="342"/>
+      <c r="C9" s="342"/>
+      <c r="D9" s="342"/>
+      <c r="E9" s="342"/>
+      <c r="F9" s="342"/>
+      <c r="G9" s="342"/>
+      <c r="H9" s="342"/>
+      <c r="I9" s="342"/>
+      <c r="J9" s="342"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="343"/>
+      <c r="O9" s="238"/>
+      <c r="P9" s="238"/>
+      <c r="Q9" s="238"/>
+      <c r="R9" s="238"/>
+      <c r="S9" s="238"/>
+      <c r="T9" s="238"/>
+      <c r="U9" s="238"/>
     </row>
     <row r="10" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="148" t="s">
+      <c r="A10" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="388" t="s">
+      <c r="B10" s="392" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="389"/>
-      <c r="D10" s="379"/>
-      <c r="E10" s="379"/>
-      <c r="F10" s="379"/>
-      <c r="G10" s="379"/>
-      <c r="H10" s="379"/>
-      <c r="I10" s="379"/>
-      <c r="J10" s="379"/>
-      <c r="K10" s="379"/>
-      <c r="L10" s="379"/>
-      <c r="M10" s="379"/>
-      <c r="N10" s="380"/>
-      <c r="O10" s="241"/>
-      <c r="P10" s="240" t="s">
+      <c r="C10" s="393"/>
+      <c r="D10" s="383"/>
+      <c r="E10" s="383"/>
+      <c r="F10" s="383"/>
+      <c r="G10" s="383"/>
+      <c r="H10" s="383"/>
+      <c r="I10" s="383"/>
+      <c r="J10" s="383"/>
+      <c r="K10" s="383"/>
+      <c r="L10" s="383"/>
+      <c r="M10" s="383"/>
+      <c r="N10" s="384"/>
+      <c r="O10" s="238"/>
+      <c r="P10" s="237" t="s">
         <v>11</v>
       </c>
-      <c r="Q10" s="241"/>
-      <c r="R10" s="241" t="s">
+      <c r="Q10" s="238"/>
+      <c r="R10" s="238" t="s">
         <v>405</v>
       </c>
-      <c r="S10" s="241" t="s">
+      <c r="S10" s="238" t="s">
         <v>406</v>
       </c>
-      <c r="T10" s="241" t="b">
+      <c r="T10" s="238" t="b">
         <v>0</v>
       </c>
-      <c r="U10" s="241"/>
+      <c r="U10" s="238"/>
     </row>
     <row r="11" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="148" t="s">
+      <c r="A11" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="390" t="s">
+      <c r="B11" s="394" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="391"/>
-      <c r="D11" s="406"/>
-      <c r="E11" s="407"/>
-      <c r="F11" s="407"/>
-      <c r="G11" s="407"/>
-      <c r="H11" s="407"/>
-      <c r="I11" s="407"/>
-      <c r="J11" s="407"/>
-      <c r="K11" s="408"/>
-      <c r="L11" s="437" t="s">
+      <c r="C11" s="395"/>
+      <c r="D11" s="408"/>
+      <c r="E11" s="409"/>
+      <c r="F11" s="409"/>
+      <c r="G11" s="409"/>
+      <c r="H11" s="409"/>
+      <c r="I11" s="409"/>
+      <c r="J11" s="409"/>
+      <c r="K11" s="410"/>
+      <c r="L11" s="438" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="438"/>
-      <c r="N11" s="439"/>
-      <c r="O11" s="241"/>
-      <c r="P11" s="241" t="s">
+      <c r="M11" s="439"/>
+      <c r="N11" s="440"/>
+      <c r="O11" s="238"/>
+      <c r="P11" s="238" t="s">
         <v>15</v>
       </c>
-      <c r="Q11" s="242" t="s">
+      <c r="Q11" s="239" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="241"/>
-      <c r="S11" s="241" t="s">
+      <c r="R11" s="238"/>
+      <c r="S11" s="238" t="s">
         <v>407</v>
       </c>
-      <c r="T11" s="241" t="b">
+      <c r="T11" s="238" t="b">
         <v>0</v>
       </c>
-      <c r="U11" s="241"/>
+      <c r="U11" s="238"/>
     </row>
     <row r="12" spans="1:21" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="149"/>
-      <c r="B12" s="392" t="s">
+      <c r="A12" s="147"/>
+      <c r="B12" s="396" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="393"/>
-      <c r="D12" s="409"/>
-      <c r="E12" s="410"/>
-      <c r="F12" s="410"/>
-      <c r="G12" s="410"/>
-      <c r="H12" s="410"/>
-      <c r="I12" s="410"/>
-      <c r="J12" s="410"/>
-      <c r="K12" s="410"/>
-      <c r="L12" s="410"/>
-      <c r="M12" s="410"/>
-      <c r="N12" s="411"/>
-      <c r="O12" s="241"/>
-      <c r="P12" s="241" t="s">
+      <c r="C12" s="397"/>
+      <c r="D12" s="411"/>
+      <c r="E12" s="412"/>
+      <c r="F12" s="412"/>
+      <c r="G12" s="412"/>
+      <c r="H12" s="412"/>
+      <c r="I12" s="412"/>
+      <c r="J12" s="412"/>
+      <c r="K12" s="412"/>
+      <c r="L12" s="412"/>
+      <c r="M12" s="412"/>
+      <c r="N12" s="413"/>
+      <c r="O12" s="238"/>
+      <c r="P12" s="238" t="s">
         <v>18</v>
       </c>
-      <c r="Q12" s="243" t="s">
+      <c r="Q12" s="240" t="s">
         <v>19</v>
       </c>
-      <c r="R12" s="241" t="s">
+      <c r="R12" s="238" t="s">
         <v>36</v>
       </c>
-      <c r="S12" s="241" t="s">
+      <c r="S12" s="238" t="s">
         <v>408</v>
       </c>
-      <c r="T12" s="241" t="b">
+      <c r="T12" s="238" t="b">
         <v>0</v>
       </c>
-      <c r="U12" s="241"/>
+      <c r="U12" s="238"/>
     </row>
     <row r="13" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="211" t="s">
+      <c r="A13" s="208" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="427" t="s">
+      <c r="B13" s="429" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="389"/>
-      <c r="D13" s="428"/>
-      <c r="E13" s="428"/>
-      <c r="F13" s="429"/>
+      <c r="C13" s="393"/>
+      <c r="D13" s="430"/>
+      <c r="E13" s="430"/>
+      <c r="F13" s="431"/>
       <c r="G13" s="82" t="s">
         <v>22</v>
       </c>
       <c r="H13" s="126"/>
       <c r="I13" s="126"/>
-      <c r="J13" s="440"/>
-      <c r="K13" s="441"/>
-      <c r="L13" s="441"/>
-      <c r="M13" s="441"/>
-      <c r="N13" s="442"/>
-      <c r="O13" s="241"/>
-      <c r="P13" s="241" t="s">
+      <c r="J13" s="441"/>
+      <c r="K13" s="442"/>
+      <c r="L13" s="442"/>
+      <c r="M13" s="442"/>
+      <c r="N13" s="443"/>
+      <c r="O13" s="238"/>
+      <c r="P13" s="238" t="s">
         <v>23</v>
       </c>
-      <c r="Q13" s="243" t="s">
+      <c r="Q13" s="240" t="s">
         <v>24</v>
       </c>
-      <c r="R13" s="241"/>
-      <c r="S13" s="241" t="s">
+      <c r="R13" s="238"/>
+      <c r="S13" s="238" t="s">
         <v>409</v>
       </c>
-      <c r="T13" s="241" t="b">
+      <c r="T13" s="238" t="b">
         <v>0</v>
       </c>
-      <c r="U13" s="241"/>
+      <c r="U13" s="238"/>
     </row>
     <row r="14" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="148"/>
-      <c r="B14" s="205"/>
-      <c r="C14" s="205"/>
-      <c r="D14" s="206"/>
-      <c r="E14" s="210"/>
-      <c r="F14" s="210"/>
+      <c r="A14" s="146"/>
+      <c r="B14" s="202"/>
+      <c r="C14" s="202"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="207"/>
+      <c r="F14" s="207"/>
       <c r="G14" s="132"/>
-      <c r="H14" s="140"/>
-      <c r="I14" s="140"/>
-      <c r="J14" s="207"/>
-      <c r="K14" s="208"/>
-      <c r="L14" s="208"/>
-      <c r="M14" s="208"/>
-      <c r="N14" s="209"/>
-      <c r="O14" s="241"/>
-      <c r="P14" s="241"/>
-      <c r="Q14" s="243"/>
-      <c r="R14" s="241"/>
-      <c r="S14" s="241" t="s">
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="204"/>
+      <c r="K14" s="205"/>
+      <c r="L14" s="205"/>
+      <c r="M14" s="205"/>
+      <c r="N14" s="206"/>
+      <c r="O14" s="238"/>
+      <c r="P14" s="238"/>
+      <c r="Q14" s="240"/>
+      <c r="R14" s="238"/>
+      <c r="S14" s="238" t="s">
         <v>406</v>
       </c>
-      <c r="T14" s="241" t="b">
+      <c r="T14" s="238" t="b">
         <v>0</v>
       </c>
-      <c r="U14" s="241"/>
+      <c r="U14" s="238"/>
     </row>
     <row r="15" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="150" t="s">
+      <c r="A15" s="148" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="77" t="s">
         <v>26</v>
       </c>
       <c r="C15" s="77"/>
-      <c r="D15" s="455"/>
-      <c r="E15" s="455"/>
-      <c r="F15" s="456"/>
-      <c r="G15" s="433" t="s">
+      <c r="D15" s="451"/>
+      <c r="E15" s="451"/>
+      <c r="F15" s="452"/>
+      <c r="G15" s="435" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="434"/>
-      <c r="I15" s="434"/>
+      <c r="H15" s="436"/>
+      <c r="I15" s="436"/>
       <c r="J15" s="127"/>
       <c r="K15" s="128"/>
-      <c r="L15" s="465" t="s">
+      <c r="L15" s="458" t="s">
         <v>28</v>
       </c>
-      <c r="M15" s="465"/>
-      <c r="N15" s="466"/>
-      <c r="O15" s="241"/>
-      <c r="P15" s="241" t="s">
+      <c r="M15" s="458"/>
+      <c r="N15" s="459"/>
+      <c r="O15" s="238"/>
+      <c r="P15" s="238" t="s">
         <v>29</v>
       </c>
-      <c r="Q15" s="243" t="s">
+      <c r="Q15" s="240" t="s">
         <v>30</v>
       </c>
-      <c r="R15" s="241"/>
-      <c r="S15" s="241" t="s">
+      <c r="R15" s="238"/>
+      <c r="S15" s="238" t="s">
         <v>410</v>
       </c>
-      <c r="T15" s="241" t="b">
+      <c r="T15" s="238" t="b">
         <v>0</v>
       </c>
-      <c r="U15" s="241"/>
+      <c r="U15" s="238"/>
     </row>
     <row r="16" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="151" t="s">
+      <c r="A16" s="149" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="233" t="s">
+      <c r="B16" s="230" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="78"/>
-      <c r="D16" s="381"/>
-      <c r="E16" s="381"/>
-      <c r="F16" s="382"/>
-      <c r="G16" s="430" t="s">
+      <c r="D16" s="385"/>
+      <c r="E16" s="385"/>
+      <c r="F16" s="386"/>
+      <c r="G16" s="432" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="431"/>
-      <c r="I16" s="432"/>
-      <c r="J16" s="467"/>
-      <c r="K16" s="468"/>
-      <c r="L16" s="468"/>
-      <c r="M16" s="468"/>
-      <c r="N16" s="469"/>
-      <c r="O16" s="241"/>
-      <c r="P16" s="241" t="s">
+      <c r="H16" s="433"/>
+      <c r="I16" s="434"/>
+      <c r="J16" s="460"/>
+      <c r="K16" s="461"/>
+      <c r="L16" s="461"/>
+      <c r="M16" s="461"/>
+      <c r="N16" s="462"/>
+      <c r="O16" s="238"/>
+      <c r="P16" s="238" t="s">
         <v>34</v>
       </c>
-      <c r="Q16" s="243" t="s">
+      <c r="Q16" s="240" t="s">
         <v>35</v>
       </c>
-      <c r="R16" s="241"/>
-      <c r="S16" s="241" t="s">
+      <c r="R16" s="238"/>
+      <c r="S16" s="238" t="s">
         <v>411</v>
       </c>
-      <c r="T16" s="241" t="b">
+      <c r="T16" s="238" t="b">
         <v>0</v>
       </c>
-      <c r="U16" s="241"/>
+      <c r="U16" s="238"/>
     </row>
     <row r="17" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="416">
+      <c r="A17" s="418">
         <v>6</v>
       </c>
-      <c r="B17" s="423" t="s">
+      <c r="B17" s="425" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="424"/>
-      <c r="D17" s="421"/>
-      <c r="E17" s="421"/>
-      <c r="F17" s="421"/>
+      <c r="C17" s="426"/>
+      <c r="D17" s="423"/>
+      <c r="E17" s="423"/>
+      <c r="F17" s="423"/>
       <c r="G17" s="83" t="s">
         <v>37</v>
       </c>
       <c r="H17" s="84"/>
-      <c r="I17" s="360"/>
-      <c r="J17" s="361"/>
-      <c r="K17" s="361"/>
-      <c r="L17" s="361"/>
-      <c r="M17" s="361"/>
-      <c r="N17" s="365"/>
-      <c r="O17" s="241"/>
-      <c r="P17" s="241"/>
-      <c r="Q17" s="243" t="s">
+      <c r="I17" s="364"/>
+      <c r="J17" s="365"/>
+      <c r="K17" s="365"/>
+      <c r="L17" s="365"/>
+      <c r="M17" s="365"/>
+      <c r="N17" s="369"/>
+      <c r="O17" s="238"/>
+      <c r="P17" s="238"/>
+      <c r="Q17" s="240" t="s">
         <v>38</v>
       </c>
-      <c r="R17" s="241" t="s">
+      <c r="R17" s="238" t="s">
         <v>412</v>
       </c>
-      <c r="S17" s="241" t="s">
+      <c r="S17" s="238" t="s">
         <v>413</v>
       </c>
-      <c r="T17" s="241" t="b">
+      <c r="T17" s="238" t="b">
         <v>0</v>
       </c>
-      <c r="U17" s="241"/>
+      <c r="U17" s="238"/>
     </row>
     <row r="18" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="417"/>
-      <c r="B18" s="425"/>
-      <c r="C18" s="426"/>
-      <c r="D18" s="422"/>
-      <c r="E18" s="422"/>
-      <c r="F18" s="422"/>
+      <c r="A18" s="419"/>
+      <c r="B18" s="427"/>
+      <c r="C18" s="428"/>
+      <c r="D18" s="424"/>
+      <c r="E18" s="424"/>
+      <c r="F18" s="424"/>
       <c r="G18" s="134"/>
       <c r="H18" s="85"/>
-      <c r="I18" s="358" t="s">
+      <c r="I18" s="362" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="359"/>
-      <c r="K18" s="359"/>
-      <c r="L18" s="359" t="s">
+      <c r="J18" s="363"/>
+      <c r="K18" s="363"/>
+      <c r="L18" s="363" t="s">
         <v>40</v>
       </c>
-      <c r="M18" s="359"/>
-      <c r="N18" s="374"/>
-      <c r="O18" s="241"/>
-      <c r="P18" s="241"/>
-      <c r="Q18" s="243" t="s">
+      <c r="M18" s="363"/>
+      <c r="N18" s="378"/>
+      <c r="O18" s="238"/>
+      <c r="P18" s="238"/>
+      <c r="Q18" s="240" t="s">
         <v>41</v>
       </c>
-      <c r="R18" s="241"/>
-      <c r="S18" s="241" t="s">
+      <c r="R18" s="238"/>
+      <c r="S18" s="238" t="s">
         <v>414</v>
       </c>
-      <c r="T18" s="241" t="b">
+      <c r="T18" s="238" t="b">
         <v>0</v>
       </c>
-      <c r="U18" s="241"/>
+      <c r="U18" s="238"/>
     </row>
     <row r="19" spans="1:21" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="152"/>
-      <c r="B19" s="192"/>
-      <c r="C19" s="142"/>
-      <c r="D19" s="141"/>
-      <c r="E19" s="141"/>
-      <c r="F19" s="141"/>
+      <c r="A19" s="150"/>
+      <c r="B19" s="189"/>
+      <c r="C19" s="140"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
       <c r="G19" s="134"/>
       <c r="H19" s="85"/>
-      <c r="I19" s="443"/>
-      <c r="J19" s="444"/>
-      <c r="K19" s="444"/>
-      <c r="L19" s="447"/>
-      <c r="M19" s="444"/>
-      <c r="N19" s="448"/>
-      <c r="O19" s="241"/>
-      <c r="P19" s="241"/>
-      <c r="Q19" s="243" t="s">
+      <c r="I19" s="444"/>
+      <c r="J19" s="746"/>
+      <c r="K19" s="746"/>
+      <c r="L19" s="445"/>
+      <c r="M19" s="746"/>
+      <c r="N19" s="747"/>
+      <c r="O19" s="238"/>
+      <c r="P19" s="238"/>
+      <c r="Q19" s="240" t="s">
         <v>42</v>
       </c>
-      <c r="R19" s="241"/>
-      <c r="S19" s="241"/>
-      <c r="T19" s="241"/>
-      <c r="U19" s="241"/>
+      <c r="R19" s="238"/>
+      <c r="S19" s="238"/>
+      <c r="T19" s="238"/>
+      <c r="U19" s="238"/>
     </row>
     <row r="20" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="417"/>
-      <c r="B20" s="192"/>
+      <c r="A20" s="419"/>
+      <c r="B20" s="189"/>
       <c r="C20" s="118"/>
       <c r="D20" s="119"/>
-      <c r="E20" s="386"/>
-      <c r="F20" s="386"/>
+      <c r="E20" s="390"/>
+      <c r="F20" s="390"/>
       <c r="G20" s="132"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="445"/>
-      <c r="J20" s="446"/>
-      <c r="K20" s="446"/>
-      <c r="L20" s="446"/>
-      <c r="M20" s="446"/>
-      <c r="N20" s="449"/>
-      <c r="O20" s="241"/>
-      <c r="P20" s="241"/>
-      <c r="Q20" s="243" t="s">
+      <c r="H20" s="138"/>
+      <c r="I20" s="748"/>
+      <c r="J20" s="749"/>
+      <c r="K20" s="749"/>
+      <c r="L20" s="749"/>
+      <c r="M20" s="749"/>
+      <c r="N20" s="750"/>
+      <c r="O20" s="238"/>
+      <c r="P20" s="238"/>
+      <c r="Q20" s="240" t="s">
         <v>43</v>
       </c>
-      <c r="R20" s="241"/>
-      <c r="S20" s="241" t="s">
+      <c r="R20" s="238"/>
+      <c r="S20" s="238" t="s">
         <v>415</v>
       </c>
-      <c r="T20" s="241" t="b">
+      <c r="T20" s="238" t="b">
         <v>0</v>
       </c>
-      <c r="U20" s="241"/>
+      <c r="U20" s="238"/>
     </row>
     <row r="21" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="418"/>
-      <c r="B21" s="193"/>
+      <c r="A21" s="420"/>
+      <c r="B21" s="190"/>
       <c r="C21" s="116"/>
       <c r="D21" s="120"/>
-      <c r="E21" s="387"/>
-      <c r="F21" s="387"/>
+      <c r="E21" s="391"/>
+      <c r="F21" s="391"/>
       <c r="G21" s="132"/>
-      <c r="H21" s="140"/>
-      <c r="I21" s="450" t="s">
+      <c r="H21" s="138"/>
+      <c r="I21" s="446" t="s">
         <v>44</v>
       </c>
-      <c r="J21" s="451"/>
-      <c r="K21" s="451"/>
-      <c r="L21" s="362" t="s">
+      <c r="J21" s="447"/>
+      <c r="K21" s="447"/>
+      <c r="L21" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="M21" s="363"/>
-      <c r="N21" s="364"/>
-      <c r="O21" s="241"/>
-      <c r="P21" s="241"/>
-      <c r="Q21" s="243" t="s">
+      <c r="M21" s="367"/>
+      <c r="N21" s="368"/>
+      <c r="O21" s="238"/>
+      <c r="P21" s="238"/>
+      <c r="Q21" s="240" t="s">
         <v>46</v>
       </c>
-      <c r="R21" s="241"/>
-      <c r="S21" s="241" t="s">
+      <c r="R21" s="238"/>
+      <c r="S21" s="238" t="s">
         <v>416</v>
       </c>
-      <c r="T21" s="241" t="b">
+      <c r="T21" s="238" t="b">
         <v>0</v>
       </c>
-      <c r="U21" s="241"/>
+      <c r="U21" s="238"/>
     </row>
     <row r="22" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="419" t="s">
+      <c r="A22" s="421" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="347" t="s">
+      <c r="B22" s="351" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="348"/>
-      <c r="D22" s="343"/>
-      <c r="E22" s="343"/>
-      <c r="F22" s="343"/>
+      <c r="C22" s="352"/>
+      <c r="D22" s="347"/>
+      <c r="E22" s="347"/>
+      <c r="F22" s="347"/>
       <c r="G22" s="132"/>
-      <c r="H22" s="140"/>
-      <c r="I22" s="360"/>
-      <c r="J22" s="361"/>
-      <c r="K22" s="361"/>
-      <c r="L22" s="361"/>
-      <c r="M22" s="361"/>
-      <c r="N22" s="365"/>
-      <c r="O22" s="241"/>
-      <c r="P22" s="241"/>
-      <c r="Q22" s="243" t="s">
+      <c r="H22" s="138"/>
+      <c r="I22" s="364"/>
+      <c r="J22" s="365"/>
+      <c r="K22" s="365"/>
+      <c r="L22" s="365"/>
+      <c r="M22" s="365"/>
+      <c r="N22" s="369"/>
+      <c r="O22" s="238"/>
+      <c r="P22" s="238"/>
+      <c r="Q22" s="240" t="s">
         <v>49</v>
       </c>
-      <c r="R22" s="241"/>
-      <c r="S22" s="241"/>
-      <c r="T22" s="241"/>
-      <c r="U22" s="241"/>
+      <c r="R22" s="238"/>
+      <c r="S22" s="238"/>
+      <c r="T22" s="238"/>
+      <c r="U22" s="238"/>
     </row>
     <row r="23" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="420"/>
-      <c r="B23" s="349"/>
-      <c r="C23" s="350"/>
-      <c r="D23" s="344"/>
-      <c r="E23" s="344"/>
-      <c r="F23" s="344"/>
+      <c r="A23" s="422"/>
+      <c r="B23" s="353"/>
+      <c r="C23" s="354"/>
+      <c r="D23" s="348"/>
+      <c r="E23" s="348"/>
+      <c r="F23" s="348"/>
       <c r="G23" s="132"/>
-      <c r="H23" s="140"/>
-      <c r="I23" s="368" t="s">
+      <c r="H23" s="138"/>
+      <c r="I23" s="372" t="s">
         <v>50</v>
       </c>
-      <c r="J23" s="369"/>
-      <c r="K23" s="369"/>
-      <c r="L23" s="366" t="s">
+      <c r="J23" s="373"/>
+      <c r="K23" s="373"/>
+      <c r="L23" s="370" t="s">
         <v>51</v>
       </c>
-      <c r="M23" s="366"/>
-      <c r="N23" s="367"/>
-      <c r="O23" s="241"/>
-      <c r="P23" s="241"/>
-      <c r="Q23" s="243" t="s">
+      <c r="M23" s="370"/>
+      <c r="N23" s="371"/>
+      <c r="O23" s="238"/>
+      <c r="P23" s="238"/>
+      <c r="Q23" s="240" t="s">
         <v>52</v>
       </c>
-      <c r="R23" s="241"/>
-      <c r="S23" s="241"/>
-      <c r="T23" s="241"/>
-      <c r="U23" s="241"/>
+      <c r="R23" s="238"/>
+      <c r="S23" s="238"/>
+      <c r="T23" s="238"/>
+      <c r="U23" s="238"/>
     </row>
     <row r="24" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="148" t="s">
+      <c r="A24" s="146" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="351" t="s">
+      <c r="B24" s="355" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="352"/>
-      <c r="D24" s="407"/>
-      <c r="E24" s="407"/>
-      <c r="F24" s="407"/>
-      <c r="G24" s="394" t="s">
+      <c r="C24" s="356"/>
+      <c r="D24" s="409"/>
+      <c r="E24" s="409"/>
+      <c r="F24" s="409"/>
+      <c r="G24" s="398" t="s">
         <v>55</v>
       </c>
-      <c r="H24" s="324"/>
-      <c r="I24" s="399"/>
-      <c r="J24" s="400"/>
-      <c r="K24" s="400"/>
-      <c r="L24" s="400"/>
-      <c r="M24" s="400"/>
-      <c r="N24" s="401"/>
-      <c r="O24" s="241"/>
-      <c r="P24" s="241"/>
-      <c r="Q24" s="243" t="s">
+      <c r="H24" s="328"/>
+      <c r="I24" s="401"/>
+      <c r="J24" s="402"/>
+      <c r="K24" s="402"/>
+      <c r="L24" s="402"/>
+      <c r="M24" s="402"/>
+      <c r="N24" s="403"/>
+      <c r="O24" s="238"/>
+      <c r="P24" s="238"/>
+      <c r="Q24" s="240" t="s">
         <v>56</v>
       </c>
-      <c r="R24" s="241"/>
-      <c r="S24" s="241"/>
-      <c r="T24" s="241"/>
-      <c r="U24" s="241"/>
+      <c r="R24" s="238"/>
+      <c r="S24" s="238"/>
+      <c r="T24" s="238"/>
+      <c r="U24" s="238"/>
     </row>
     <row r="25" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="345" t="s">
+      <c r="A25" s="349" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="347" t="s">
+      <c r="B25" s="351" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="348"/>
-      <c r="D25" s="385"/>
-      <c r="E25" s="385"/>
-      <c r="F25" s="385"/>
+      <c r="C25" s="352"/>
+      <c r="D25" s="389"/>
+      <c r="E25" s="389"/>
+      <c r="F25" s="389"/>
       <c r="G25" s="90" t="s">
         <v>59</v>
       </c>
       <c r="H25" s="79"/>
-      <c r="I25" s="435"/>
-      <c r="J25" s="397"/>
-      <c r="K25" s="397"/>
-      <c r="L25" s="397"/>
-      <c r="M25" s="397"/>
-      <c r="N25" s="398"/>
+      <c r="I25" s="364"/>
+      <c r="J25" s="365"/>
+      <c r="K25" s="365"/>
+      <c r="L25" s="365"/>
+      <c r="M25" s="365"/>
+      <c r="N25" s="369"/>
       <c r="Q25" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="346"/>
-      <c r="B26" s="349"/>
-      <c r="C26" s="350"/>
-      <c r="D26" s="344"/>
-      <c r="E26" s="344"/>
-      <c r="F26" s="344"/>
+      <c r="A26" s="350"/>
+      <c r="B26" s="353"/>
+      <c r="C26" s="354"/>
+      <c r="D26" s="348"/>
+      <c r="E26" s="348"/>
+      <c r="F26" s="348"/>
       <c r="G26" s="132"/>
-      <c r="H26" s="140"/>
-      <c r="I26" s="358" t="s">
+      <c r="H26" s="138"/>
+      <c r="I26" s="362" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="359"/>
-      <c r="K26" s="359"/>
-      <c r="L26" s="359" t="s">
+      <c r="J26" s="363"/>
+      <c r="K26" s="363"/>
+      <c r="L26" s="363" t="s">
         <v>40</v>
       </c>
-      <c r="M26" s="359"/>
-      <c r="N26" s="374"/>
+      <c r="M26" s="363"/>
+      <c r="N26" s="378"/>
       <c r="Q26" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="345" t="s">
+      <c r="A27" s="349" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="353" t="s">
+      <c r="B27" s="357" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="348"/>
-      <c r="D27" s="385"/>
-      <c r="E27" s="385"/>
-      <c r="F27" s="385"/>
+      <c r="C27" s="352"/>
+      <c r="D27" s="389"/>
+      <c r="E27" s="389"/>
+      <c r="F27" s="389"/>
       <c r="G27" s="134"/>
       <c r="H27" s="85"/>
-      <c r="I27" s="435"/>
-      <c r="J27" s="397"/>
-      <c r="K27" s="397"/>
-      <c r="L27" s="397"/>
-      <c r="M27" s="397"/>
-      <c r="N27" s="398"/>
+      <c r="I27" s="364"/>
+      <c r="J27" s="365"/>
+      <c r="K27" s="365"/>
+      <c r="L27" s="365"/>
+      <c r="M27" s="365"/>
+      <c r="N27" s="369"/>
       <c r="Q27" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="346"/>
-      <c r="B28" s="349"/>
-      <c r="C28" s="350"/>
-      <c r="D28" s="344"/>
-      <c r="E28" s="344"/>
-      <c r="F28" s="344"/>
+      <c r="A28" s="350"/>
+      <c r="B28" s="353"/>
+      <c r="C28" s="354"/>
+      <c r="D28" s="348"/>
+      <c r="E28" s="348"/>
+      <c r="F28" s="348"/>
       <c r="G28" s="134"/>
       <c r="H28" s="85"/>
-      <c r="I28" s="354" t="s">
+      <c r="I28" s="358" t="s">
         <v>44</v>
       </c>
-      <c r="J28" s="355"/>
-      <c r="K28" s="355"/>
-      <c r="L28" s="356" t="s">
+      <c r="J28" s="359"/>
+      <c r="K28" s="359"/>
+      <c r="L28" s="360" t="s">
         <v>45</v>
       </c>
-      <c r="M28" s="355"/>
-      <c r="N28" s="357"/>
+      <c r="M28" s="359"/>
+      <c r="N28" s="361"/>
       <c r="Q28" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="345" t="s">
+      <c r="A29" s="349" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="347" t="s">
+      <c r="B29" s="351" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="348"/>
-      <c r="D29" s="412"/>
-      <c r="E29" s="385"/>
-      <c r="F29" s="413"/>
+      <c r="C29" s="352"/>
+      <c r="D29" s="414"/>
+      <c r="E29" s="389"/>
+      <c r="F29" s="415"/>
       <c r="G29" s="134"/>
-      <c r="H29" s="143"/>
-      <c r="I29" s="136"/>
-      <c r="J29" s="137"/>
-      <c r="K29" s="137"/>
-      <c r="L29" s="137"/>
-      <c r="M29" s="137"/>
-      <c r="N29" s="153"/>
+      <c r="H29" s="141"/>
+      <c r="I29" s="751"/>
+      <c r="J29" s="752"/>
+      <c r="K29" s="752"/>
+      <c r="L29" s="752"/>
+      <c r="M29" s="752"/>
+      <c r="N29" s="753"/>
       <c r="Q29" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="346"/>
-      <c r="B30" s="349"/>
-      <c r="C30" s="350"/>
-      <c r="D30" s="414"/>
-      <c r="E30" s="344"/>
-      <c r="F30" s="415"/>
+      <c r="A30" s="350"/>
+      <c r="B30" s="353"/>
+      <c r="C30" s="354"/>
+      <c r="D30" s="416"/>
+      <c r="E30" s="348"/>
+      <c r="F30" s="417"/>
       <c r="G30" s="134"/>
-      <c r="H30" s="143"/>
-      <c r="I30" s="370" t="s">
+      <c r="H30" s="141"/>
+      <c r="I30" s="374" t="s">
         <v>50</v>
       </c>
-      <c r="J30" s="370"/>
-      <c r="K30" s="370"/>
-      <c r="L30" s="370" t="s">
+      <c r="J30" s="374"/>
+      <c r="K30" s="374"/>
+      <c r="L30" s="374" t="s">
         <v>51</v>
       </c>
-      <c r="M30" s="370"/>
-      <c r="N30" s="436"/>
+      <c r="M30" s="374"/>
+      <c r="N30" s="437"/>
       <c r="Q30" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="150" t="s">
+      <c r="A31" s="148" t="s">
         <v>70</v>
       </c>
       <c r="B31" s="77" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="78"/>
-      <c r="D31" s="385"/>
-      <c r="E31" s="385"/>
-      <c r="F31" s="385"/>
-      <c r="G31" s="394" t="s">
+      <c r="D31" s="389"/>
+      <c r="E31" s="389"/>
+      <c r="F31" s="389"/>
+      <c r="G31" s="398" t="s">
         <v>55</v>
       </c>
-      <c r="H31" s="324"/>
-      <c r="I31" s="368"/>
-      <c r="J31" s="369"/>
-      <c r="K31" s="369"/>
-      <c r="L31" s="362"/>
-      <c r="M31" s="362"/>
-      <c r="N31" s="460"/>
+      <c r="H31" s="328"/>
+      <c r="I31" s="274"/>
+      <c r="J31" s="275"/>
+      <c r="K31" s="275"/>
+      <c r="L31" s="275"/>
+      <c r="M31" s="275"/>
+      <c r="N31" s="276"/>
       <c r="Q31" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="148" t="s">
+      <c r="A32" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="233" t="s">
+      <c r="B32" s="230" t="s">
         <v>74</v>
       </c>
       <c r="C32" s="78"/>
-      <c r="D32" s="407"/>
-      <c r="E32" s="407"/>
-      <c r="F32" s="407"/>
+      <c r="D32" s="409"/>
+      <c r="E32" s="409"/>
+      <c r="F32" s="409"/>
       <c r="G32" s="131" t="s">
         <v>75</v>
       </c>
       <c r="H32" s="135"/>
-      <c r="I32" s="457"/>
-      <c r="J32" s="458"/>
-      <c r="K32" s="458"/>
-      <c r="L32" s="458"/>
-      <c r="M32" s="458"/>
-      <c r="N32" s="459"/>
+      <c r="I32" s="329"/>
+      <c r="J32" s="330"/>
+      <c r="K32" s="330"/>
+      <c r="L32" s="330"/>
+      <c r="M32" s="330"/>
+      <c r="N32" s="453"/>
       <c r="Q32" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="395" t="s">
+      <c r="A33" s="399" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="351"/>
-      <c r="C33" s="352"/>
-      <c r="D33" s="396"/>
-      <c r="E33" s="396"/>
-      <c r="F33" s="396"/>
-      <c r="G33" s="178" t="s">
+      <c r="B33" s="355"/>
+      <c r="C33" s="356"/>
+      <c r="D33" s="400"/>
+      <c r="E33" s="400"/>
+      <c r="F33" s="400"/>
+      <c r="G33" s="175" t="s">
         <v>78</v>
       </c>
       <c r="H33" s="133"/>
-      <c r="I33" s="457"/>
-      <c r="J33" s="458"/>
-      <c r="K33" s="458"/>
-      <c r="L33" s="458"/>
-      <c r="M33" s="458"/>
-      <c r="N33" s="459"/>
+      <c r="I33" s="329"/>
+      <c r="J33" s="330"/>
+      <c r="K33" s="330"/>
+      <c r="L33" s="330"/>
+      <c r="M33" s="330"/>
+      <c r="N33" s="453"/>
       <c r="Q33" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="154" t="s">
+      <c r="A34" s="151" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="194"/>
-      <c r="C34" s="138"/>
-      <c r="D34" s="385"/>
-      <c r="E34" s="385"/>
-      <c r="F34" s="385"/>
+      <c r="B34" s="191"/>
+      <c r="C34" s="136"/>
+      <c r="D34" s="389"/>
+      <c r="E34" s="389"/>
+      <c r="F34" s="389"/>
       <c r="G34" s="90" t="s">
         <v>81</v>
       </c>
       <c r="H34" s="79"/>
-      <c r="I34" s="452"/>
-      <c r="J34" s="453"/>
-      <c r="K34" s="453"/>
-      <c r="L34" s="453"/>
-      <c r="M34" s="453"/>
-      <c r="N34" s="454"/>
+      <c r="I34" s="448"/>
+      <c r="J34" s="449"/>
+      <c r="K34" s="449"/>
+      <c r="L34" s="449"/>
+      <c r="M34" s="449"/>
+      <c r="N34" s="450"/>
       <c r="Q34" s="3" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="185" t="s">
+      <c r="A35" s="182" t="s">
         <v>83</v>
       </c>
-      <c r="B35" s="186"/>
-      <c r="C35" s="186"/>
-      <c r="D35" s="186"/>
-      <c r="E35" s="186"/>
-      <c r="F35" s="186"/>
-      <c r="G35" s="186"/>
-      <c r="H35" s="186"/>
-      <c r="I35" s="186"/>
-      <c r="J35" s="186"/>
-      <c r="K35" s="186"/>
-      <c r="L35" s="186"/>
-      <c r="M35" s="186"/>
-      <c r="N35" s="187"/>
+      <c r="B35" s="183"/>
+      <c r="C35" s="183"/>
+      <c r="D35" s="183"/>
+      <c r="E35" s="183"/>
+      <c r="F35" s="183"/>
+      <c r="G35" s="183"/>
+      <c r="H35" s="183"/>
+      <c r="I35" s="183"/>
+      <c r="J35" s="183"/>
+      <c r="K35" s="183"/>
+      <c r="L35" s="183"/>
+      <c r="M35" s="183"/>
+      <c r="N35" s="184"/>
       <c r="Q35" s="3" t="s">
         <v>84</v>
       </c>
@@ -11086,25 +11087,25 @@
       <c r="A36" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="B36" s="197" t="s">
+      <c r="B36" s="194" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="198"/>
-      <c r="D36" s="470"/>
-      <c r="E36" s="471"/>
-      <c r="F36" s="471"/>
-      <c r="G36" s="471"/>
-      <c r="H36" s="472"/>
-      <c r="I36" s="461" t="s">
+      <c r="C36" s="195"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
+      <c r="G36" s="464"/>
+      <c r="H36" s="465"/>
+      <c r="I36" s="454" t="s">
         <v>87</v>
       </c>
-      <c r="J36" s="461"/>
-      <c r="K36" s="461"/>
-      <c r="L36" s="462"/>
-      <c r="M36" s="463" t="s">
+      <c r="J36" s="454"/>
+      <c r="K36" s="454"/>
+      <c r="L36" s="455"/>
+      <c r="M36" s="456" t="s">
         <v>88</v>
       </c>
-      <c r="N36" s="464"/>
+      <c r="N36" s="457"/>
       <c r="Q36" s="3" t="s">
         <v>89</v>
       </c>
@@ -11114,104 +11115,104 @@
       <c r="B37" s="85" t="s">
         <v>90</v>
       </c>
-      <c r="C37" s="143"/>
-      <c r="D37" s="287"/>
-      <c r="E37" s="288"/>
-      <c r="F37" s="289"/>
-      <c r="G37" s="303" t="s">
+      <c r="C37" s="141"/>
+      <c r="D37" s="291"/>
+      <c r="E37" s="292"/>
+      <c r="F37" s="293"/>
+      <c r="G37" s="307" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="303"/>
-      <c r="I37" s="285"/>
-      <c r="J37" s="285"/>
-      <c r="K37" s="285"/>
-      <c r="L37" s="286"/>
-      <c r="M37" s="283"/>
-      <c r="N37" s="284"/>
+      <c r="H37" s="307"/>
+      <c r="I37" s="289"/>
+      <c r="J37" s="289"/>
+      <c r="K37" s="289"/>
+      <c r="L37" s="290"/>
+      <c r="M37" s="287"/>
+      <c r="N37" s="288"/>
       <c r="Q37" s="3" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="155"/>
-      <c r="B38" s="190" t="s">
+      <c r="A38" s="152"/>
+      <c r="B38" s="187" t="s">
         <v>93</v>
       </c>
-      <c r="C38" s="189"/>
-      <c r="D38" s="287"/>
-      <c r="E38" s="288"/>
-      <c r="F38" s="288"/>
-      <c r="G38" s="288"/>
-      <c r="H38" s="289"/>
-      <c r="I38" s="285"/>
-      <c r="J38" s="285"/>
-      <c r="K38" s="285"/>
-      <c r="L38" s="286"/>
-      <c r="M38" s="283"/>
-      <c r="N38" s="284"/>
+      <c r="C38" s="186"/>
+      <c r="D38" s="291"/>
+      <c r="E38" s="292"/>
+      <c r="F38" s="292"/>
+      <c r="G38" s="292"/>
+      <c r="H38" s="293"/>
+      <c r="I38" s="289"/>
+      <c r="J38" s="289"/>
+      <c r="K38" s="289"/>
+      <c r="L38" s="290"/>
+      <c r="M38" s="287"/>
+      <c r="N38" s="288"/>
       <c r="Q38" s="3" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="156"/>
+      <c r="A39" s="153"/>
       <c r="B39" s="77" t="s">
         <v>95</v>
       </c>
       <c r="C39" s="78"/>
-      <c r="D39" s="287"/>
-      <c r="E39" s="288"/>
-      <c r="F39" s="288"/>
-      <c r="G39" s="288"/>
-      <c r="H39" s="289"/>
-      <c r="I39" s="285"/>
-      <c r="J39" s="285"/>
-      <c r="K39" s="285"/>
-      <c r="L39" s="286"/>
-      <c r="M39" s="283"/>
-      <c r="N39" s="284"/>
+      <c r="D39" s="291"/>
+      <c r="E39" s="292"/>
+      <c r="F39" s="292"/>
+      <c r="G39" s="292"/>
+      <c r="H39" s="293"/>
+      <c r="I39" s="289"/>
+      <c r="J39" s="289"/>
+      <c r="K39" s="289"/>
+      <c r="L39" s="290"/>
+      <c r="M39" s="287"/>
+      <c r="N39" s="288"/>
       <c r="Q39" s="3" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="156"/>
+      <c r="A40" s="153"/>
       <c r="B40" s="77" t="s">
         <v>97</v>
       </c>
       <c r="C40" s="78"/>
-      <c r="D40" s="287"/>
-      <c r="E40" s="288"/>
-      <c r="F40" s="288"/>
-      <c r="G40" s="288"/>
-      <c r="H40" s="289"/>
-      <c r="I40" s="285"/>
-      <c r="J40" s="285"/>
-      <c r="K40" s="285"/>
-      <c r="L40" s="286"/>
-      <c r="M40" s="283"/>
-      <c r="N40" s="284"/>
+      <c r="D40" s="291"/>
+      <c r="E40" s="292"/>
+      <c r="F40" s="292"/>
+      <c r="G40" s="292"/>
+      <c r="H40" s="293"/>
+      <c r="I40" s="289"/>
+      <c r="J40" s="289"/>
+      <c r="K40" s="289"/>
+      <c r="L40" s="290"/>
+      <c r="M40" s="287"/>
+      <c r="N40" s="288"/>
       <c r="Q40" s="3" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="156"/>
+      <c r="A41" s="153"/>
       <c r="B41" s="77" t="s">
         <v>99</v>
       </c>
       <c r="C41" s="78"/>
-      <c r="D41" s="287"/>
-      <c r="E41" s="288"/>
-      <c r="F41" s="288"/>
-      <c r="G41" s="288"/>
-      <c r="H41" s="289"/>
-      <c r="I41" s="285"/>
-      <c r="J41" s="285"/>
-      <c r="K41" s="285"/>
-      <c r="L41" s="286"/>
-      <c r="M41" s="283"/>
-      <c r="N41" s="284"/>
+      <c r="D41" s="291"/>
+      <c r="E41" s="292"/>
+      <c r="F41" s="292"/>
+      <c r="G41" s="292"/>
+      <c r="H41" s="293"/>
+      <c r="I41" s="289"/>
+      <c r="J41" s="289"/>
+      <c r="K41" s="289"/>
+      <c r="L41" s="290"/>
+      <c r="M41" s="287"/>
+      <c r="N41" s="288"/>
       <c r="Q41" s="3" t="s">
         <v>100</v>
       </c>
@@ -11222,84 +11223,84 @@
         <v>101</v>
       </c>
       <c r="C42" s="117"/>
-      <c r="D42" s="287"/>
-      <c r="E42" s="288"/>
-      <c r="F42" s="288"/>
-      <c r="G42" s="288"/>
-      <c r="H42" s="289"/>
-      <c r="I42" s="285"/>
-      <c r="J42" s="285"/>
-      <c r="K42" s="285"/>
-      <c r="L42" s="286"/>
-      <c r="M42" s="283"/>
-      <c r="N42" s="284"/>
+      <c r="D42" s="291"/>
+      <c r="E42" s="292"/>
+      <c r="F42" s="292"/>
+      <c r="G42" s="292"/>
+      <c r="H42" s="293"/>
+      <c r="I42" s="289"/>
+      <c r="J42" s="289"/>
+      <c r="K42" s="289"/>
+      <c r="L42" s="290"/>
+      <c r="M42" s="287"/>
+      <c r="N42" s="288"/>
       <c r="Q42" s="3" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="188" t="s">
+      <c r="A43" s="185" t="s">
         <v>103</v>
       </c>
-      <c r="B43" s="195" t="s">
+      <c r="B43" s="192" t="s">
         <v>104</v>
       </c>
       <c r="C43" s="84"/>
-      <c r="D43" s="287"/>
-      <c r="E43" s="288"/>
-      <c r="F43" s="288"/>
-      <c r="G43" s="288"/>
-      <c r="H43" s="289"/>
-      <c r="I43" s="285"/>
-      <c r="J43" s="285"/>
-      <c r="K43" s="285"/>
-      <c r="L43" s="286"/>
-      <c r="M43" s="283"/>
-      <c r="N43" s="284"/>
+      <c r="D43" s="291"/>
+      <c r="E43" s="292"/>
+      <c r="F43" s="292"/>
+      <c r="G43" s="292"/>
+      <c r="H43" s="293"/>
+      <c r="I43" s="289"/>
+      <c r="J43" s="289"/>
+      <c r="K43" s="289"/>
+      <c r="L43" s="290"/>
+      <c r="M43" s="287"/>
+      <c r="N43" s="288"/>
       <c r="Q43" s="3" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="132"/>
-      <c r="B44" s="140" t="s">
+      <c r="B44" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="140"/>
-      <c r="D44" s="287"/>
-      <c r="E44" s="288"/>
-      <c r="F44" s="289"/>
-      <c r="G44" s="303" t="s">
+      <c r="C44" s="138"/>
+      <c r="D44" s="291"/>
+      <c r="E44" s="292"/>
+      <c r="F44" s="293"/>
+      <c r="G44" s="307" t="s">
         <v>106</v>
       </c>
-      <c r="H44" s="303"/>
-      <c r="I44" s="285"/>
-      <c r="J44" s="285"/>
-      <c r="K44" s="285"/>
-      <c r="L44" s="286"/>
-      <c r="M44" s="283"/>
-      <c r="N44" s="284"/>
+      <c r="H44" s="307"/>
+      <c r="I44" s="289"/>
+      <c r="J44" s="289"/>
+      <c r="K44" s="289"/>
+      <c r="L44" s="290"/>
+      <c r="M44" s="287"/>
+      <c r="N44" s="288"/>
       <c r="Q44" s="3" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="155"/>
-      <c r="B45" s="183" t="s">
+      <c r="A45" s="152"/>
+      <c r="B45" s="180" t="s">
         <v>17</v>
       </c>
-      <c r="C45" s="183"/>
-      <c r="D45" s="287"/>
-      <c r="E45" s="288"/>
-      <c r="F45" s="288"/>
-      <c r="G45" s="288"/>
-      <c r="H45" s="289"/>
-      <c r="I45" s="285"/>
-      <c r="J45" s="285"/>
-      <c r="K45" s="285"/>
-      <c r="L45" s="286"/>
-      <c r="M45" s="283"/>
-      <c r="N45" s="284"/>
+      <c r="C45" s="180"/>
+      <c r="D45" s="291"/>
+      <c r="E45" s="292"/>
+      <c r="F45" s="292"/>
+      <c r="G45" s="292"/>
+      <c r="H45" s="293"/>
+      <c r="I45" s="289"/>
+      <c r="J45" s="289"/>
+      <c r="K45" s="289"/>
+      <c r="L45" s="290"/>
+      <c r="M45" s="287"/>
+      <c r="N45" s="288"/>
       <c r="Q45" s="3" t="s">
         <v>108</v>
       </c>
@@ -11308,142 +11309,142 @@
       <c r="A46" s="132" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="347" t="s">
+      <c r="B46" s="351" t="s">
         <v>110</v>
       </c>
-      <c r="C46" s="347"/>
-      <c r="D46" s="347"/>
-      <c r="E46" s="347"/>
-      <c r="F46" s="347"/>
-      <c r="G46" s="347"/>
-      <c r="H46" s="348"/>
-      <c r="I46" s="285"/>
-      <c r="J46" s="285"/>
-      <c r="K46" s="285"/>
-      <c r="L46" s="286"/>
-      <c r="M46" s="283"/>
-      <c r="N46" s="284"/>
+      <c r="C46" s="351"/>
+      <c r="D46" s="351"/>
+      <c r="E46" s="351"/>
+      <c r="F46" s="351"/>
+      <c r="G46" s="351"/>
+      <c r="H46" s="352"/>
+      <c r="I46" s="289"/>
+      <c r="J46" s="289"/>
+      <c r="K46" s="289"/>
+      <c r="L46" s="290"/>
+      <c r="M46" s="287"/>
+      <c r="N46" s="288"/>
       <c r="Q46" s="3" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="132"/>
-      <c r="B47" s="140" t="s">
+      <c r="B47" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="C47" s="140"/>
-      <c r="D47" s="300"/>
-      <c r="E47" s="301"/>
-      <c r="F47" s="301"/>
-      <c r="G47" s="301"/>
-      <c r="H47" s="302"/>
-      <c r="I47" s="285"/>
-      <c r="J47" s="285"/>
-      <c r="K47" s="285"/>
-      <c r="L47" s="286"/>
-      <c r="M47" s="283"/>
-      <c r="N47" s="284"/>
+      <c r="C47" s="138"/>
+      <c r="D47" s="304"/>
+      <c r="E47" s="305"/>
+      <c r="F47" s="305"/>
+      <c r="G47" s="305"/>
+      <c r="H47" s="306"/>
+      <c r="I47" s="289"/>
+      <c r="J47" s="289"/>
+      <c r="K47" s="289"/>
+      <c r="L47" s="290"/>
+      <c r="M47" s="287"/>
+      <c r="N47" s="288"/>
       <c r="Q47" s="3" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="132"/>
-      <c r="B48" s="140" t="s">
+      <c r="B48" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="C48" s="140"/>
-      <c r="D48" s="300"/>
-      <c r="E48" s="301"/>
-      <c r="F48" s="301"/>
-      <c r="G48" s="301"/>
-      <c r="H48" s="302"/>
-      <c r="I48" s="285"/>
-      <c r="J48" s="285"/>
-      <c r="K48" s="285"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="283"/>
-      <c r="N48" s="284"/>
+      <c r="C48" s="138"/>
+      <c r="D48" s="304"/>
+      <c r="E48" s="305"/>
+      <c r="F48" s="305"/>
+      <c r="G48" s="305"/>
+      <c r="H48" s="306"/>
+      <c r="I48" s="289"/>
+      <c r="J48" s="289"/>
+      <c r="K48" s="289"/>
+      <c r="L48" s="290"/>
+      <c r="M48" s="287"/>
+      <c r="N48" s="288"/>
       <c r="Q48" s="3" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="157"/>
-      <c r="B49" s="184" t="s">
+      <c r="A49" s="154"/>
+      <c r="B49" s="181" t="s">
         <v>17</v>
       </c>
-      <c r="C49" s="184"/>
-      <c r="D49" s="477"/>
-      <c r="E49" s="478"/>
-      <c r="F49" s="478"/>
-      <c r="G49" s="478"/>
-      <c r="H49" s="479"/>
-      <c r="I49" s="475" t="s">
+      <c r="C49" s="181"/>
+      <c r="D49" s="470"/>
+      <c r="E49" s="471"/>
+      <c r="F49" s="471"/>
+      <c r="G49" s="471"/>
+      <c r="H49" s="472"/>
+      <c r="I49" s="468" t="s">
         <v>114</v>
       </c>
-      <c r="J49" s="475"/>
-      <c r="K49" s="475"/>
-      <c r="L49" s="475"/>
-      <c r="M49" s="475"/>
-      <c r="N49" s="476"/>
+      <c r="J49" s="468"/>
+      <c r="K49" s="468"/>
+      <c r="L49" s="468"/>
+      <c r="M49" s="468"/>
+      <c r="N49" s="469"/>
       <c r="Q49" s="3" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="158" t="s">
+      <c r="A50" s="155" t="s">
         <v>116</v>
       </c>
-      <c r="B50" s="158"/>
+      <c r="B50" s="155"/>
       <c r="C50" s="80"/>
       <c r="D50" s="81"/>
       <c r="E50" s="81"/>
       <c r="F50" s="81"/>
       <c r="G50" s="81"/>
       <c r="H50" s="81"/>
-      <c r="I50" s="383" t="s">
+      <c r="I50" s="387" t="s">
         <v>117</v>
       </c>
-      <c r="J50" s="383"/>
-      <c r="K50" s="383"/>
-      <c r="L50" s="383"/>
-      <c r="M50" s="383"/>
-      <c r="N50" s="384"/>
+      <c r="J50" s="387"/>
+      <c r="K50" s="387"/>
+      <c r="L50" s="387"/>
+      <c r="M50" s="387"/>
+      <c r="N50" s="388"/>
       <c r="Q50" s="3" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="375" t="s">
+      <c r="A51" s="379" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="319" t="s">
+      <c r="B51" s="323" t="s">
         <v>120</v>
       </c>
-      <c r="C51" s="319"/>
-      <c r="D51" s="304" t="s">
+      <c r="C51" s="323"/>
+      <c r="D51" s="308" t="s">
         <v>121</v>
       </c>
-      <c r="E51" s="305"/>
-      <c r="F51" s="322"/>
-      <c r="G51" s="304" t="s">
+      <c r="E51" s="309"/>
+      <c r="F51" s="326"/>
+      <c r="G51" s="308" t="s">
         <v>122</v>
       </c>
-      <c r="H51" s="305"/>
-      <c r="I51" s="306"/>
-      <c r="J51" s="402" t="s">
+      <c r="H51" s="309"/>
+      <c r="I51" s="310"/>
+      <c r="J51" s="404" t="s">
         <v>123</v>
       </c>
-      <c r="K51" s="403"/>
-      <c r="L51" s="295" t="s">
+      <c r="K51" s="405"/>
+      <c r="L51" s="299" t="s">
         <v>124</v>
       </c>
-      <c r="M51" s="377" t="s">
+      <c r="M51" s="381" t="s">
         <v>125</v>
       </c>
-      <c r="N51" s="473" t="s">
+      <c r="N51" s="466" t="s">
         <v>126</v>
       </c>
       <c r="Q51" s="3" t="s">
@@ -11451,43 +11452,43 @@
       </c>
     </row>
     <row r="52" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="376"/>
-      <c r="B52" s="320"/>
-      <c r="C52" s="320"/>
-      <c r="D52" s="307"/>
-      <c r="E52" s="308"/>
-      <c r="F52" s="323"/>
-      <c r="G52" s="307"/>
-      <c r="H52" s="308"/>
-      <c r="I52" s="309"/>
-      <c r="J52" s="404"/>
-      <c r="K52" s="405"/>
-      <c r="L52" s="295"/>
-      <c r="M52" s="377"/>
-      <c r="N52" s="473"/>
+      <c r="A52" s="380"/>
+      <c r="B52" s="324"/>
+      <c r="C52" s="324"/>
+      <c r="D52" s="311"/>
+      <c r="E52" s="312"/>
+      <c r="F52" s="327"/>
+      <c r="G52" s="311"/>
+      <c r="H52" s="312"/>
+      <c r="I52" s="313"/>
+      <c r="J52" s="406"/>
+      <c r="K52" s="407"/>
+      <c r="L52" s="299"/>
+      <c r="M52" s="381"/>
+      <c r="N52" s="466"/>
       <c r="Q52" s="3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="196"/>
-      <c r="B53" s="321"/>
-      <c r="C53" s="321"/>
-      <c r="D53" s="310"/>
-      <c r="E53" s="311"/>
-      <c r="F53" s="324"/>
-      <c r="G53" s="310"/>
-      <c r="H53" s="311"/>
-      <c r="I53" s="312"/>
+      <c r="A53" s="193"/>
+      <c r="B53" s="325"/>
+      <c r="C53" s="325"/>
+      <c r="D53" s="314"/>
+      <c r="E53" s="315"/>
+      <c r="F53" s="328"/>
+      <c r="G53" s="314"/>
+      <c r="H53" s="315"/>
+      <c r="I53" s="316"/>
       <c r="J53" s="86" t="s">
         <v>129</v>
       </c>
       <c r="K53" s="87" t="s">
         <v>130</v>
       </c>
-      <c r="L53" s="296"/>
-      <c r="M53" s="378"/>
-      <c r="N53" s="474"/>
+      <c r="L53" s="300"/>
+      <c r="M53" s="382"/>
+      <c r="N53" s="467"/>
       <c r="O53" s="88"/>
       <c r="P53" s="88"/>
       <c r="Q53" s="3" t="s">
@@ -11495,177 +11496,177 @@
       </c>
     </row>
     <row r="54" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="200"/>
-      <c r="B54" s="201" t="s">
+      <c r="A54" s="197"/>
+      <c r="B54" s="198" t="s">
         <v>132</v>
       </c>
-      <c r="C54" s="201"/>
-      <c r="D54" s="325"/>
-      <c r="E54" s="326"/>
-      <c r="F54" s="327"/>
-      <c r="G54" s="297"/>
-      <c r="H54" s="298"/>
-      <c r="I54" s="299"/>
-      <c r="J54" s="270"/>
+      <c r="C54" s="198"/>
+      <c r="D54" s="329"/>
+      <c r="E54" s="330"/>
+      <c r="F54" s="331"/>
+      <c r="G54" s="301"/>
+      <c r="H54" s="302"/>
+      <c r="I54" s="303"/>
+      <c r="J54" s="267"/>
       <c r="K54" s="10"/>
-      <c r="L54" s="271"/>
-      <c r="M54" s="272"/>
-      <c r="N54" s="139"/>
+      <c r="L54" s="268"/>
+      <c r="M54" s="269"/>
+      <c r="N54" s="137"/>
       <c r="Q54" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="200"/>
-      <c r="B55" s="201" t="s">
+      <c r="A55" s="197"/>
+      <c r="B55" s="198" t="s">
         <v>134</v>
       </c>
-      <c r="C55" s="201"/>
-      <c r="D55" s="325"/>
-      <c r="E55" s="326"/>
-      <c r="F55" s="327"/>
-      <c r="G55" s="297"/>
-      <c r="H55" s="298"/>
-      <c r="I55" s="299"/>
-      <c r="J55" s="270"/>
+      <c r="C55" s="198"/>
+      <c r="D55" s="329"/>
+      <c r="E55" s="330"/>
+      <c r="F55" s="331"/>
+      <c r="G55" s="301"/>
+      <c r="H55" s="302"/>
+      <c r="I55" s="303"/>
+      <c r="J55" s="267"/>
       <c r="K55" s="10"/>
-      <c r="L55" s="204"/>
-      <c r="M55" s="273"/>
-      <c r="N55" s="139"/>
+      <c r="L55" s="201"/>
+      <c r="M55" s="270"/>
+      <c r="N55" s="137"/>
       <c r="Q55" s="3" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="200"/>
-      <c r="B56" s="201" t="s">
+      <c r="A56" s="197"/>
+      <c r="B56" s="198" t="s">
         <v>136</v>
       </c>
-      <c r="C56" s="201"/>
-      <c r="D56" s="325"/>
-      <c r="E56" s="326"/>
-      <c r="F56" s="327"/>
-      <c r="G56" s="313"/>
-      <c r="H56" s="314"/>
-      <c r="I56" s="315"/>
-      <c r="J56" s="270"/>
+      <c r="C56" s="198"/>
+      <c r="D56" s="329"/>
+      <c r="E56" s="330"/>
+      <c r="F56" s="331"/>
+      <c r="G56" s="317"/>
+      <c r="H56" s="318"/>
+      <c r="I56" s="319"/>
+      <c r="J56" s="267"/>
       <c r="K56" s="10"/>
-      <c r="L56" s="271"/>
-      <c r="M56" s="272"/>
-      <c r="N56" s="139"/>
+      <c r="L56" s="268"/>
+      <c r="M56" s="269"/>
+      <c r="N56" s="137"/>
       <c r="Q56" s="3" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="200"/>
-      <c r="B57" s="201" t="s">
+      <c r="A57" s="197"/>
+      <c r="B57" s="198" t="s">
         <v>138</v>
       </c>
-      <c r="C57" s="201"/>
-      <c r="D57" s="325"/>
-      <c r="E57" s="326"/>
-      <c r="F57" s="327"/>
-      <c r="G57" s="313"/>
-      <c r="H57" s="314"/>
-      <c r="I57" s="315"/>
-      <c r="J57" s="270"/>
+      <c r="C57" s="198"/>
+      <c r="D57" s="329"/>
+      <c r="E57" s="330"/>
+      <c r="F57" s="331"/>
+      <c r="G57" s="317"/>
+      <c r="H57" s="318"/>
+      <c r="I57" s="319"/>
+      <c r="J57" s="267"/>
       <c r="K57" s="10"/>
-      <c r="L57" s="271"/>
-      <c r="M57" s="273"/>
-      <c r="N57" s="139"/>
+      <c r="L57" s="268"/>
+      <c r="M57" s="270"/>
+      <c r="N57" s="137"/>
       <c r="Q57" s="3" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="202"/>
-      <c r="B58" s="203" t="s">
+      <c r="A58" s="199"/>
+      <c r="B58" s="200" t="s">
         <v>140</v>
       </c>
-      <c r="C58" s="203"/>
-      <c r="D58" s="328"/>
-      <c r="E58" s="329"/>
-      <c r="F58" s="330"/>
-      <c r="G58" s="316"/>
-      <c r="H58" s="317"/>
-      <c r="I58" s="318"/>
-      <c r="J58" s="274"/>
-      <c r="K58" s="199"/>
+      <c r="C58" s="200"/>
+      <c r="D58" s="332"/>
+      <c r="E58" s="333"/>
+      <c r="F58" s="334"/>
+      <c r="G58" s="320"/>
+      <c r="H58" s="321"/>
+      <c r="I58" s="322"/>
+      <c r="J58" s="271"/>
+      <c r="K58" s="196"/>
       <c r="L58" s="9"/>
-      <c r="M58" s="275"/>
-      <c r="N58" s="139"/>
+      <c r="M58" s="272"/>
+      <c r="N58" s="137"/>
       <c r="Q58" s="3" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="280" t="s">
+      <c r="A59" s="281" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="281"/>
-      <c r="C59" s="281"/>
-      <c r="D59" s="281"/>
-      <c r="E59" s="281"/>
-      <c r="F59" s="281"/>
-      <c r="G59" s="281"/>
-      <c r="H59" s="281"/>
-      <c r="I59" s="281"/>
-      <c r="J59" s="281"/>
-      <c r="K59" s="281"/>
-      <c r="L59" s="281"/>
-      <c r="M59" s="281"/>
-      <c r="N59" s="282"/>
+      <c r="B59" s="282"/>
+      <c r="C59" s="282"/>
+      <c r="D59" s="282"/>
+      <c r="E59" s="282"/>
+      <c r="F59" s="282"/>
+      <c r="G59" s="282"/>
+      <c r="H59" s="282"/>
+      <c r="I59" s="282"/>
+      <c r="J59" s="282"/>
+      <c r="K59" s="282"/>
+      <c r="L59" s="282"/>
+      <c r="M59" s="282"/>
+      <c r="N59" s="283"/>
       <c r="Q59" s="3" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="277" t="s">
+      <c r="A60" s="278" t="s">
         <v>143</v>
       </c>
-      <c r="B60" s="278"/>
-      <c r="C60" s="279"/>
-      <c r="D60" s="290" t="s">
+      <c r="B60" s="279"/>
+      <c r="C60" s="280"/>
+      <c r="D60" s="294" t="s">
         <v>144</v>
       </c>
-      <c r="E60" s="291"/>
-      <c r="F60" s="291"/>
-      <c r="G60" s="291"/>
-      <c r="H60" s="291"/>
-      <c r="I60" s="292"/>
-      <c r="J60" s="293" t="s">
+      <c r="E60" s="295"/>
+      <c r="F60" s="295"/>
+      <c r="G60" s="295"/>
+      <c r="H60" s="295"/>
+      <c r="I60" s="296"/>
+      <c r="J60" s="297" t="s">
         <v>145</v>
       </c>
-      <c r="K60" s="294"/>
-      <c r="L60" s="748">
+      <c r="K60" s="298"/>
+      <c r="L60" s="284">
         <f ca="1">NOW()</f>
-        <v>45982.693544444446</v>
-      </c>
-      <c r="M60" s="749"/>
-      <c r="N60" s="750"/>
+        <v>45982.839370949077</v>
+      </c>
+      <c r="M60" s="285"/>
+      <c r="N60" s="286"/>
       <c r="Q60" s="3" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="124" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="276" t="s">
+      <c r="A61" s="277" t="s">
         <v>404</v>
       </c>
-      <c r="B61" s="276"/>
-      <c r="C61" s="276"/>
-      <c r="D61" s="276"/>
-      <c r="E61" s="276"/>
-      <c r="F61" s="276"/>
-      <c r="G61" s="276"/>
-      <c r="H61" s="276"/>
-      <c r="I61" s="276"/>
-      <c r="J61" s="276"/>
-      <c r="K61" s="276"/>
-      <c r="L61" s="276"/>
-      <c r="M61" s="276"/>
-      <c r="N61" s="276"/>
-      <c r="Q61" s="216" t="s">
+      <c r="B61" s="277"/>
+      <c r="C61" s="277"/>
+      <c r="D61" s="277"/>
+      <c r="E61" s="277"/>
+      <c r="F61" s="277"/>
+      <c r="G61" s="277"/>
+      <c r="H61" s="277"/>
+      <c r="I61" s="277"/>
+      <c r="J61" s="277"/>
+      <c r="K61" s="277"/>
+      <c r="L61" s="277"/>
+      <c r="M61" s="277"/>
+      <c r="N61" s="277"/>
+      <c r="Q61" s="213" t="s">
         <v>147</v>
       </c>
     </row>
@@ -12262,12 +12263,12 @@
       <c r="A93" s="89"/>
       <c r="B93" s="89"/>
       <c r="C93" s="89"/>
-      <c r="D93" s="230" t="s">
+      <c r="D93" s="227" t="s">
         <v>179</v>
       </c>
       <c r="E93" s="89"/>
       <c r="F93" s="89"/>
-      <c r="G93" s="231"/>
+      <c r="G93" s="228"/>
       <c r="H93" s="89"/>
       <c r="I93" s="89"/>
       <c r="J93" s="89"/>
@@ -15392,7 +15393,7 @@
       <headerFooter alignWithMargins="0"/>
     </customSheetView>
   </customSheetViews>
-  <mergeCells count="143">
+  <mergeCells count="144">
     <mergeCell ref="N51:N53"/>
     <mergeCell ref="D39:H39"/>
     <mergeCell ref="D40:H40"/>
@@ -15417,13 +15418,11 @@
     <mergeCell ref="D32:F32"/>
     <mergeCell ref="I25:K25"/>
     <mergeCell ref="I33:N33"/>
-    <mergeCell ref="L31:N31"/>
     <mergeCell ref="I38:L38"/>
     <mergeCell ref="I39:L39"/>
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="I32:N32"/>
     <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I31:K31"/>
     <mergeCell ref="M36:N36"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="I26:K26"/>
@@ -15433,6 +15432,8 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="J16:N16"/>
     <mergeCell ref="D36:H36"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="L29:N29"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="G16:I16"/>
@@ -15503,6 +15504,7 @@
     <mergeCell ref="I30:K30"/>
     <mergeCell ref="A5:N5"/>
     <mergeCell ref="L18:N18"/>
+    <mergeCell ref="I46:L46"/>
     <mergeCell ref="G56:I56"/>
     <mergeCell ref="G58:I58"/>
     <mergeCell ref="B51:C53"/>
@@ -15512,6 +15514,7 @@
     <mergeCell ref="D56:F56"/>
     <mergeCell ref="D57:F57"/>
     <mergeCell ref="D58:F58"/>
+    <mergeCell ref="I31:N31"/>
     <mergeCell ref="A61:N61"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="A59:N59"/>
@@ -15535,7 +15538,6 @@
     <mergeCell ref="G51:I53"/>
     <mergeCell ref="G55:I55"/>
     <mergeCell ref="G57:I57"/>
-    <mergeCell ref="I46:L46"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -16023,198 +16025,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="480"/>
-      <c r="B1" s="481"/>
-      <c r="C1" s="481"/>
-      <c r="D1" s="481"/>
-      <c r="E1" s="481"/>
-      <c r="F1" s="481"/>
-      <c r="G1" s="481"/>
-      <c r="H1" s="481"/>
-      <c r="I1" s="481"/>
-      <c r="J1" s="481"/>
-      <c r="K1" s="482"/>
+      <c r="A1" s="473"/>
+      <c r="B1" s="474"/>
+      <c r="C1" s="474"/>
+      <c r="D1" s="474"/>
+      <c r="E1" s="474"/>
+      <c r="F1" s="474"/>
+      <c r="G1" s="474"/>
+      <c r="H1" s="474"/>
+      <c r="I1" s="474"/>
+      <c r="J1" s="474"/>
+      <c r="K1" s="475"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="493" t="s">
+      <c r="A2" s="486" t="s">
         <v>304</v>
       </c>
-      <c r="B2" s="494"/>
-      <c r="C2" s="494"/>
-      <c r="D2" s="494"/>
-      <c r="E2" s="494"/>
-      <c r="F2" s="494"/>
-      <c r="G2" s="494"/>
-      <c r="H2" s="494"/>
-      <c r="I2" s="494"/>
-      <c r="J2" s="494"/>
-      <c r="K2" s="495"/>
+      <c r="B2" s="487"/>
+      <c r="C2" s="487"/>
+      <c r="D2" s="487"/>
+      <c r="E2" s="487"/>
+      <c r="F2" s="487"/>
+      <c r="G2" s="487"/>
+      <c r="H2" s="487"/>
+      <c r="I2" s="487"/>
+      <c r="J2" s="487"/>
+      <c r="K2" s="488"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="121" t="s">
         <v>305</v>
       </c>
-      <c r="B3" s="483" t="s">
+      <c r="B3" s="476" t="s">
         <v>306</v>
       </c>
-      <c r="C3" s="483"/>
-      <c r="D3" s="483"/>
-      <c r="E3" s="484"/>
-      <c r="F3" s="491" t="s">
+      <c r="C3" s="476"/>
+      <c r="D3" s="476"/>
+      <c r="E3" s="477"/>
+      <c r="F3" s="484" t="s">
         <v>307</v>
       </c>
-      <c r="G3" s="487" t="s">
+      <c r="G3" s="480" t="s">
         <v>308</v>
       </c>
-      <c r="H3" s="484"/>
-      <c r="I3" s="487" t="s">
+      <c r="H3" s="477"/>
+      <c r="I3" s="480" t="s">
         <v>309</v>
       </c>
-      <c r="J3" s="489" t="s">
+      <c r="J3" s="482" t="s">
         <v>310</v>
       </c>
-      <c r="K3" s="490"/>
+      <c r="K3" s="483"/>
     </row>
     <row r="4" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="485"/>
-      <c r="C4" s="485"/>
-      <c r="D4" s="485"/>
-      <c r="E4" s="486"/>
-      <c r="F4" s="492"/>
-      <c r="G4" s="488"/>
-      <c r="H4" s="486"/>
-      <c r="I4" s="488"/>
+      <c r="B4" s="478"/>
+      <c r="C4" s="478"/>
+      <c r="D4" s="478"/>
+      <c r="E4" s="479"/>
+      <c r="F4" s="485"/>
+      <c r="G4" s="481"/>
+      <c r="H4" s="479"/>
+      <c r="I4" s="481"/>
       <c r="J4" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="K4" s="234" t="s">
+      <c r="K4" s="231" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="499"/>
-      <c r="B5" s="500"/>
-      <c r="C5" s="500"/>
-      <c r="D5" s="500"/>
-      <c r="E5" s="500"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="498"/>
-      <c r="H5" s="498"/>
-      <c r="I5" s="253"/>
-      <c r="J5" s="254"/>
-      <c r="K5" s="255"/>
+      <c r="A5" s="492"/>
+      <c r="B5" s="493"/>
+      <c r="C5" s="493"/>
+      <c r="D5" s="493"/>
+      <c r="E5" s="493"/>
+      <c r="F5" s="249"/>
+      <c r="G5" s="491"/>
+      <c r="H5" s="491"/>
+      <c r="I5" s="250"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="252"/>
     </row>
     <row r="6" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="499"/>
-      <c r="B6" s="500"/>
-      <c r="C6" s="500"/>
-      <c r="D6" s="500"/>
-      <c r="E6" s="500"/>
-      <c r="F6" s="252"/>
-      <c r="G6" s="506"/>
-      <c r="H6" s="507"/>
-      <c r="I6" s="253"/>
-      <c r="J6" s="254"/>
-      <c r="K6" s="255"/>
+      <c r="A6" s="492"/>
+      <c r="B6" s="493"/>
+      <c r="C6" s="493"/>
+      <c r="D6" s="493"/>
+      <c r="E6" s="493"/>
+      <c r="F6" s="249"/>
+      <c r="G6" s="499"/>
+      <c r="H6" s="500"/>
+      <c r="I6" s="250"/>
+      <c r="J6" s="251"/>
+      <c r="K6" s="252"/>
     </row>
     <row r="7" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="499"/>
-      <c r="B7" s="500"/>
-      <c r="C7" s="500"/>
-      <c r="D7" s="500"/>
-      <c r="E7" s="500"/>
-      <c r="F7" s="252"/>
-      <c r="G7" s="498"/>
-      <c r="H7" s="498"/>
-      <c r="I7" s="253"/>
-      <c r="J7" s="254"/>
-      <c r="K7" s="255"/>
+      <c r="A7" s="492"/>
+      <c r="B7" s="493"/>
+      <c r="C7" s="493"/>
+      <c r="D7" s="493"/>
+      <c r="E7" s="493"/>
+      <c r="F7" s="249"/>
+      <c r="G7" s="491"/>
+      <c r="H7" s="491"/>
+      <c r="I7" s="250"/>
+      <c r="J7" s="251"/>
+      <c r="K7" s="252"/>
     </row>
     <row r="8" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="499"/>
-      <c r="B8" s="500"/>
-      <c r="C8" s="500"/>
-      <c r="D8" s="500"/>
-      <c r="E8" s="500"/>
-      <c r="F8" s="252"/>
-      <c r="G8" s="498"/>
-      <c r="H8" s="498"/>
-      <c r="I8" s="253"/>
-      <c r="J8" s="254"/>
-      <c r="K8" s="255"/>
+      <c r="A8" s="492"/>
+      <c r="B8" s="493"/>
+      <c r="C8" s="493"/>
+      <c r="D8" s="493"/>
+      <c r="E8" s="493"/>
+      <c r="F8" s="249"/>
+      <c r="G8" s="491"/>
+      <c r="H8" s="491"/>
+      <c r="I8" s="250"/>
+      <c r="J8" s="251"/>
+      <c r="K8" s="252"/>
     </row>
     <row r="9" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="499"/>
-      <c r="B9" s="500"/>
-      <c r="C9" s="500"/>
-      <c r="D9" s="500"/>
-      <c r="E9" s="500"/>
-      <c r="F9" s="252"/>
-      <c r="G9" s="498"/>
-      <c r="H9" s="498"/>
-      <c r="I9" s="253"/>
-      <c r="J9" s="254"/>
-      <c r="K9" s="255"/>
+      <c r="A9" s="492"/>
+      <c r="B9" s="493"/>
+      <c r="C9" s="493"/>
+      <c r="D9" s="493"/>
+      <c r="E9" s="493"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="491"/>
+      <c r="H9" s="491"/>
+      <c r="I9" s="250"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="252"/>
     </row>
     <row r="10" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="499"/>
-      <c r="B10" s="500"/>
-      <c r="C10" s="500"/>
-      <c r="D10" s="500"/>
-      <c r="E10" s="500"/>
-      <c r="F10" s="252"/>
-      <c r="G10" s="498"/>
-      <c r="H10" s="498"/>
-      <c r="I10" s="253"/>
-      <c r="J10" s="254"/>
-      <c r="K10" s="255"/>
+      <c r="A10" s="492"/>
+      <c r="B10" s="493"/>
+      <c r="C10" s="493"/>
+      <c r="D10" s="493"/>
+      <c r="E10" s="493"/>
+      <c r="F10" s="249"/>
+      <c r="G10" s="491"/>
+      <c r="H10" s="491"/>
+      <c r="I10" s="250"/>
+      <c r="J10" s="251"/>
+      <c r="K10" s="252"/>
     </row>
     <row r="11" spans="1:11" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="514"/>
-      <c r="B11" s="515"/>
-      <c r="C11" s="515"/>
-      <c r="D11" s="515"/>
-      <c r="E11" s="515"/>
-      <c r="F11" s="256"/>
-      <c r="G11" s="522"/>
-      <c r="H11" s="522"/>
-      <c r="I11" s="257"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="259"/>
+      <c r="A11" s="507"/>
+      <c r="B11" s="508"/>
+      <c r="C11" s="508"/>
+      <c r="D11" s="508"/>
+      <c r="E11" s="508"/>
+      <c r="F11" s="253"/>
+      <c r="G11" s="515"/>
+      <c r="H11" s="515"/>
+      <c r="I11" s="254"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="256"/>
     </row>
     <row r="12" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="516" t="s">
+      <c r="A12" s="509" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="517"/>
-      <c r="C12" s="517"/>
-      <c r="D12" s="517"/>
-      <c r="E12" s="517"/>
-      <c r="F12" s="517"/>
-      <c r="G12" s="517"/>
-      <c r="H12" s="517"/>
-      <c r="I12" s="517"/>
-      <c r="J12" s="517"/>
-      <c r="K12" s="518"/>
+      <c r="B12" s="510"/>
+      <c r="C12" s="510"/>
+      <c r="D12" s="510"/>
+      <c r="E12" s="510"/>
+      <c r="F12" s="510"/>
+      <c r="G12" s="510"/>
+      <c r="H12" s="510"/>
+      <c r="I12" s="510"/>
+      <c r="J12" s="510"/>
+      <c r="K12" s="511"/>
     </row>
     <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="519" t="s">
+      <c r="A13" s="512" t="s">
         <v>313</v>
       </c>
-      <c r="B13" s="520"/>
-      <c r="C13" s="520"/>
-      <c r="D13" s="520"/>
-      <c r="E13" s="520"/>
-      <c r="F13" s="520"/>
-      <c r="G13" s="520"/>
-      <c r="H13" s="520"/>
-      <c r="I13" s="520"/>
-      <c r="J13" s="520"/>
-      <c r="K13" s="521"/>
+      <c r="B13" s="513"/>
+      <c r="C13" s="513"/>
+      <c r="D13" s="513"/>
+      <c r="E13" s="513"/>
+      <c r="F13" s="513"/>
+      <c r="G13" s="513"/>
+      <c r="H13" s="513"/>
+      <c r="I13" s="513"/>
+      <c r="J13" s="513"/>
+      <c r="K13" s="514"/>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="182" t="s">
+      <c r="A14" s="179" t="s">
         <v>398</v>
       </c>
       <c r="B14" s="81"/>
@@ -16226,485 +16228,485 @@
       <c r="H14" s="81"/>
       <c r="I14" s="81"/>
       <c r="J14" s="81"/>
-      <c r="K14" s="181"/>
+      <c r="K14" s="178"/>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="B15" s="504" t="s">
+      <c r="B15" s="497" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="505"/>
-      <c r="D15" s="503" t="s">
+      <c r="C15" s="498"/>
+      <c r="D15" s="496" t="s">
         <v>316</v>
       </c>
-      <c r="E15" s="504"/>
-      <c r="F15" s="505"/>
-      <c r="G15" s="503" t="s">
+      <c r="E15" s="497"/>
+      <c r="F15" s="498"/>
+      <c r="G15" s="496" t="s">
         <v>317</v>
       </c>
-      <c r="H15" s="504"/>
-      <c r="I15" s="505"/>
-      <c r="J15" s="525" t="s">
+      <c r="H15" s="497"/>
+      <c r="I15" s="498"/>
+      <c r="J15" s="518" t="s">
         <v>318</v>
       </c>
-      <c r="K15" s="496" t="s">
+      <c r="K15" s="489" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="485"/>
-      <c r="C16" s="486"/>
-      <c r="D16" s="503"/>
-      <c r="E16" s="504"/>
-      <c r="F16" s="505"/>
-      <c r="G16" s="503"/>
-      <c r="H16" s="504"/>
-      <c r="I16" s="505"/>
-      <c r="J16" s="525"/>
-      <c r="K16" s="496"/>
+      <c r="B16" s="478"/>
+      <c r="C16" s="479"/>
+      <c r="D16" s="496"/>
+      <c r="E16" s="497"/>
+      <c r="F16" s="498"/>
+      <c r="G16" s="496"/>
+      <c r="H16" s="497"/>
+      <c r="I16" s="498"/>
+      <c r="J16" s="518"/>
+      <c r="K16" s="489"/>
     </row>
     <row r="17" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="501" t="s">
+      <c r="A17" s="494" t="s">
         <v>129</v>
       </c>
-      <c r="B17" s="502"/>
+      <c r="B17" s="495"/>
       <c r="C17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="488"/>
-      <c r="E17" s="485"/>
-      <c r="F17" s="486"/>
-      <c r="G17" s="488"/>
-      <c r="H17" s="485"/>
-      <c r="I17" s="486"/>
-      <c r="J17" s="526"/>
-      <c r="K17" s="497"/>
+      <c r="D17" s="481"/>
+      <c r="E17" s="478"/>
+      <c r="F17" s="479"/>
+      <c r="G17" s="481"/>
+      <c r="H17" s="478"/>
+      <c r="I17" s="479"/>
+      <c r="J17" s="519"/>
+      <c r="K17" s="490"/>
     </row>
     <row r="18" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="512"/>
-      <c r="B18" s="513"/>
-      <c r="C18" s="260"/>
-      <c r="D18" s="511"/>
-      <c r="E18" s="511"/>
-      <c r="F18" s="511"/>
-      <c r="G18" s="511"/>
-      <c r="H18" s="511"/>
-      <c r="I18" s="511"/>
-      <c r="J18" s="261"/>
-      <c r="K18" s="262"/>
+      <c r="A18" s="505"/>
+      <c r="B18" s="506"/>
+      <c r="C18" s="257"/>
+      <c r="D18" s="504"/>
+      <c r="E18" s="504"/>
+      <c r="F18" s="504"/>
+      <c r="G18" s="504"/>
+      <c r="H18" s="504"/>
+      <c r="I18" s="504"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="259"/>
     </row>
     <row r="19" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="512"/>
-      <c r="B19" s="513"/>
-      <c r="C19" s="260"/>
-      <c r="D19" s="511"/>
-      <c r="E19" s="511"/>
-      <c r="F19" s="511"/>
-      <c r="G19" s="511"/>
-      <c r="H19" s="511"/>
-      <c r="I19" s="511"/>
-      <c r="J19" s="261"/>
-      <c r="K19" s="262"/>
+      <c r="A19" s="505"/>
+      <c r="B19" s="506"/>
+      <c r="C19" s="257"/>
+      <c r="D19" s="504"/>
+      <c r="E19" s="504"/>
+      <c r="F19" s="504"/>
+      <c r="G19" s="504"/>
+      <c r="H19" s="504"/>
+      <c r="I19" s="504"/>
+      <c r="J19" s="258"/>
+      <c r="K19" s="259"/>
     </row>
     <row r="20" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="512"/>
-      <c r="B20" s="513"/>
-      <c r="C20" s="260"/>
-      <c r="D20" s="511"/>
-      <c r="E20" s="511"/>
-      <c r="F20" s="511"/>
-      <c r="G20" s="511"/>
-      <c r="H20" s="511"/>
-      <c r="I20" s="511"/>
-      <c r="J20" s="261"/>
-      <c r="K20" s="262"/>
+      <c r="A20" s="505"/>
+      <c r="B20" s="506"/>
+      <c r="C20" s="257"/>
+      <c r="D20" s="504"/>
+      <c r="E20" s="504"/>
+      <c r="F20" s="504"/>
+      <c r="G20" s="504"/>
+      <c r="H20" s="504"/>
+      <c r="I20" s="504"/>
+      <c r="J20" s="258"/>
+      <c r="K20" s="259"/>
     </row>
     <row r="21" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="512"/>
-      <c r="B21" s="513"/>
-      <c r="C21" s="260"/>
-      <c r="D21" s="511"/>
-      <c r="E21" s="511"/>
-      <c r="F21" s="511"/>
-      <c r="G21" s="511"/>
-      <c r="H21" s="511"/>
-      <c r="I21" s="511"/>
-      <c r="J21" s="261"/>
-      <c r="K21" s="262"/>
+      <c r="A21" s="505"/>
+      <c r="B21" s="506"/>
+      <c r="C21" s="257"/>
+      <c r="D21" s="504"/>
+      <c r="E21" s="504"/>
+      <c r="F21" s="504"/>
+      <c r="G21" s="504"/>
+      <c r="H21" s="504"/>
+      <c r="I21" s="504"/>
+      <c r="J21" s="258"/>
+      <c r="K21" s="259"/>
     </row>
     <row r="22" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="512"/>
-      <c r="B22" s="513"/>
-      <c r="C22" s="260"/>
-      <c r="D22" s="511"/>
-      <c r="E22" s="511"/>
-      <c r="F22" s="511"/>
-      <c r="G22" s="511"/>
-      <c r="H22" s="511"/>
-      <c r="I22" s="511"/>
-      <c r="J22" s="261"/>
-      <c r="K22" s="262"/>
+      <c r="A22" s="505"/>
+      <c r="B22" s="506"/>
+      <c r="C22" s="257"/>
+      <c r="D22" s="504"/>
+      <c r="E22" s="504"/>
+      <c r="F22" s="504"/>
+      <c r="G22" s="504"/>
+      <c r="H22" s="504"/>
+      <c r="I22" s="504"/>
+      <c r="J22" s="258"/>
+      <c r="K22" s="259"/>
     </row>
     <row r="23" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="512"/>
-      <c r="B23" s="513"/>
-      <c r="C23" s="260"/>
-      <c r="D23" s="511"/>
-      <c r="E23" s="511"/>
-      <c r="F23" s="511"/>
-      <c r="G23" s="511"/>
-      <c r="H23" s="511"/>
-      <c r="I23" s="511"/>
-      <c r="J23" s="261"/>
-      <c r="K23" s="262"/>
+      <c r="A23" s="505"/>
+      <c r="B23" s="506"/>
+      <c r="C23" s="257"/>
+      <c r="D23" s="504"/>
+      <c r="E23" s="504"/>
+      <c r="F23" s="504"/>
+      <c r="G23" s="504"/>
+      <c r="H23" s="504"/>
+      <c r="I23" s="504"/>
+      <c r="J23" s="258"/>
+      <c r="K23" s="259"/>
     </row>
     <row r="24" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="512"/>
-      <c r="B24" s="513"/>
-      <c r="C24" s="260"/>
-      <c r="D24" s="511"/>
-      <c r="E24" s="511"/>
-      <c r="F24" s="511"/>
-      <c r="G24" s="511"/>
-      <c r="H24" s="511"/>
-      <c r="I24" s="511"/>
-      <c r="J24" s="261"/>
-      <c r="K24" s="262"/>
+      <c r="A24" s="505"/>
+      <c r="B24" s="506"/>
+      <c r="C24" s="257"/>
+      <c r="D24" s="504"/>
+      <c r="E24" s="504"/>
+      <c r="F24" s="504"/>
+      <c r="G24" s="504"/>
+      <c r="H24" s="504"/>
+      <c r="I24" s="504"/>
+      <c r="J24" s="258"/>
+      <c r="K24" s="259"/>
     </row>
     <row r="25" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="512"/>
-      <c r="B25" s="513"/>
-      <c r="C25" s="260"/>
-      <c r="D25" s="511"/>
-      <c r="E25" s="511"/>
-      <c r="F25" s="511"/>
-      <c r="G25" s="511"/>
-      <c r="H25" s="511"/>
-      <c r="I25" s="511"/>
-      <c r="J25" s="261"/>
-      <c r="K25" s="262"/>
+      <c r="A25" s="505"/>
+      <c r="B25" s="506"/>
+      <c r="C25" s="257"/>
+      <c r="D25" s="504"/>
+      <c r="E25" s="504"/>
+      <c r="F25" s="504"/>
+      <c r="G25" s="504"/>
+      <c r="H25" s="504"/>
+      <c r="I25" s="504"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="259"/>
     </row>
     <row r="26" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="512"/>
-      <c r="B26" s="513"/>
-      <c r="C26" s="260"/>
-      <c r="D26" s="511"/>
-      <c r="E26" s="511"/>
-      <c r="F26" s="511"/>
-      <c r="G26" s="511"/>
-      <c r="H26" s="511"/>
-      <c r="I26" s="511"/>
-      <c r="J26" s="261"/>
-      <c r="K26" s="262"/>
+      <c r="A26" s="505"/>
+      <c r="B26" s="506"/>
+      <c r="C26" s="257"/>
+      <c r="D26" s="504"/>
+      <c r="E26" s="504"/>
+      <c r="F26" s="504"/>
+      <c r="G26" s="504"/>
+      <c r="H26" s="504"/>
+      <c r="I26" s="504"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="259"/>
     </row>
     <row r="27" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="512"/>
-      <c r="B27" s="513"/>
-      <c r="C27" s="260"/>
-      <c r="D27" s="511"/>
-      <c r="E27" s="511"/>
-      <c r="F27" s="511"/>
-      <c r="G27" s="511"/>
-      <c r="H27" s="511"/>
-      <c r="I27" s="511"/>
-      <c r="J27" s="261"/>
-      <c r="K27" s="262"/>
+      <c r="A27" s="505"/>
+      <c r="B27" s="506"/>
+      <c r="C27" s="257"/>
+      <c r="D27" s="504"/>
+      <c r="E27" s="504"/>
+      <c r="F27" s="504"/>
+      <c r="G27" s="504"/>
+      <c r="H27" s="504"/>
+      <c r="I27" s="504"/>
+      <c r="J27" s="258"/>
+      <c r="K27" s="259"/>
     </row>
     <row r="28" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="512"/>
-      <c r="B28" s="513"/>
-      <c r="C28" s="260"/>
-      <c r="D28" s="511"/>
-      <c r="E28" s="511"/>
-      <c r="F28" s="511"/>
-      <c r="G28" s="511"/>
-      <c r="H28" s="511"/>
-      <c r="I28" s="511"/>
-      <c r="J28" s="261"/>
-      <c r="K28" s="262"/>
+      <c r="A28" s="505"/>
+      <c r="B28" s="506"/>
+      <c r="C28" s="257"/>
+      <c r="D28" s="504"/>
+      <c r="E28" s="504"/>
+      <c r="F28" s="504"/>
+      <c r="G28" s="504"/>
+      <c r="H28" s="504"/>
+      <c r="I28" s="504"/>
+      <c r="J28" s="258"/>
+      <c r="K28" s="259"/>
     </row>
     <row r="29" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="512"/>
-      <c r="B29" s="513"/>
-      <c r="C29" s="260"/>
-      <c r="D29" s="511"/>
-      <c r="E29" s="511"/>
-      <c r="F29" s="511"/>
-      <c r="G29" s="511"/>
-      <c r="H29" s="511"/>
-      <c r="I29" s="511"/>
-      <c r="J29" s="261"/>
-      <c r="K29" s="262"/>
+      <c r="A29" s="505"/>
+      <c r="B29" s="506"/>
+      <c r="C29" s="257"/>
+      <c r="D29" s="504"/>
+      <c r="E29" s="504"/>
+      <c r="F29" s="504"/>
+      <c r="G29" s="504"/>
+      <c r="H29" s="504"/>
+      <c r="I29" s="504"/>
+      <c r="J29" s="258"/>
+      <c r="K29" s="259"/>
     </row>
     <row r="30" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="512"/>
-      <c r="B30" s="513"/>
-      <c r="C30" s="260"/>
-      <c r="D30" s="511"/>
-      <c r="E30" s="511"/>
-      <c r="F30" s="511"/>
-      <c r="G30" s="511"/>
-      <c r="H30" s="511"/>
-      <c r="I30" s="511"/>
-      <c r="J30" s="261"/>
-      <c r="K30" s="262"/>
+      <c r="A30" s="505"/>
+      <c r="B30" s="506"/>
+      <c r="C30" s="257"/>
+      <c r="D30" s="504"/>
+      <c r="E30" s="504"/>
+      <c r="F30" s="504"/>
+      <c r="G30" s="504"/>
+      <c r="H30" s="504"/>
+      <c r="I30" s="504"/>
+      <c r="J30" s="258"/>
+      <c r="K30" s="259"/>
     </row>
     <row r="31" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="512"/>
-      <c r="B31" s="513"/>
-      <c r="C31" s="260"/>
-      <c r="D31" s="511"/>
-      <c r="E31" s="511"/>
-      <c r="F31" s="511"/>
-      <c r="G31" s="511"/>
-      <c r="H31" s="511"/>
-      <c r="I31" s="511"/>
-      <c r="J31" s="261"/>
-      <c r="K31" s="262"/>
+      <c r="A31" s="505"/>
+      <c r="B31" s="506"/>
+      <c r="C31" s="257"/>
+      <c r="D31" s="504"/>
+      <c r="E31" s="504"/>
+      <c r="F31" s="504"/>
+      <c r="G31" s="504"/>
+      <c r="H31" s="504"/>
+      <c r="I31" s="504"/>
+      <c r="J31" s="258"/>
+      <c r="K31" s="259"/>
     </row>
     <row r="32" spans="1:11" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="512"/>
-      <c r="B32" s="513"/>
-      <c r="C32" s="260"/>
-      <c r="D32" s="511"/>
-      <c r="E32" s="511"/>
-      <c r="F32" s="511"/>
-      <c r="G32" s="511"/>
-      <c r="H32" s="511"/>
-      <c r="I32" s="511"/>
-      <c r="J32" s="261"/>
-      <c r="K32" s="262"/>
+      <c r="A32" s="505"/>
+      <c r="B32" s="506"/>
+      <c r="C32" s="257"/>
+      <c r="D32" s="504"/>
+      <c r="E32" s="504"/>
+      <c r="F32" s="504"/>
+      <c r="G32" s="504"/>
+      <c r="H32" s="504"/>
+      <c r="I32" s="504"/>
+      <c r="J32" s="258"/>
+      <c r="K32" s="259"/>
     </row>
     <row r="33" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="512"/>
-      <c r="B33" s="513"/>
-      <c r="C33" s="260"/>
-      <c r="D33" s="511"/>
-      <c r="E33" s="511"/>
-      <c r="F33" s="511"/>
-      <c r="G33" s="511"/>
-      <c r="H33" s="511"/>
-      <c r="I33" s="511"/>
-      <c r="J33" s="261"/>
-      <c r="K33" s="262"/>
+      <c r="A33" s="505"/>
+      <c r="B33" s="506"/>
+      <c r="C33" s="257"/>
+      <c r="D33" s="504"/>
+      <c r="E33" s="504"/>
+      <c r="F33" s="504"/>
+      <c r="G33" s="504"/>
+      <c r="H33" s="504"/>
+      <c r="I33" s="504"/>
+      <c r="J33" s="258"/>
+      <c r="K33" s="259"/>
     </row>
     <row r="34" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="512"/>
-      <c r="B34" s="513"/>
-      <c r="C34" s="260"/>
-      <c r="D34" s="511"/>
-      <c r="E34" s="511"/>
-      <c r="F34" s="511"/>
-      <c r="G34" s="511"/>
-      <c r="H34" s="511"/>
-      <c r="I34" s="511"/>
-      <c r="J34" s="261"/>
-      <c r="K34" s="262"/>
+      <c r="A34" s="505"/>
+      <c r="B34" s="506"/>
+      <c r="C34" s="257"/>
+      <c r="D34" s="504"/>
+      <c r="E34" s="504"/>
+      <c r="F34" s="504"/>
+      <c r="G34" s="504"/>
+      <c r="H34" s="504"/>
+      <c r="I34" s="504"/>
+      <c r="J34" s="258"/>
+      <c r="K34" s="259"/>
     </row>
     <row r="35" spans="1:12" s="8" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="512"/>
-      <c r="B35" s="513"/>
-      <c r="C35" s="260"/>
-      <c r="D35" s="511"/>
-      <c r="E35" s="511"/>
-      <c r="F35" s="511"/>
-      <c r="G35" s="511"/>
-      <c r="H35" s="511"/>
-      <c r="I35" s="511"/>
-      <c r="J35" s="261"/>
-      <c r="K35" s="262"/>
+      <c r="A35" s="505"/>
+      <c r="B35" s="506"/>
+      <c r="C35" s="257"/>
+      <c r="D35" s="504"/>
+      <c r="E35" s="504"/>
+      <c r="F35" s="504"/>
+      <c r="G35" s="504"/>
+      <c r="H35" s="504"/>
+      <c r="I35" s="504"/>
+      <c r="J35" s="258"/>
+      <c r="K35" s="259"/>
     </row>
     <row r="36" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="512"/>
-      <c r="B36" s="513"/>
-      <c r="C36" s="260"/>
-      <c r="D36" s="511"/>
-      <c r="E36" s="511"/>
-      <c r="F36" s="511"/>
-      <c r="G36" s="511"/>
-      <c r="H36" s="511"/>
-      <c r="I36" s="511"/>
-      <c r="J36" s="261"/>
-      <c r="K36" s="262"/>
+      <c r="A36" s="505"/>
+      <c r="B36" s="506"/>
+      <c r="C36" s="257"/>
+      <c r="D36" s="504"/>
+      <c r="E36" s="504"/>
+      <c r="F36" s="504"/>
+      <c r="G36" s="504"/>
+      <c r="H36" s="504"/>
+      <c r="I36" s="504"/>
+      <c r="J36" s="258"/>
+      <c r="K36" s="259"/>
     </row>
     <row r="37" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="512"/>
-      <c r="B37" s="513"/>
-      <c r="C37" s="260"/>
-      <c r="D37" s="511"/>
-      <c r="E37" s="511"/>
-      <c r="F37" s="511"/>
-      <c r="G37" s="511"/>
-      <c r="H37" s="511"/>
-      <c r="I37" s="511"/>
-      <c r="J37" s="261"/>
-      <c r="K37" s="262"/>
+      <c r="A37" s="505"/>
+      <c r="B37" s="506"/>
+      <c r="C37" s="257"/>
+      <c r="D37" s="504"/>
+      <c r="E37" s="504"/>
+      <c r="F37" s="504"/>
+      <c r="G37" s="504"/>
+      <c r="H37" s="504"/>
+      <c r="I37" s="504"/>
+      <c r="J37" s="258"/>
+      <c r="K37" s="259"/>
     </row>
     <row r="38" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="512"/>
-      <c r="B38" s="513"/>
-      <c r="C38" s="260"/>
-      <c r="D38" s="511"/>
-      <c r="E38" s="511"/>
-      <c r="F38" s="511"/>
-      <c r="G38" s="511"/>
-      <c r="H38" s="511"/>
-      <c r="I38" s="511"/>
-      <c r="J38" s="261"/>
-      <c r="K38" s="262"/>
+      <c r="A38" s="505"/>
+      <c r="B38" s="506"/>
+      <c r="C38" s="257"/>
+      <c r="D38" s="504"/>
+      <c r="E38" s="504"/>
+      <c r="F38" s="504"/>
+      <c r="G38" s="504"/>
+      <c r="H38" s="504"/>
+      <c r="I38" s="504"/>
+      <c r="J38" s="258"/>
+      <c r="K38" s="259"/>
     </row>
     <row r="39" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="512"/>
-      <c r="B39" s="513"/>
-      <c r="C39" s="260"/>
-      <c r="D39" s="511"/>
-      <c r="E39" s="511"/>
-      <c r="F39" s="511"/>
-      <c r="G39" s="511"/>
-      <c r="H39" s="511"/>
-      <c r="I39" s="511"/>
-      <c r="J39" s="261"/>
-      <c r="K39" s="262"/>
+      <c r="A39" s="505"/>
+      <c r="B39" s="506"/>
+      <c r="C39" s="257"/>
+      <c r="D39" s="504"/>
+      <c r="E39" s="504"/>
+      <c r="F39" s="504"/>
+      <c r="G39" s="504"/>
+      <c r="H39" s="504"/>
+      <c r="I39" s="504"/>
+      <c r="J39" s="258"/>
+      <c r="K39" s="259"/>
     </row>
     <row r="40" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="512"/>
-      <c r="B40" s="513"/>
-      <c r="C40" s="260"/>
-      <c r="D40" s="511"/>
-      <c r="E40" s="511"/>
-      <c r="F40" s="511"/>
-      <c r="G40" s="511"/>
-      <c r="H40" s="511"/>
-      <c r="I40" s="511"/>
-      <c r="J40" s="261"/>
-      <c r="K40" s="262"/>
+      <c r="A40" s="505"/>
+      <c r="B40" s="506"/>
+      <c r="C40" s="257"/>
+      <c r="D40" s="504"/>
+      <c r="E40" s="504"/>
+      <c r="F40" s="504"/>
+      <c r="G40" s="504"/>
+      <c r="H40" s="504"/>
+      <c r="I40" s="504"/>
+      <c r="J40" s="258"/>
+      <c r="K40" s="259"/>
     </row>
     <row r="41" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="512"/>
-      <c r="B41" s="513"/>
-      <c r="C41" s="260"/>
-      <c r="D41" s="511"/>
-      <c r="E41" s="511"/>
-      <c r="F41" s="511"/>
-      <c r="G41" s="511"/>
-      <c r="H41" s="511"/>
-      <c r="I41" s="511"/>
-      <c r="J41" s="261"/>
-      <c r="K41" s="262"/>
+      <c r="A41" s="505"/>
+      <c r="B41" s="506"/>
+      <c r="C41" s="257"/>
+      <c r="D41" s="504"/>
+      <c r="E41" s="504"/>
+      <c r="F41" s="504"/>
+      <c r="G41" s="504"/>
+      <c r="H41" s="504"/>
+      <c r="I41" s="504"/>
+      <c r="J41" s="258"/>
+      <c r="K41" s="259"/>
     </row>
     <row r="42" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="512"/>
-      <c r="B42" s="513"/>
-      <c r="C42" s="260"/>
-      <c r="D42" s="511"/>
-      <c r="E42" s="511"/>
-      <c r="F42" s="511"/>
-      <c r="G42" s="511"/>
-      <c r="H42" s="511"/>
-      <c r="I42" s="511"/>
-      <c r="J42" s="261"/>
-      <c r="K42" s="262"/>
+      <c r="A42" s="505"/>
+      <c r="B42" s="506"/>
+      <c r="C42" s="257"/>
+      <c r="D42" s="504"/>
+      <c r="E42" s="504"/>
+      <c r="F42" s="504"/>
+      <c r="G42" s="504"/>
+      <c r="H42" s="504"/>
+      <c r="I42" s="504"/>
+      <c r="J42" s="258"/>
+      <c r="K42" s="259"/>
     </row>
     <row r="43" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="512"/>
-      <c r="B43" s="513"/>
-      <c r="C43" s="260"/>
-      <c r="D43" s="511"/>
-      <c r="E43" s="511"/>
-      <c r="F43" s="511"/>
-      <c r="G43" s="511"/>
-      <c r="H43" s="511"/>
-      <c r="I43" s="511"/>
-      <c r="J43" s="261"/>
-      <c r="K43" s="262"/>
+      <c r="A43" s="505"/>
+      <c r="B43" s="506"/>
+      <c r="C43" s="257"/>
+      <c r="D43" s="504"/>
+      <c r="E43" s="504"/>
+      <c r="F43" s="504"/>
+      <c r="G43" s="504"/>
+      <c r="H43" s="504"/>
+      <c r="I43" s="504"/>
+      <c r="J43" s="258"/>
+      <c r="K43" s="259"/>
     </row>
     <row r="44" spans="1:12" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="512"/>
-      <c r="B44" s="513"/>
-      <c r="C44" s="260"/>
-      <c r="D44" s="511"/>
-      <c r="E44" s="511"/>
-      <c r="F44" s="511"/>
-      <c r="G44" s="511"/>
-      <c r="H44" s="511"/>
-      <c r="I44" s="511"/>
-      <c r="J44" s="261"/>
-      <c r="K44" s="262"/>
+      <c r="A44" s="505"/>
+      <c r="B44" s="506"/>
+      <c r="C44" s="257"/>
+      <c r="D44" s="504"/>
+      <c r="E44" s="504"/>
+      <c r="F44" s="504"/>
+      <c r="G44" s="504"/>
+      <c r="H44" s="504"/>
+      <c r="I44" s="504"/>
+      <c r="J44" s="258"/>
+      <c r="K44" s="259"/>
     </row>
     <row r="45" spans="1:12" s="8" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="523"/>
-      <c r="B45" s="524"/>
-      <c r="C45" s="263"/>
-      <c r="D45" s="527"/>
-      <c r="E45" s="527"/>
-      <c r="F45" s="527"/>
-      <c r="G45" s="527"/>
-      <c r="H45" s="527"/>
-      <c r="I45" s="527"/>
-      <c r="J45" s="264"/>
-      <c r="K45" s="265"/>
+      <c r="A45" s="516"/>
+      <c r="B45" s="517"/>
+      <c r="C45" s="260"/>
+      <c r="D45" s="520"/>
+      <c r="E45" s="520"/>
+      <c r="F45" s="520"/>
+      <c r="G45" s="520"/>
+      <c r="H45" s="520"/>
+      <c r="I45" s="520"/>
+      <c r="J45" s="261"/>
+      <c r="K45" s="262"/>
     </row>
     <row r="46" spans="1:12" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="528" t="s">
+      <c r="A46" s="521" t="s">
         <v>114</v>
       </c>
-      <c r="B46" s="529"/>
-      <c r="C46" s="529"/>
-      <c r="D46" s="529"/>
-      <c r="E46" s="529"/>
-      <c r="F46" s="529"/>
-      <c r="G46" s="529"/>
-      <c r="H46" s="529"/>
-      <c r="I46" s="529"/>
-      <c r="J46" s="530"/>
-      <c r="K46" s="531"/>
+      <c r="B46" s="522"/>
+      <c r="C46" s="522"/>
+      <c r="D46" s="522"/>
+      <c r="E46" s="522"/>
+      <c r="F46" s="522"/>
+      <c r="G46" s="522"/>
+      <c r="H46" s="522"/>
+      <c r="I46" s="522"/>
+      <c r="J46" s="523"/>
+      <c r="K46" s="524"/>
     </row>
     <row r="47" spans="1:12" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="277" t="s">
+      <c r="A47" s="278" t="s">
         <v>143</v>
       </c>
-      <c r="B47" s="278"/>
-      <c r="C47" s="279"/>
-      <c r="D47" s="508" t="s">
+      <c r="B47" s="279"/>
+      <c r="C47" s="280"/>
+      <c r="D47" s="501" t="s">
         <v>144</v>
       </c>
-      <c r="E47" s="509"/>
-      <c r="F47" s="509"/>
-      <c r="G47" s="509"/>
-      <c r="H47" s="510"/>
-      <c r="I47" s="213" t="s">
+      <c r="E47" s="502"/>
+      <c r="F47" s="502"/>
+      <c r="G47" s="502"/>
+      <c r="H47" s="503"/>
+      <c r="I47" s="210" t="s">
         <v>145</v>
       </c>
-      <c r="J47" s="751">
+      <c r="J47" s="525">
         <f ca="1">NOW()</f>
-        <v>45982.693544444446</v>
-      </c>
-      <c r="K47" s="752"/>
-      <c r="L47" s="214"/>
+        <v>45982.839370949077</v>
+      </c>
+      <c r="K47" s="526"/>
+      <c r="L47" s="211"/>
     </row>
     <row r="48" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="276" t="s">
+      <c r="A48" s="277" t="s">
         <v>403</v>
       </c>
-      <c r="B48" s="276"/>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="276"/>
-      <c r="L48" s="217"/>
+      <c r="B48" s="277"/>
+      <c r="C48" s="277"/>
+      <c r="D48" s="277"/>
+      <c r="E48" s="277"/>
+      <c r="F48" s="277"/>
+      <c r="G48" s="277"/>
+      <c r="H48" s="277"/>
+      <c r="I48" s="277"/>
+      <c r="J48" s="277"/>
+      <c r="K48" s="277"/>
+      <c r="L48" s="214"/>
     </row>
     <row r="60" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L60" s="747">
+      <c r="L60" s="273">
         <f ca="1">NOW()</f>
-        <v>45982.693544444446</v>
+        <v>45982.839370949077</v>
       </c>
     </row>
   </sheetData>
@@ -16718,7 +16720,6 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="118">
-    <mergeCell ref="J47:K47"/>
     <mergeCell ref="G44:I44"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="D37:F37"/>
@@ -16742,7 +16743,6 @@
     <mergeCell ref="G22:I22"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="D42:F42"/>
-    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="A47:C47"/>
@@ -16766,6 +16766,7 @@
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A44:B44"/>
+    <mergeCell ref="J47:K47"/>
     <mergeCell ref="D44:F44"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="G11:H11"/>
@@ -16789,6 +16790,7 @@
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="G27:I27"/>
     <mergeCell ref="G25:I25"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A48:K48"/>
     <mergeCell ref="D47:H47"/>
     <mergeCell ref="G43:I43"/>
@@ -16867,564 +16869,564 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="561"/>
-      <c r="B1" s="562"/>
-      <c r="C1" s="562"/>
-      <c r="D1" s="562"/>
-      <c r="E1" s="562"/>
-      <c r="F1" s="562"/>
-      <c r="G1" s="562"/>
-      <c r="H1" s="562"/>
-      <c r="I1" s="562"/>
-      <c r="J1" s="562"/>
-      <c r="K1" s="563"/>
+      <c r="A1" s="557"/>
+      <c r="B1" s="558"/>
+      <c r="C1" s="558"/>
+      <c r="D1" s="558"/>
+      <c r="E1" s="558"/>
+      <c r="F1" s="558"/>
+      <c r="G1" s="558"/>
+      <c r="H1" s="558"/>
+      <c r="I1" s="558"/>
+      <c r="J1" s="558"/>
+      <c r="K1" s="559"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="583" t="s">
+      <c r="A2" s="579" t="s">
         <v>320</v>
       </c>
-      <c r="B2" s="584"/>
-      <c r="C2" s="584"/>
-      <c r="D2" s="584"/>
-      <c r="E2" s="584"/>
-      <c r="F2" s="584"/>
-      <c r="G2" s="584"/>
-      <c r="H2" s="584"/>
-      <c r="I2" s="584"/>
-      <c r="J2" s="584"/>
-      <c r="K2" s="585"/>
+      <c r="B2" s="580"/>
+      <c r="C2" s="580"/>
+      <c r="D2" s="580"/>
+      <c r="E2" s="580"/>
+      <c r="F2" s="580"/>
+      <c r="G2" s="580"/>
+      <c r="H2" s="580"/>
+      <c r="I2" s="580"/>
+      <c r="J2" s="580"/>
+      <c r="K2" s="581"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="569" t="s">
+      <c r="A3" s="565" t="s">
         <v>321</v>
       </c>
-      <c r="B3" s="571" t="s">
+      <c r="B3" s="567" t="s">
         <v>322</v>
       </c>
-      <c r="C3" s="571"/>
-      <c r="D3" s="572"/>
-      <c r="E3" s="483" t="s">
+      <c r="C3" s="567"/>
+      <c r="D3" s="568"/>
+      <c r="E3" s="476" t="s">
         <v>323</v>
       </c>
-      <c r="F3" s="484"/>
-      <c r="G3" s="546" t="s">
+      <c r="F3" s="477"/>
+      <c r="G3" s="542" t="s">
         <v>324</v>
       </c>
-      <c r="H3" s="487" t="s">
+      <c r="H3" s="480" t="s">
         <v>325</v>
       </c>
-      <c r="I3" s="578"/>
-      <c r="J3" s="578"/>
-      <c r="K3" s="579"/>
+      <c r="I3" s="574"/>
+      <c r="J3" s="574"/>
+      <c r="K3" s="575"/>
     </row>
     <row r="4" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="570"/>
-      <c r="B4" s="573"/>
-      <c r="C4" s="573"/>
-      <c r="D4" s="574"/>
-      <c r="E4" s="485"/>
-      <c r="F4" s="486"/>
-      <c r="G4" s="547"/>
-      <c r="H4" s="580"/>
-      <c r="I4" s="564"/>
-      <c r="J4" s="564"/>
-      <c r="K4" s="581"/>
+      <c r="A4" s="566"/>
+      <c r="B4" s="569"/>
+      <c r="C4" s="569"/>
+      <c r="D4" s="570"/>
+      <c r="E4" s="478"/>
+      <c r="F4" s="479"/>
+      <c r="G4" s="543"/>
+      <c r="H4" s="576"/>
+      <c r="I4" s="560"/>
+      <c r="J4" s="560"/>
+      <c r="K4" s="577"/>
     </row>
     <row r="5" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
-      <c r="B5" s="586"/>
-      <c r="C5" s="586"/>
-      <c r="D5" s="587"/>
+      <c r="B5" s="582"/>
+      <c r="C5" s="582"/>
+      <c r="D5" s="583"/>
       <c r="E5" s="12" t="s">
         <v>129</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G5" s="548"/>
-      <c r="H5" s="582"/>
-      <c r="I5" s="363"/>
-      <c r="J5" s="363"/>
-      <c r="K5" s="364"/>
+      <c r="G5" s="544"/>
+      <c r="H5" s="578"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="367"/>
+      <c r="K5" s="368"/>
     </row>
     <row r="6" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="543"/>
-      <c r="B6" s="544"/>
-      <c r="C6" s="544"/>
-      <c r="D6" s="545"/>
+      <c r="A6" s="539"/>
+      <c r="B6" s="540"/>
+      <c r="C6" s="540"/>
+      <c r="D6" s="541"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="19"/>
-      <c r="H6" s="549"/>
-      <c r="I6" s="550"/>
-      <c r="J6" s="550"/>
-      <c r="K6" s="551"/>
+      <c r="H6" s="545"/>
+      <c r="I6" s="546"/>
+      <c r="J6" s="546"/>
+      <c r="K6" s="547"/>
     </row>
     <row r="7" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="543"/>
-      <c r="B7" s="544"/>
-      <c r="C7" s="544"/>
-      <c r="D7" s="545"/>
+      <c r="A7" s="539"/>
+      <c r="B7" s="540"/>
+      <c r="C7" s="540"/>
+      <c r="D7" s="541"/>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
       <c r="G7" s="19"/>
-      <c r="H7" s="549"/>
-      <c r="I7" s="550"/>
-      <c r="J7" s="550"/>
-      <c r="K7" s="551"/>
+      <c r="H7" s="545"/>
+      <c r="I7" s="546"/>
+      <c r="J7" s="546"/>
+      <c r="K7" s="547"/>
     </row>
     <row r="8" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="543"/>
-      <c r="B8" s="544"/>
-      <c r="C8" s="544"/>
-      <c r="D8" s="545"/>
+      <c r="A8" s="539"/>
+      <c r="B8" s="540"/>
+      <c r="C8" s="540"/>
+      <c r="D8" s="541"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
       <c r="G8" s="19"/>
-      <c r="H8" s="549"/>
-      <c r="I8" s="550"/>
-      <c r="J8" s="550"/>
-      <c r="K8" s="551"/>
+      <c r="H8" s="545"/>
+      <c r="I8" s="546"/>
+      <c r="J8" s="546"/>
+      <c r="K8" s="547"/>
     </row>
     <row r="9" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="543"/>
-      <c r="B9" s="544"/>
-      <c r="C9" s="544"/>
-      <c r="D9" s="545"/>
+      <c r="A9" s="539"/>
+      <c r="B9" s="540"/>
+      <c r="C9" s="540"/>
+      <c r="D9" s="541"/>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
       <c r="G9" s="19"/>
-      <c r="H9" s="549"/>
-      <c r="I9" s="550"/>
-      <c r="J9" s="550"/>
-      <c r="K9" s="551"/>
+      <c r="H9" s="545"/>
+      <c r="I9" s="546"/>
+      <c r="J9" s="546"/>
+      <c r="K9" s="547"/>
     </row>
     <row r="10" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="543"/>
-      <c r="B10" s="544"/>
-      <c r="C10" s="544"/>
-      <c r="D10" s="545"/>
+      <c r="A10" s="539"/>
+      <c r="B10" s="540"/>
+      <c r="C10" s="540"/>
+      <c r="D10" s="541"/>
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
       <c r="G10" s="19"/>
-      <c r="H10" s="549"/>
-      <c r="I10" s="550"/>
-      <c r="J10" s="550"/>
-      <c r="K10" s="551"/>
+      <c r="H10" s="545"/>
+      <c r="I10" s="546"/>
+      <c r="J10" s="546"/>
+      <c r="K10" s="547"/>
     </row>
     <row r="11" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="543"/>
-      <c r="B11" s="544"/>
-      <c r="C11" s="544"/>
-      <c r="D11" s="545"/>
+      <c r="A11" s="539"/>
+      <c r="B11" s="540"/>
+      <c r="C11" s="540"/>
+      <c r="D11" s="541"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
       <c r="G11" s="19"/>
-      <c r="H11" s="549"/>
-      <c r="I11" s="550"/>
-      <c r="J11" s="550"/>
-      <c r="K11" s="551"/>
+      <c r="H11" s="545"/>
+      <c r="I11" s="546"/>
+      <c r="J11" s="546"/>
+      <c r="K11" s="547"/>
     </row>
     <row r="12" spans="1:11" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="575"/>
-      <c r="B12" s="576"/>
-      <c r="C12" s="576"/>
-      <c r="D12" s="577"/>
+      <c r="A12" s="571"/>
+      <c r="B12" s="572"/>
+      <c r="C12" s="572"/>
+      <c r="D12" s="573"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="20"/>
-      <c r="H12" s="588"/>
-      <c r="I12" s="589"/>
-      <c r="J12" s="589"/>
-      <c r="K12" s="590"/>
+      <c r="H12" s="584"/>
+      <c r="I12" s="585"/>
+      <c r="J12" s="585"/>
+      <c r="K12" s="586"/>
     </row>
     <row r="13" spans="1:11" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="516" t="s">
+      <c r="A13" s="509" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="517"/>
-      <c r="C13" s="517"/>
-      <c r="D13" s="517"/>
-      <c r="E13" s="517"/>
-      <c r="F13" s="517"/>
-      <c r="G13" s="517"/>
-      <c r="H13" s="517"/>
-      <c r="I13" s="517"/>
-      <c r="J13" s="517"/>
-      <c r="K13" s="518"/>
+      <c r="B13" s="510"/>
+      <c r="C13" s="510"/>
+      <c r="D13" s="510"/>
+      <c r="E13" s="510"/>
+      <c r="F13" s="510"/>
+      <c r="G13" s="510"/>
+      <c r="H13" s="510"/>
+      <c r="I13" s="510"/>
+      <c r="J13" s="510"/>
+      <c r="K13" s="511"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="591" t="s">
+      <c r="A14" s="587" t="s">
         <v>326</v>
       </c>
-      <c r="B14" s="592"/>
-      <c r="C14" s="592"/>
-      <c r="D14" s="592"/>
-      <c r="E14" s="592"/>
-      <c r="F14" s="592"/>
-      <c r="G14" s="592"/>
-      <c r="H14" s="592"/>
-      <c r="I14" s="592"/>
-      <c r="J14" s="592"/>
-      <c r="K14" s="593"/>
+      <c r="B14" s="588"/>
+      <c r="C14" s="588"/>
+      <c r="D14" s="588"/>
+      <c r="E14" s="588"/>
+      <c r="F14" s="588"/>
+      <c r="G14" s="588"/>
+      <c r="H14" s="588"/>
+      <c r="I14" s="588"/>
+      <c r="J14" s="588"/>
+      <c r="K14" s="589"/>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="570" t="s">
+      <c r="A15" s="566" t="s">
         <v>327</v>
       </c>
-      <c r="B15" s="504" t="s">
+      <c r="B15" s="497" t="s">
         <v>328</v>
       </c>
-      <c r="C15" s="564"/>
-      <c r="D15" s="565"/>
-      <c r="E15" s="504" t="s">
+      <c r="C15" s="560"/>
+      <c r="D15" s="561"/>
+      <c r="E15" s="497" t="s">
         <v>329</v>
       </c>
-      <c r="F15" s="505"/>
-      <c r="G15" s="594" t="s">
+      <c r="F15" s="498"/>
+      <c r="G15" s="590" t="s">
         <v>324</v>
       </c>
-      <c r="H15" s="567" t="s">
+      <c r="H15" s="563" t="s">
         <v>330</v>
       </c>
-      <c r="I15" s="503" t="s">
+      <c r="I15" s="496" t="s">
         <v>331</v>
       </c>
-      <c r="J15" s="564"/>
-      <c r="K15" s="581"/>
+      <c r="J15" s="560"/>
+      <c r="K15" s="577"/>
     </row>
     <row r="16" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="570"/>
-      <c r="B16" s="564"/>
-      <c r="C16" s="564"/>
-      <c r="D16" s="565"/>
-      <c r="E16" s="485"/>
-      <c r="F16" s="486"/>
-      <c r="G16" s="594"/>
-      <c r="H16" s="567"/>
-      <c r="I16" s="580"/>
-      <c r="J16" s="564"/>
-      <c r="K16" s="581"/>
+      <c r="A16" s="566"/>
+      <c r="B16" s="560"/>
+      <c r="C16" s="560"/>
+      <c r="D16" s="561"/>
+      <c r="E16" s="478"/>
+      <c r="F16" s="479"/>
+      <c r="G16" s="590"/>
+      <c r="H16" s="563"/>
+      <c r="I16" s="576"/>
+      <c r="J16" s="560"/>
+      <c r="K16" s="577"/>
     </row>
     <row r="17" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
-      <c r="B17" s="363"/>
-      <c r="C17" s="363"/>
-      <c r="D17" s="566"/>
+      <c r="B17" s="367"/>
+      <c r="C17" s="367"/>
+      <c r="D17" s="562"/>
       <c r="E17" s="12" t="s">
         <v>129</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="595"/>
-      <c r="H17" s="568"/>
-      <c r="I17" s="582"/>
-      <c r="J17" s="363"/>
-      <c r="K17" s="364"/>
+      <c r="G17" s="591"/>
+      <c r="H17" s="564"/>
+      <c r="I17" s="578"/>
+      <c r="J17" s="367"/>
+      <c r="K17" s="368"/>
     </row>
     <row r="18" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="552"/>
-      <c r="B18" s="553"/>
-      <c r="C18" s="553"/>
-      <c r="D18" s="554"/>
+      <c r="A18" s="548"/>
+      <c r="B18" s="549"/>
+      <c r="C18" s="549"/>
+      <c r="D18" s="550"/>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
       <c r="G18" s="15"/>
       <c r="H18" s="14"/>
-      <c r="I18" s="555"/>
-      <c r="J18" s="556"/>
-      <c r="K18" s="557"/>
+      <c r="I18" s="551"/>
+      <c r="J18" s="552"/>
+      <c r="K18" s="553"/>
     </row>
     <row r="19" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="552"/>
-      <c r="B19" s="553"/>
-      <c r="C19" s="553"/>
-      <c r="D19" s="554"/>
+      <c r="A19" s="548"/>
+      <c r="B19" s="549"/>
+      <c r="C19" s="549"/>
+      <c r="D19" s="550"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
       <c r="G19" s="15"/>
       <c r="H19" s="14"/>
-      <c r="I19" s="251"/>
-      <c r="J19" s="266"/>
-      <c r="K19" s="267"/>
+      <c r="I19" s="248"/>
+      <c r="J19" s="263"/>
+      <c r="K19" s="264"/>
     </row>
     <row r="20" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="552"/>
-      <c r="B20" s="553"/>
-      <c r="C20" s="553"/>
-      <c r="D20" s="554"/>
+      <c r="A20" s="548"/>
+      <c r="B20" s="549"/>
+      <c r="C20" s="549"/>
+      <c r="D20" s="550"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
       <c r="G20" s="15"/>
       <c r="H20" s="14"/>
-      <c r="I20" s="251"/>
-      <c r="J20" s="266"/>
-      <c r="K20" s="267"/>
+      <c r="I20" s="248"/>
+      <c r="J20" s="263"/>
+      <c r="K20" s="264"/>
     </row>
     <row r="21" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="552"/>
-      <c r="B21" s="553"/>
-      <c r="C21" s="553"/>
-      <c r="D21" s="554"/>
+      <c r="A21" s="548"/>
+      <c r="B21" s="549"/>
+      <c r="C21" s="549"/>
+      <c r="D21" s="550"/>
       <c r="E21" s="13"/>
       <c r="F21" s="13"/>
       <c r="G21" s="15"/>
       <c r="H21" s="14"/>
-      <c r="I21" s="251"/>
-      <c r="J21" s="266"/>
-      <c r="K21" s="267"/>
+      <c r="I21" s="248"/>
+      <c r="J21" s="263"/>
+      <c r="K21" s="264"/>
     </row>
     <row r="22" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="552"/>
-      <c r="B22" s="553"/>
-      <c r="C22" s="553"/>
-      <c r="D22" s="554"/>
+      <c r="A22" s="548"/>
+      <c r="B22" s="549"/>
+      <c r="C22" s="549"/>
+      <c r="D22" s="550"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
       <c r="G22" s="15"/>
       <c r="H22" s="14"/>
-      <c r="I22" s="251"/>
-      <c r="J22" s="266"/>
-      <c r="K22" s="267"/>
+      <c r="I22" s="248"/>
+      <c r="J22" s="263"/>
+      <c r="K22" s="264"/>
     </row>
     <row r="23" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="552"/>
-      <c r="B23" s="553"/>
-      <c r="C23" s="553"/>
-      <c r="D23" s="554"/>
+      <c r="A23" s="548"/>
+      <c r="B23" s="549"/>
+      <c r="C23" s="549"/>
+      <c r="D23" s="550"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
       <c r="G23" s="15"/>
       <c r="H23" s="14"/>
-      <c r="I23" s="251"/>
-      <c r="J23" s="266"/>
-      <c r="K23" s="267"/>
+      <c r="I23" s="248"/>
+      <c r="J23" s="263"/>
+      <c r="K23" s="264"/>
     </row>
     <row r="24" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="552"/>
-      <c r="B24" s="553"/>
-      <c r="C24" s="553"/>
-      <c r="D24" s="554"/>
+      <c r="A24" s="548"/>
+      <c r="B24" s="549"/>
+      <c r="C24" s="549"/>
+      <c r="D24" s="550"/>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
       <c r="G24" s="15"/>
       <c r="H24" s="14"/>
-      <c r="I24" s="251"/>
-      <c r="J24" s="266"/>
-      <c r="K24" s="267"/>
+      <c r="I24" s="248"/>
+      <c r="J24" s="263"/>
+      <c r="K24" s="264"/>
     </row>
     <row r="25" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="552"/>
-      <c r="B25" s="553"/>
-      <c r="C25" s="553"/>
-      <c r="D25" s="554"/>
+      <c r="A25" s="548"/>
+      <c r="B25" s="549"/>
+      <c r="C25" s="549"/>
+      <c r="D25" s="550"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="15"/>
       <c r="H25" s="14"/>
-      <c r="I25" s="251"/>
-      <c r="J25" s="266"/>
-      <c r="K25" s="267"/>
+      <c r="I25" s="248"/>
+      <c r="J25" s="263"/>
+      <c r="K25" s="264"/>
     </row>
     <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="552"/>
-      <c r="B26" s="553"/>
-      <c r="C26" s="553"/>
-      <c r="D26" s="554"/>
+      <c r="A26" s="548"/>
+      <c r="B26" s="549"/>
+      <c r="C26" s="549"/>
+      <c r="D26" s="550"/>
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
       <c r="G26" s="15"/>
       <c r="H26" s="14"/>
-      <c r="I26" s="555"/>
-      <c r="J26" s="556"/>
-      <c r="K26" s="557"/>
+      <c r="I26" s="551"/>
+      <c r="J26" s="552"/>
+      <c r="K26" s="553"/>
     </row>
     <row r="27" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="552"/>
-      <c r="B27" s="553"/>
-      <c r="C27" s="553"/>
-      <c r="D27" s="554"/>
+      <c r="A27" s="548"/>
+      <c r="B27" s="549"/>
+      <c r="C27" s="549"/>
+      <c r="D27" s="550"/>
       <c r="E27" s="13"/>
       <c r="F27" s="13"/>
       <c r="G27" s="15"/>
       <c r="H27" s="14"/>
-      <c r="I27" s="555"/>
-      <c r="J27" s="556"/>
-      <c r="K27" s="557"/>
+      <c r="I27" s="551"/>
+      <c r="J27" s="552"/>
+      <c r="K27" s="553"/>
     </row>
     <row r="28" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="552"/>
-      <c r="B28" s="553"/>
-      <c r="C28" s="553"/>
-      <c r="D28" s="554"/>
+      <c r="A28" s="548"/>
+      <c r="B28" s="549"/>
+      <c r="C28" s="549"/>
+      <c r="D28" s="550"/>
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
       <c r="G28" s="15"/>
       <c r="H28" s="14"/>
-      <c r="I28" s="555"/>
-      <c r="J28" s="556"/>
-      <c r="K28" s="557"/>
+      <c r="I28" s="551"/>
+      <c r="J28" s="552"/>
+      <c r="K28" s="553"/>
     </row>
     <row r="29" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="248"/>
-      <c r="B29" s="249"/>
-      <c r="C29" s="249"/>
-      <c r="D29" s="250"/>
+      <c r="A29" s="245"/>
+      <c r="B29" s="246"/>
+      <c r="C29" s="246"/>
+      <c r="D29" s="247"/>
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
       <c r="G29" s="15"/>
       <c r="H29" s="14"/>
-      <c r="I29" s="251"/>
-      <c r="J29" s="266"/>
-      <c r="K29" s="267"/>
+      <c r="I29" s="248"/>
+      <c r="J29" s="263"/>
+      <c r="K29" s="264"/>
     </row>
     <row r="30" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="248"/>
-      <c r="B30" s="249"/>
-      <c r="C30" s="249"/>
-      <c r="D30" s="250"/>
+      <c r="A30" s="245"/>
+      <c r="B30" s="246"/>
+      <c r="C30" s="246"/>
+      <c r="D30" s="247"/>
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
       <c r="G30" s="15"/>
       <c r="H30" s="14"/>
-      <c r="I30" s="251"/>
-      <c r="J30" s="266"/>
-      <c r="K30" s="267"/>
+      <c r="I30" s="248"/>
+      <c r="J30" s="263"/>
+      <c r="K30" s="264"/>
     </row>
     <row r="31" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="248"/>
-      <c r="B31" s="249"/>
-      <c r="C31" s="249"/>
-      <c r="D31" s="250"/>
+      <c r="A31" s="245"/>
+      <c r="B31" s="246"/>
+      <c r="C31" s="246"/>
+      <c r="D31" s="247"/>
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
       <c r="G31" s="15"/>
       <c r="H31" s="14"/>
-      <c r="I31" s="251"/>
-      <c r="J31" s="266"/>
-      <c r="K31" s="267"/>
+      <c r="I31" s="248"/>
+      <c r="J31" s="263"/>
+      <c r="K31" s="264"/>
     </row>
     <row r="32" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="248"/>
-      <c r="B32" s="249"/>
-      <c r="C32" s="249"/>
-      <c r="D32" s="250"/>
+      <c r="A32" s="245"/>
+      <c r="B32" s="246"/>
+      <c r="C32" s="246"/>
+      <c r="D32" s="247"/>
       <c r="E32" s="13"/>
       <c r="F32" s="13"/>
       <c r="G32" s="15"/>
       <c r="H32" s="14"/>
-      <c r="I32" s="251"/>
-      <c r="J32" s="266"/>
-      <c r="K32" s="267"/>
+      <c r="I32" s="248"/>
+      <c r="J32" s="263"/>
+      <c r="K32" s="264"/>
     </row>
     <row r="33" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="248"/>
-      <c r="B33" s="249"/>
-      <c r="C33" s="249"/>
-      <c r="D33" s="250"/>
+      <c r="A33" s="245"/>
+      <c r="B33" s="246"/>
+      <c r="C33" s="246"/>
+      <c r="D33" s="247"/>
       <c r="E33" s="13"/>
       <c r="F33" s="13"/>
       <c r="G33" s="15"/>
       <c r="H33" s="14"/>
-      <c r="I33" s="251"/>
-      <c r="J33" s="266"/>
-      <c r="K33" s="267"/>
+      <c r="I33" s="248"/>
+      <c r="J33" s="263"/>
+      <c r="K33" s="264"/>
     </row>
     <row r="34" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="248"/>
-      <c r="B34" s="249"/>
-      <c r="C34" s="249"/>
-      <c r="D34" s="250"/>
+      <c r="A34" s="245"/>
+      <c r="B34" s="246"/>
+      <c r="C34" s="246"/>
+      <c r="D34" s="247"/>
       <c r="E34" s="13"/>
       <c r="F34" s="13"/>
       <c r="G34" s="15"/>
       <c r="H34" s="14"/>
-      <c r="I34" s="251"/>
-      <c r="J34" s="266"/>
-      <c r="K34" s="267"/>
+      <c r="I34" s="248"/>
+      <c r="J34" s="263"/>
+      <c r="K34" s="264"/>
     </row>
     <row r="35" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="552"/>
-      <c r="B35" s="553"/>
-      <c r="C35" s="553"/>
-      <c r="D35" s="554"/>
+      <c r="A35" s="548"/>
+      <c r="B35" s="549"/>
+      <c r="C35" s="549"/>
+      <c r="D35" s="550"/>
       <c r="E35" s="13"/>
       <c r="F35" s="13"/>
       <c r="G35" s="15"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="555"/>
-      <c r="J35" s="556"/>
-      <c r="K35" s="557"/>
+      <c r="I35" s="551"/>
+      <c r="J35" s="552"/>
+      <c r="K35" s="553"/>
     </row>
     <row r="36" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="552"/>
-      <c r="B36" s="553"/>
-      <c r="C36" s="553"/>
-      <c r="D36" s="554"/>
+      <c r="A36" s="548"/>
+      <c r="B36" s="549"/>
+      <c r="C36" s="549"/>
+      <c r="D36" s="550"/>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
       <c r="G36" s="15"/>
       <c r="H36" s="14"/>
-      <c r="I36" s="555"/>
-      <c r="J36" s="556"/>
-      <c r="K36" s="557"/>
+      <c r="I36" s="551"/>
+      <c r="J36" s="552"/>
+      <c r="K36" s="553"/>
     </row>
     <row r="37" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="552"/>
-      <c r="B37" s="553"/>
-      <c r="C37" s="553"/>
-      <c r="D37" s="554"/>
+      <c r="A37" s="548"/>
+      <c r="B37" s="549"/>
+      <c r="C37" s="549"/>
+      <c r="D37" s="550"/>
       <c r="E37" s="13"/>
       <c r="F37" s="13"/>
       <c r="G37" s="15"/>
       <c r="H37" s="14"/>
-      <c r="I37" s="555"/>
-      <c r="J37" s="556"/>
-      <c r="K37" s="557"/>
+      <c r="I37" s="551"/>
+      <c r="J37" s="552"/>
+      <c r="K37" s="553"/>
     </row>
     <row r="38" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="596"/>
-      <c r="B38" s="597"/>
-      <c r="C38" s="597"/>
-      <c r="D38" s="598"/>
+      <c r="A38" s="592"/>
+      <c r="B38" s="593"/>
+      <c r="C38" s="593"/>
+      <c r="D38" s="594"/>
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
       <c r="G38" s="16"/>
       <c r="H38" s="17"/>
-      <c r="I38" s="599"/>
-      <c r="J38" s="600"/>
-      <c r="K38" s="601"/>
+      <c r="I38" s="595"/>
+      <c r="J38" s="596"/>
+      <c r="K38" s="597"/>
     </row>
     <row r="39" spans="1:11" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="280" t="s">
+      <c r="A39" s="281" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="281"/>
-      <c r="C39" s="281"/>
-      <c r="D39" s="281"/>
-      <c r="E39" s="281"/>
-      <c r="F39" s="281"/>
-      <c r="G39" s="281"/>
-      <c r="H39" s="281"/>
-      <c r="I39" s="281"/>
-      <c r="J39" s="281"/>
-      <c r="K39" s="282"/>
+      <c r="B39" s="282"/>
+      <c r="C39" s="282"/>
+      <c r="D39" s="282"/>
+      <c r="E39" s="282"/>
+      <c r="F39" s="282"/>
+      <c r="G39" s="282"/>
+      <c r="H39" s="282"/>
+      <c r="I39" s="282"/>
+      <c r="J39" s="282"/>
+      <c r="K39" s="283"/>
     </row>
     <row r="40" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="558" t="s">
+      <c r="A40" s="554" t="s">
         <v>332</v>
       </c>
-      <c r="B40" s="559"/>
-      <c r="C40" s="559"/>
-      <c r="D40" s="559"/>
-      <c r="E40" s="559"/>
-      <c r="F40" s="559"/>
-      <c r="G40" s="559"/>
-      <c r="H40" s="559"/>
-      <c r="I40" s="559"/>
-      <c r="J40" s="559"/>
-      <c r="K40" s="560"/>
+      <c r="B40" s="555"/>
+      <c r="C40" s="555"/>
+      <c r="D40" s="555"/>
+      <c r="E40" s="555"/>
+      <c r="F40" s="555"/>
+      <c r="G40" s="555"/>
+      <c r="H40" s="555"/>
+      <c r="I40" s="555"/>
+      <c r="J40" s="555"/>
+      <c r="K40" s="556"/>
     </row>
     <row r="41" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="122" t="s">
@@ -17436,153 +17438,153 @@
       <c r="C41" s="123" t="s">
         <v>335</v>
       </c>
-      <c r="D41" s="541" t="s">
+      <c r="D41" s="537" t="s">
         <v>336</v>
       </c>
-      <c r="E41" s="541"/>
-      <c r="F41" s="541"/>
-      <c r="G41" s="541"/>
-      <c r="H41" s="542"/>
+      <c r="E41" s="537"/>
+      <c r="F41" s="537"/>
+      <c r="G41" s="537"/>
+      <c r="H41" s="538"/>
       <c r="I41" s="123" t="s">
         <v>337</v>
       </c>
-      <c r="J41" s="541" t="s">
+      <c r="J41" s="537" t="s">
         <v>338</v>
       </c>
-      <c r="K41" s="464"/>
+      <c r="K41" s="457"/>
     </row>
     <row r="42" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="536"/>
-      <c r="B42" s="537"/>
-      <c r="C42" s="538"/>
-      <c r="D42" s="539"/>
-      <c r="E42" s="539"/>
-      <c r="F42" s="539"/>
-      <c r="G42" s="539"/>
-      <c r="H42" s="537"/>
-      <c r="I42" s="538"/>
-      <c r="J42" s="539"/>
-      <c r="K42" s="540"/>
+      <c r="A42" s="532"/>
+      <c r="B42" s="533"/>
+      <c r="C42" s="534"/>
+      <c r="D42" s="535"/>
+      <c r="E42" s="535"/>
+      <c r="F42" s="535"/>
+      <c r="G42" s="535"/>
+      <c r="H42" s="533"/>
+      <c r="I42" s="534"/>
+      <c r="J42" s="535"/>
+      <c r="K42" s="536"/>
     </row>
     <row r="43" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="536"/>
-      <c r="B43" s="537"/>
-      <c r="C43" s="538"/>
-      <c r="D43" s="539"/>
-      <c r="E43" s="539"/>
-      <c r="F43" s="539"/>
-      <c r="G43" s="539"/>
-      <c r="H43" s="537"/>
-      <c r="I43" s="538"/>
-      <c r="J43" s="539"/>
-      <c r="K43" s="540"/>
+      <c r="A43" s="532"/>
+      <c r="B43" s="533"/>
+      <c r="C43" s="534"/>
+      <c r="D43" s="535"/>
+      <c r="E43" s="535"/>
+      <c r="F43" s="535"/>
+      <c r="G43" s="535"/>
+      <c r="H43" s="533"/>
+      <c r="I43" s="534"/>
+      <c r="J43" s="535"/>
+      <c r="K43" s="536"/>
     </row>
     <row r="44" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="536"/>
-      <c r="B44" s="537"/>
-      <c r="C44" s="538"/>
-      <c r="D44" s="539"/>
-      <c r="E44" s="539"/>
-      <c r="F44" s="539"/>
-      <c r="G44" s="539"/>
-      <c r="H44" s="537"/>
-      <c r="I44" s="538"/>
-      <c r="J44" s="539"/>
-      <c r="K44" s="540"/>
+      <c r="A44" s="532"/>
+      <c r="B44" s="533"/>
+      <c r="C44" s="534"/>
+      <c r="D44" s="535"/>
+      <c r="E44" s="535"/>
+      <c r="F44" s="535"/>
+      <c r="G44" s="535"/>
+      <c r="H44" s="533"/>
+      <c r="I44" s="534"/>
+      <c r="J44" s="535"/>
+      <c r="K44" s="536"/>
     </row>
     <row r="45" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="536"/>
-      <c r="B45" s="537"/>
-      <c r="C45" s="538"/>
-      <c r="D45" s="539"/>
-      <c r="E45" s="539"/>
-      <c r="F45" s="539"/>
-      <c r="G45" s="539"/>
-      <c r="H45" s="537"/>
-      <c r="I45" s="538"/>
-      <c r="J45" s="539"/>
-      <c r="K45" s="540"/>
+      <c r="A45" s="532"/>
+      <c r="B45" s="533"/>
+      <c r="C45" s="534"/>
+      <c r="D45" s="535"/>
+      <c r="E45" s="535"/>
+      <c r="F45" s="535"/>
+      <c r="G45" s="535"/>
+      <c r="H45" s="533"/>
+      <c r="I45" s="534"/>
+      <c r="J45" s="535"/>
+      <c r="K45" s="536"/>
     </row>
     <row r="46" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="536"/>
-      <c r="B46" s="537"/>
-      <c r="C46" s="538"/>
-      <c r="D46" s="539"/>
-      <c r="E46" s="539"/>
-      <c r="F46" s="539"/>
-      <c r="G46" s="539"/>
-      <c r="H46" s="537"/>
-      <c r="I46" s="538"/>
-      <c r="J46" s="539"/>
-      <c r="K46" s="540"/>
+      <c r="A46" s="532"/>
+      <c r="B46" s="533"/>
+      <c r="C46" s="534"/>
+      <c r="D46" s="535"/>
+      <c r="E46" s="535"/>
+      <c r="F46" s="535"/>
+      <c r="G46" s="535"/>
+      <c r="H46" s="533"/>
+      <c r="I46" s="534"/>
+      <c r="J46" s="535"/>
+      <c r="K46" s="536"/>
     </row>
     <row r="47" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="536"/>
-      <c r="B47" s="537"/>
-      <c r="C47" s="538"/>
-      <c r="D47" s="539"/>
-      <c r="E47" s="539"/>
-      <c r="F47" s="539"/>
-      <c r="G47" s="539"/>
-      <c r="H47" s="537"/>
-      <c r="I47" s="538"/>
-      <c r="J47" s="539"/>
-      <c r="K47" s="540"/>
+      <c r="A47" s="532"/>
+      <c r="B47" s="533"/>
+      <c r="C47" s="534"/>
+      <c r="D47" s="535"/>
+      <c r="E47" s="535"/>
+      <c r="F47" s="535"/>
+      <c r="G47" s="535"/>
+      <c r="H47" s="533"/>
+      <c r="I47" s="534"/>
+      <c r="J47" s="535"/>
+      <c r="K47" s="536"/>
     </row>
     <row r="48" spans="1:11" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="536"/>
-      <c r="B48" s="537"/>
-      <c r="C48" s="538"/>
-      <c r="D48" s="539"/>
-      <c r="E48" s="539"/>
-      <c r="F48" s="539"/>
-      <c r="G48" s="539"/>
-      <c r="H48" s="537"/>
-      <c r="I48" s="538"/>
-      <c r="J48" s="539"/>
-      <c r="K48" s="540"/>
+      <c r="A48" s="532"/>
+      <c r="B48" s="533"/>
+      <c r="C48" s="534"/>
+      <c r="D48" s="535"/>
+      <c r="E48" s="535"/>
+      <c r="F48" s="535"/>
+      <c r="G48" s="535"/>
+      <c r="H48" s="533"/>
+      <c r="I48" s="534"/>
+      <c r="J48" s="535"/>
+      <c r="K48" s="536"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="280" t="s">
+      <c r="A49" s="281" t="s">
         <v>114</v>
       </c>
-      <c r="B49" s="281"/>
-      <c r="C49" s="281"/>
-      <c r="D49" s="281"/>
-      <c r="E49" s="281"/>
-      <c r="F49" s="281"/>
-      <c r="G49" s="281"/>
-      <c r="H49" s="281"/>
-      <c r="I49" s="281"/>
-      <c r="J49" s="281"/>
-      <c r="K49" s="518"/>
+      <c r="B49" s="282"/>
+      <c r="C49" s="282"/>
+      <c r="D49" s="282"/>
+      <c r="E49" s="282"/>
+      <c r="F49" s="282"/>
+      <c r="G49" s="282"/>
+      <c r="H49" s="282"/>
+      <c r="I49" s="282"/>
+      <c r="J49" s="282"/>
+      <c r="K49" s="511"/>
     </row>
     <row r="50" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="277" t="s">
+      <c r="A50" s="278" t="s">
         <v>143</v>
       </c>
-      <c r="B50" s="279"/>
-      <c r="C50" s="508" t="s">
+      <c r="B50" s="280"/>
+      <c r="C50" s="501" t="s">
         <v>144</v>
       </c>
-      <c r="D50" s="534"/>
-      <c r="E50" s="534"/>
-      <c r="F50" s="535"/>
-      <c r="G50" s="532" t="s">
+      <c r="D50" s="529"/>
+      <c r="E50" s="529"/>
+      <c r="F50" s="530"/>
+      <c r="G50" s="527" t="s">
         <v>145</v>
       </c>
-      <c r="H50" s="533"/>
-      <c r="I50" s="751">
+      <c r="H50" s="528"/>
+      <c r="I50" s="525">
         <f ca="1">NOW()</f>
-        <v>45982.693544444446</v>
-      </c>
-      <c r="J50" s="753"/>
-      <c r="K50" s="752"/>
-      <c r="L50" s="215"/>
-      <c r="M50" s="215"/>
+        <v>45982.839370949077</v>
+      </c>
+      <c r="J50" s="531"/>
+      <c r="K50" s="526"/>
+      <c r="L50" s="212"/>
+      <c r="M50" s="212"/>
     </row>
     <row r="51" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K51" s="218" t="s">
+      <c r="K51" s="215" t="s">
         <v>401</v>
       </c>
     </row>
@@ -17713,320 +17715,320 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="718"/>
-      <c r="B1" s="719"/>
-      <c r="C1" s="719"/>
-      <c r="D1" s="719"/>
-      <c r="E1" s="719"/>
-      <c r="F1" s="719"/>
-      <c r="G1" s="719"/>
-      <c r="H1" s="719"/>
-      <c r="I1" s="719"/>
-      <c r="J1" s="719"/>
-      <c r="K1" s="719"/>
-      <c r="L1" s="719"/>
-      <c r="M1" s="720"/>
-      <c r="O1" s="246"/>
-      <c r="P1" s="246"/>
-      <c r="Q1" s="246"/>
-      <c r="R1" s="246"/>
-      <c r="S1" s="246"/>
-      <c r="T1" s="246"/>
-      <c r="U1" s="246"/>
-      <c r="V1" s="246"/>
-      <c r="W1" s="246"/>
+      <c r="A1" s="698"/>
+      <c r="B1" s="699"/>
+      <c r="C1" s="699"/>
+      <c r="D1" s="699"/>
+      <c r="E1" s="699"/>
+      <c r="F1" s="699"/>
+      <c r="G1" s="699"/>
+      <c r="H1" s="699"/>
+      <c r="I1" s="699"/>
+      <c r="J1" s="699"/>
+      <c r="K1" s="699"/>
+      <c r="L1" s="699"/>
+      <c r="M1" s="700"/>
+      <c r="O1" s="243"/>
+      <c r="P1" s="243"/>
+      <c r="Q1" s="243"/>
+      <c r="R1" s="243"/>
+      <c r="S1" s="243"/>
+      <c r="T1" s="243"/>
+      <c r="U1" s="243"/>
+      <c r="V1" s="243"/>
+      <c r="W1" s="243"/>
     </row>
     <row r="2" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="693" t="s">
+      <c r="A2" s="673" t="s">
         <v>339</v>
       </c>
-      <c r="B2" s="694"/>
-      <c r="C2" s="723" t="s">
+      <c r="B2" s="674"/>
+      <c r="C2" s="703" t="s">
         <v>340</v>
       </c>
-      <c r="D2" s="723"/>
-      <c r="E2" s="723"/>
-      <c r="F2" s="724"/>
+      <c r="D2" s="703"/>
+      <c r="E2" s="703"/>
+      <c r="F2" s="704"/>
       <c r="G2" s="21"/>
       <c r="H2" s="21"/>
-      <c r="I2" s="721"/>
-      <c r="J2" s="721"/>
+      <c r="I2" s="701"/>
+      <c r="J2" s="701"/>
       <c r="K2" s="22"/>
       <c r="L2" s="22"/>
       <c r="M2" s="23"/>
-      <c r="O2" s="247"/>
-      <c r="P2" s="244"/>
-      <c r="Q2" s="244"/>
-      <c r="R2" s="244"/>
-      <c r="S2" s="244"/>
-      <c r="T2" s="244"/>
-      <c r="U2" s="244"/>
-      <c r="V2" s="244"/>
-      <c r="W2" s="246"/>
+      <c r="O2" s="244"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="241"/>
+      <c r="U2" s="241"/>
+      <c r="V2" s="241"/>
+      <c r="W2" s="243"/>
     </row>
     <row r="3" spans="1:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
       <c r="B3" s="25"/>
-      <c r="C3" s="709" t="s">
+      <c r="C3" s="689" t="s">
         <v>341</v>
       </c>
-      <c r="D3" s="709"/>
-      <c r="E3" s="709"/>
-      <c r="F3" s="710"/>
+      <c r="D3" s="689"/>
+      <c r="E3" s="689"/>
+      <c r="F3" s="690"/>
       <c r="G3" s="26"/>
       <c r="H3" s="26"/>
-      <c r="I3" s="722"/>
-      <c r="J3" s="722"/>
+      <c r="I3" s="702"/>
+      <c r="J3" s="702"/>
       <c r="K3" s="27"/>
       <c r="L3" s="27"/>
       <c r="M3" s="28"/>
-      <c r="O3" s="247"/>
-      <c r="P3" s="244"/>
-      <c r="Q3" s="244"/>
-      <c r="R3" s="244"/>
-      <c r="S3" s="244"/>
-      <c r="T3" s="244"/>
-      <c r="U3" s="244"/>
-      <c r="V3" s="244"/>
-      <c r="W3" s="247"/>
+      <c r="O3" s="244"/>
+      <c r="P3" s="241"/>
+      <c r="Q3" s="241"/>
+      <c r="R3" s="241"/>
+      <c r="S3" s="241"/>
+      <c r="T3" s="241"/>
+      <c r="U3" s="241"/>
+      <c r="V3" s="241"/>
+      <c r="W3" s="244"/>
     </row>
     <row r="4" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
-      <c r="C4" s="709" t="s">
+      <c r="C4" s="689" t="s">
         <v>342</v>
       </c>
-      <c r="D4" s="709"/>
-      <c r="E4" s="709"/>
-      <c r="F4" s="710"/>
+      <c r="D4" s="689"/>
+      <c r="E4" s="689"/>
+      <c r="F4" s="690"/>
       <c r="M4" s="2"/>
-      <c r="O4" s="247"/>
-      <c r="P4" s="244"/>
-      <c r="Q4" s="244"/>
-      <c r="R4" s="244" t="s">
+      <c r="O4" s="244"/>
+      <c r="P4" s="241"/>
+      <c r="Q4" s="241"/>
+      <c r="R4" s="241" t="s">
         <v>417</v>
       </c>
-      <c r="S4" s="244" t="s">
+      <c r="S4" s="241" t="s">
         <v>418</v>
       </c>
-      <c r="T4" s="244"/>
-      <c r="U4" s="244"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="247"/>
+      <c r="T4" s="241"/>
+      <c r="U4" s="241"/>
+      <c r="V4" s="241"/>
+      <c r="W4" s="244"/>
     </row>
     <row r="5" spans="1:23" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
       <c r="B5" s="25"/>
-      <c r="C5" s="709"/>
-      <c r="D5" s="709"/>
-      <c r="E5" s="709"/>
-      <c r="F5" s="710"/>
-      <c r="G5" s="628"/>
-      <c r="H5" s="628"/>
-      <c r="I5" s="628"/>
-      <c r="J5" s="628"/>
-      <c r="K5" s="628"/>
-      <c r="L5" s="628"/>
+      <c r="C5" s="689"/>
+      <c r="D5" s="689"/>
+      <c r="E5" s="689"/>
+      <c r="F5" s="690"/>
+      <c r="G5" s="603"/>
+      <c r="H5" s="603"/>
+      <c r="I5" s="603"/>
+      <c r="J5" s="603"/>
+      <c r="K5" s="603"/>
+      <c r="L5" s="603"/>
       <c r="M5" s="2"/>
-      <c r="O5" s="247"/>
-      <c r="P5" s="244"/>
-      <c r="Q5" s="244"/>
-      <c r="R5" s="244"/>
-      <c r="S5" s="244"/>
-      <c r="T5" s="244"/>
-      <c r="U5" s="244"/>
-      <c r="V5" s="244"/>
-      <c r="W5" s="247"/>
+      <c r="O5" s="244"/>
+      <c r="P5" s="241"/>
+      <c r="Q5" s="241"/>
+      <c r="R5" s="241"/>
+      <c r="S5" s="241"/>
+      <c r="T5" s="241"/>
+      <c r="U5" s="241"/>
+      <c r="V5" s="241"/>
+      <c r="W5" s="244"/>
     </row>
     <row r="6" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="24"/>
       <c r="B6" s="25"/>
-      <c r="C6" s="709" t="s">
+      <c r="C6" s="689" t="s">
         <v>343</v>
       </c>
-      <c r="D6" s="709"/>
-      <c r="E6" s="709"/>
-      <c r="F6" s="710"/>
-      <c r="I6" s="714"/>
-      <c r="J6" s="714"/>
-      <c r="K6" s="714"/>
-      <c r="L6" s="714"/>
+      <c r="D6" s="689"/>
+      <c r="E6" s="689"/>
+      <c r="F6" s="690"/>
+      <c r="I6" s="694"/>
+      <c r="J6" s="694"/>
+      <c r="K6" s="694"/>
+      <c r="L6" s="694"/>
       <c r="M6" s="2"/>
-      <c r="O6" s="247"/>
-      <c r="P6" s="244">
+      <c r="O6" s="244"/>
+      <c r="P6" s="241">
         <v>34</v>
       </c>
-      <c r="Q6" s="244" t="s">
+      <c r="Q6" s="241" t="s">
         <v>419</v>
       </c>
-      <c r="R6" s="245"/>
-      <c r="S6" s="245"/>
-      <c r="T6" s="245" t="s">
+      <c r="R6" s="242"/>
+      <c r="S6" s="242"/>
+      <c r="T6" s="242" t="s">
         <v>420</v>
       </c>
-      <c r="U6" s="245" t="b">
+      <c r="U6" s="242" t="b">
         <v>0</v>
       </c>
-      <c r="V6" s="245"/>
-      <c r="W6" s="247"/>
+      <c r="V6" s="242"/>
+      <c r="W6" s="244"/>
     </row>
     <row r="7" spans="1:23" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="24"/>
       <c r="B7" s="25"/>
-      <c r="C7" s="164"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="164"/>
-      <c r="F7" s="165"/>
-      <c r="I7" s="168"/>
-      <c r="J7" s="168"/>
-      <c r="K7" s="168"/>
-      <c r="L7" s="168"/>
+      <c r="C7" s="161"/>
+      <c r="D7" s="161"/>
+      <c r="E7" s="161"/>
+      <c r="F7" s="162"/>
+      <c r="I7" s="165"/>
+      <c r="J7" s="165"/>
+      <c r="K7" s="165"/>
+      <c r="L7" s="165"/>
       <c r="M7" s="2"/>
-      <c r="O7" s="247"/>
-      <c r="P7" s="244"/>
-      <c r="Q7" s="244"/>
-      <c r="R7" s="245"/>
-      <c r="S7" s="245"/>
-      <c r="T7" s="245"/>
-      <c r="U7" s="245"/>
-      <c r="V7" s="245"/>
-      <c r="W7" s="247"/>
+      <c r="O7" s="244"/>
+      <c r="P7" s="241"/>
+      <c r="Q7" s="241"/>
+      <c r="R7" s="242"/>
+      <c r="S7" s="242"/>
+      <c r="T7" s="242"/>
+      <c r="U7" s="242"/>
+      <c r="V7" s="242"/>
+      <c r="W7" s="244"/>
     </row>
     <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="24"/>
       <c r="B8" s="25"/>
-      <c r="C8" s="709" t="s">
+      <c r="C8" s="689" t="s">
         <v>344</v>
       </c>
-      <c r="D8" s="709"/>
-      <c r="E8" s="709"/>
-      <c r="F8" s="710"/>
+      <c r="D8" s="689"/>
+      <c r="E8" s="689"/>
+      <c r="F8" s="690"/>
       <c r="M8" s="29"/>
-      <c r="O8" s="247"/>
-      <c r="P8" s="244">
+      <c r="O8" s="244"/>
+      <c r="P8" s="241">
         <v>35</v>
       </c>
-      <c r="Q8" s="244" t="s">
+      <c r="Q8" s="241" t="s">
         <v>419</v>
       </c>
-      <c r="R8" s="245"/>
-      <c r="S8" s="245"/>
-      <c r="T8" s="245"/>
-      <c r="U8" s="245"/>
-      <c r="V8" s="245"/>
-      <c r="W8" s="247"/>
+      <c r="R8" s="242"/>
+      <c r="S8" s="242"/>
+      <c r="T8" s="242"/>
+      <c r="U8" s="242"/>
+      <c r="V8" s="242"/>
+      <c r="W8" s="244"/>
     </row>
     <row r="9" spans="1:23" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="24"/>
       <c r="B9" s="25"/>
-      <c r="C9" s="164"/>
-      <c r="D9" s="164"/>
-      <c r="E9" s="164"/>
-      <c r="F9" s="165"/>
+      <c r="C9" s="161"/>
+      <c r="D9" s="161"/>
+      <c r="E9" s="161"/>
+      <c r="F9" s="162"/>
       <c r="M9" s="29"/>
-      <c r="O9" s="247"/>
-      <c r="P9" s="244"/>
-      <c r="Q9" s="244"/>
-      <c r="R9" s="245"/>
-      <c r="S9" s="245"/>
-      <c r="T9" s="245"/>
-      <c r="U9" s="245"/>
-      <c r="V9" s="245"/>
-      <c r="W9" s="247"/>
+      <c r="O9" s="244"/>
+      <c r="P9" s="241"/>
+      <c r="Q9" s="241"/>
+      <c r="R9" s="242"/>
+      <c r="S9" s="242"/>
+      <c r="T9" s="242"/>
+      <c r="U9" s="242"/>
+      <c r="V9" s="242"/>
+      <c r="W9" s="244"/>
     </row>
     <row r="10" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="24"/>
       <c r="B10" s="25"/>
-      <c r="C10" s="709"/>
-      <c r="D10" s="709"/>
-      <c r="E10" s="709"/>
-      <c r="F10" s="710"/>
-      <c r="G10" s="628" t="s">
+      <c r="C10" s="689"/>
+      <c r="D10" s="689"/>
+      <c r="E10" s="689"/>
+      <c r="F10" s="690"/>
+      <c r="G10" s="603" t="s">
         <v>345</v>
       </c>
-      <c r="H10" s="628"/>
-      <c r="I10" s="628"/>
-      <c r="J10" s="628"/>
-      <c r="K10" s="628"/>
-      <c r="L10" s="628"/>
+      <c r="H10" s="603"/>
+      <c r="I10" s="603"/>
+      <c r="J10" s="603"/>
+      <c r="K10" s="603"/>
+      <c r="L10" s="603"/>
       <c r="M10" s="74"/>
-      <c r="O10" s="247"/>
-      <c r="P10" s="244"/>
-      <c r="Q10" s="244" t="s">
+      <c r="O10" s="244"/>
+      <c r="P10" s="241"/>
+      <c r="Q10" s="241" t="s">
         <v>420</v>
       </c>
-      <c r="R10" s="245" t="b">
+      <c r="R10" s="242" t="b">
         <v>0</v>
       </c>
-      <c r="S10" s="245" t="b">
+      <c r="S10" s="242" t="b">
         <v>0</v>
       </c>
-      <c r="T10" s="245"/>
-      <c r="U10" s="245"/>
-      <c r="V10" s="245"/>
-      <c r="W10" s="247"/>
+      <c r="T10" s="242"/>
+      <c r="U10" s="242"/>
+      <c r="V10" s="242"/>
+      <c r="W10" s="244"/>
     </row>
     <row r="11" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="24"/>
       <c r="B11" s="25"/>
-      <c r="C11" s="709"/>
-      <c r="D11" s="709"/>
-      <c r="E11" s="709"/>
-      <c r="F11" s="710"/>
-      <c r="G11" s="715"/>
-      <c r="H11" s="716"/>
-      <c r="I11" s="716"/>
-      <c r="J11" s="716"/>
-      <c r="K11" s="716"/>
-      <c r="L11" s="716"/>
-      <c r="M11" s="717"/>
-      <c r="O11" s="247"/>
-      <c r="P11" s="244">
+      <c r="C11" s="689"/>
+      <c r="D11" s="689"/>
+      <c r="E11" s="689"/>
+      <c r="F11" s="690"/>
+      <c r="G11" s="695"/>
+      <c r="H11" s="696"/>
+      <c r="I11" s="696"/>
+      <c r="J11" s="696"/>
+      <c r="K11" s="696"/>
+      <c r="L11" s="696"/>
+      <c r="M11" s="697"/>
+      <c r="O11" s="244"/>
+      <c r="P11" s="241">
         <v>36</v>
       </c>
-      <c r="Q11" s="244"/>
-      <c r="R11" s="245"/>
-      <c r="S11" s="245"/>
-      <c r="T11" s="245"/>
-      <c r="U11" s="245"/>
-      <c r="V11" s="245"/>
-      <c r="W11" s="247"/>
+      <c r="Q11" s="241"/>
+      <c r="R11" s="242"/>
+      <c r="S11" s="242"/>
+      <c r="T11" s="242"/>
+      <c r="U11" s="242"/>
+      <c r="V11" s="242"/>
+      <c r="W11" s="244"/>
     </row>
     <row r="12" spans="1:23" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="30"/>
       <c r="B12" s="31"/>
-      <c r="C12" s="711"/>
-      <c r="D12" s="711"/>
-      <c r="E12" s="711"/>
-      <c r="F12" s="712"/>
+      <c r="C12" s="691"/>
+      <c r="D12" s="691"/>
+      <c r="E12" s="691"/>
+      <c r="F12" s="692"/>
       <c r="G12" s="130"/>
       <c r="H12" s="130"/>
-      <c r="I12" s="713"/>
-      <c r="J12" s="713"/>
-      <c r="K12" s="713"/>
-      <c r="L12" s="713"/>
+      <c r="I12" s="693"/>
+      <c r="J12" s="693"/>
+      <c r="K12" s="693"/>
+      <c r="L12" s="693"/>
       <c r="M12" s="110"/>
-      <c r="O12" s="247"/>
-      <c r="P12" s="244"/>
-      <c r="Q12" s="244"/>
-      <c r="R12" s="245"/>
-      <c r="S12" s="245"/>
-      <c r="T12" s="245"/>
-      <c r="U12" s="245"/>
-      <c r="V12" s="245"/>
-      <c r="W12" s="247"/>
+      <c r="O12" s="244"/>
+      <c r="P12" s="241"/>
+      <c r="Q12" s="241"/>
+      <c r="R12" s="242"/>
+      <c r="S12" s="242"/>
+      <c r="T12" s="242"/>
+      <c r="U12" s="242"/>
+      <c r="V12" s="242"/>
+      <c r="W12" s="244"/>
     </row>
     <row r="13" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="740" t="s">
+      <c r="A13" s="721" t="s">
         <v>346</v>
       </c>
-      <c r="B13" s="741"/>
-      <c r="C13" s="731" t="s">
+      <c r="B13" s="722"/>
+      <c r="C13" s="712" t="s">
         <v>347</v>
       </c>
-      <c r="D13" s="731"/>
-      <c r="E13" s="564"/>
-      <c r="F13" s="565"/>
+      <c r="D13" s="712"/>
+      <c r="E13" s="560"/>
+      <c r="F13" s="561"/>
       <c r="G13" s="32"/>
       <c r="H13" s="32"/>
       <c r="I13" s="32"/>
@@ -18034,97 +18036,97 @@
       <c r="K13" s="32"/>
       <c r="L13" s="32"/>
       <c r="M13" s="33"/>
-      <c r="O13" s="247"/>
-      <c r="P13" s="244">
+      <c r="O13" s="244"/>
+      <c r="P13" s="241">
         <v>37</v>
       </c>
-      <c r="Q13" s="244"/>
-      <c r="R13" s="245"/>
-      <c r="S13" s="245"/>
-      <c r="T13" s="245"/>
-      <c r="U13" s="245"/>
-      <c r="V13" s="245"/>
-      <c r="W13" s="247"/>
+      <c r="Q13" s="241"/>
+      <c r="R13" s="242"/>
+      <c r="S13" s="242"/>
+      <c r="T13" s="242"/>
+      <c r="U13" s="242"/>
+      <c r="V13" s="242"/>
+      <c r="W13" s="244"/>
     </row>
     <row r="14" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="47"/>
       <c r="B14" s="48"/>
-      <c r="C14" s="731"/>
-      <c r="D14" s="731"/>
-      <c r="E14" s="564"/>
-      <c r="F14" s="565"/>
-      <c r="G14" s="627" t="s">
+      <c r="C14" s="712"/>
+      <c r="D14" s="712"/>
+      <c r="E14" s="560"/>
+      <c r="F14" s="561"/>
+      <c r="G14" s="602" t="s">
         <v>345</v>
       </c>
-      <c r="H14" s="628"/>
-      <c r="I14" s="628"/>
-      <c r="J14" s="628"/>
-      <c r="K14" s="628"/>
-      <c r="L14" s="628"/>
+      <c r="H14" s="603"/>
+      <c r="I14" s="603"/>
+      <c r="J14" s="603"/>
+      <c r="K14" s="603"/>
+      <c r="L14" s="603"/>
       <c r="M14" s="109"/>
-      <c r="O14" s="247"/>
-      <c r="P14" s="244">
+      <c r="O14" s="244"/>
+      <c r="P14" s="241">
         <v>38</v>
       </c>
-      <c r="Q14" s="244" t="s">
+      <c r="Q14" s="241" t="s">
         <v>419</v>
       </c>
-      <c r="R14" s="245"/>
-      <c r="S14" s="245"/>
-      <c r="T14" s="245"/>
-      <c r="U14" s="245"/>
-      <c r="V14" s="245"/>
-      <c r="W14" s="247"/>
+      <c r="R14" s="242"/>
+      <c r="S14" s="242"/>
+      <c r="T14" s="242"/>
+      <c r="U14" s="242"/>
+      <c r="V14" s="242"/>
+      <c r="W14" s="244"/>
     </row>
     <row r="15" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="47"/>
       <c r="B15" s="48"/>
-      <c r="C15" s="731"/>
-      <c r="D15" s="731"/>
-      <c r="E15" s="564"/>
-      <c r="F15" s="565"/>
-      <c r="G15" s="742"/>
-      <c r="H15" s="743"/>
-      <c r="I15" s="743"/>
-      <c r="J15" s="743"/>
-      <c r="K15" s="743"/>
-      <c r="L15" s="743"/>
-      <c r="M15" s="744"/>
-      <c r="O15" s="247"/>
-      <c r="P15" s="244"/>
-      <c r="Q15" s="244" t="s">
+      <c r="C15" s="712"/>
+      <c r="D15" s="712"/>
+      <c r="E15" s="560"/>
+      <c r="F15" s="561"/>
+      <c r="G15" s="723"/>
+      <c r="H15" s="724"/>
+      <c r="I15" s="724"/>
+      <c r="J15" s="724"/>
+      <c r="K15" s="724"/>
+      <c r="L15" s="724"/>
+      <c r="M15" s="725"/>
+      <c r="O15" s="244"/>
+      <c r="P15" s="241"/>
+      <c r="Q15" s="241" t="s">
         <v>420</v>
       </c>
-      <c r="R15" s="245"/>
-      <c r="S15" s="245"/>
-      <c r="T15" s="245"/>
-      <c r="U15" s="245"/>
-      <c r="V15" s="245"/>
-      <c r="W15" s="247"/>
+      <c r="R15" s="242"/>
+      <c r="S15" s="242"/>
+      <c r="T15" s="242"/>
+      <c r="U15" s="242"/>
+      <c r="V15" s="242"/>
+      <c r="W15" s="244"/>
     </row>
     <row r="16" spans="1:23" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="34"/>
       <c r="B16" s="35"/>
-      <c r="C16" s="564"/>
-      <c r="D16" s="564"/>
-      <c r="E16" s="564"/>
-      <c r="F16" s="565"/>
+      <c r="C16" s="560"/>
+      <c r="D16" s="560"/>
+      <c r="E16" s="560"/>
+      <c r="F16" s="561"/>
       <c r="G16" s="106"/>
-      <c r="H16" s="219"/>
-      <c r="I16" s="728"/>
-      <c r="J16" s="728"/>
-      <c r="K16" s="728"/>
-      <c r="L16" s="728"/>
+      <c r="H16" s="216"/>
+      <c r="I16" s="709"/>
+      <c r="J16" s="709"/>
+      <c r="K16" s="709"/>
+      <c r="L16" s="709"/>
       <c r="M16" s="107"/>
-      <c r="O16" s="247"/>
-      <c r="P16" s="244"/>
-      <c r="Q16" s="244"/>
-      <c r="R16" s="245"/>
-      <c r="S16" s="245"/>
-      <c r="T16" s="245"/>
-      <c r="U16" s="245"/>
-      <c r="V16" s="245"/>
-      <c r="W16" s="247"/>
+      <c r="O16" s="244"/>
+      <c r="P16" s="241"/>
+      <c r="Q16" s="241"/>
+      <c r="R16" s="242"/>
+      <c r="S16" s="242"/>
+      <c r="T16" s="242"/>
+      <c r="U16" s="242"/>
+      <c r="V16" s="242"/>
+      <c r="W16" s="244"/>
     </row>
     <row r="17" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="36"/>
@@ -18140,25 +18142,25 @@
       <c r="K17" s="92"/>
       <c r="L17" s="92"/>
       <c r="M17" s="93"/>
-      <c r="O17" s="247"/>
-      <c r="P17" s="244"/>
-      <c r="Q17" s="244"/>
-      <c r="R17" s="245"/>
-      <c r="S17" s="245"/>
-      <c r="T17" s="245"/>
-      <c r="U17" s="245"/>
-      <c r="V17" s="245"/>
-      <c r="W17" s="247"/>
+      <c r="O17" s="244"/>
+      <c r="P17" s="241"/>
+      <c r="Q17" s="241"/>
+      <c r="R17" s="242"/>
+      <c r="S17" s="242"/>
+      <c r="T17" s="242"/>
+      <c r="U17" s="242"/>
+      <c r="V17" s="242"/>
+      <c r="W17" s="244"/>
     </row>
     <row r="18" spans="1:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="36"/>
       <c r="B18" s="37"/>
-      <c r="C18" s="630" t="s">
+      <c r="C18" s="605" t="s">
         <v>348</v>
       </c>
-      <c r="D18" s="630"/>
-      <c r="E18" s="631"/>
-      <c r="F18" s="632"/>
+      <c r="D18" s="605"/>
+      <c r="E18" s="606"/>
+      <c r="F18" s="607"/>
       <c r="G18" s="41"/>
       <c r="H18" s="41"/>
       <c r="I18" s="41"/>
@@ -18166,141 +18168,141 @@
       <c r="K18" s="41"/>
       <c r="L18" s="41"/>
       <c r="M18" s="42"/>
-      <c r="O18" s="247"/>
-      <c r="P18" s="244">
+      <c r="O18" s="244"/>
+      <c r="P18" s="241">
         <v>39</v>
       </c>
-      <c r="Q18" s="244"/>
-      <c r="R18" s="245"/>
-      <c r="S18" s="245"/>
-      <c r="T18" s="245"/>
-      <c r="U18" s="245"/>
-      <c r="V18" s="245"/>
-      <c r="W18" s="247"/>
+      <c r="Q18" s="241"/>
+      <c r="R18" s="242"/>
+      <c r="S18" s="242"/>
+      <c r="T18" s="242"/>
+      <c r="U18" s="242"/>
+      <c r="V18" s="242"/>
+      <c r="W18" s="244"/>
     </row>
     <row r="19" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="36"/>
       <c r="B19" s="37"/>
-      <c r="C19" s="630"/>
-      <c r="D19" s="630"/>
-      <c r="E19" s="631"/>
-      <c r="F19" s="632"/>
-      <c r="G19" s="627" t="s">
+      <c r="C19" s="605"/>
+      <c r="D19" s="605"/>
+      <c r="E19" s="606"/>
+      <c r="F19" s="607"/>
+      <c r="G19" s="602" t="s">
         <v>345</v>
       </c>
-      <c r="H19" s="628"/>
-      <c r="I19" s="628"/>
-      <c r="J19" s="628"/>
-      <c r="K19" s="628"/>
-      <c r="L19" s="628"/>
+      <c r="H19" s="603"/>
+      <c r="I19" s="603"/>
+      <c r="J19" s="603"/>
+      <c r="K19" s="603"/>
+      <c r="L19" s="603"/>
       <c r="M19" s="42"/>
-      <c r="O19" s="247"/>
-      <c r="P19" s="244">
+      <c r="O19" s="244"/>
+      <c r="P19" s="241">
         <v>40</v>
       </c>
-      <c r="Q19" s="244" t="s">
+      <c r="Q19" s="241" t="s">
         <v>419</v>
       </c>
-      <c r="R19" s="245"/>
-      <c r="S19" s="245"/>
-      <c r="T19" s="245"/>
-      <c r="U19" s="245"/>
-      <c r="V19" s="245"/>
-      <c r="W19" s="247"/>
+      <c r="R19" s="242"/>
+      <c r="S19" s="242"/>
+      <c r="T19" s="242"/>
+      <c r="U19" s="242"/>
+      <c r="V19" s="242"/>
+      <c r="W19" s="244"/>
     </row>
     <row r="20" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="36"/>
       <c r="B20" s="37"/>
-      <c r="C20" s="630"/>
-      <c r="D20" s="630"/>
-      <c r="E20" s="631"/>
-      <c r="F20" s="632"/>
+      <c r="C20" s="605"/>
+      <c r="D20" s="605"/>
+      <c r="E20" s="606"/>
+      <c r="F20" s="607"/>
       <c r="G20" s="41"/>
-      <c r="H20" s="603" t="s">
+      <c r="H20" s="743" t="s">
         <v>349</v>
       </c>
-      <c r="I20" s="603"/>
-      <c r="J20" s="229"/>
-      <c r="K20" s="735"/>
-      <c r="L20" s="735"/>
-      <c r="M20" s="736"/>
-      <c r="O20" s="247"/>
-      <c r="P20" s="244"/>
-      <c r="Q20" s="244" t="s">
+      <c r="I20" s="743"/>
+      <c r="J20" s="226"/>
+      <c r="K20" s="729"/>
+      <c r="L20" s="729"/>
+      <c r="M20" s="730"/>
+      <c r="O20" s="244"/>
+      <c r="P20" s="241"/>
+      <c r="Q20" s="241" t="s">
         <v>420</v>
       </c>
-      <c r="R20" s="245"/>
-      <c r="S20" s="245"/>
-      <c r="T20" s="245"/>
-      <c r="U20" s="245"/>
-      <c r="V20" s="245"/>
-      <c r="W20" s="247"/>
+      <c r="R20" s="242"/>
+      <c r="S20" s="242"/>
+      <c r="T20" s="242"/>
+      <c r="U20" s="242"/>
+      <c r="V20" s="242"/>
+      <c r="W20" s="244"/>
     </row>
     <row r="21" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="36"/>
       <c r="B21" s="37"/>
-      <c r="C21" s="630"/>
-      <c r="D21" s="630"/>
-      <c r="E21" s="631"/>
-      <c r="F21" s="632"/>
-      <c r="G21" s="604" t="s">
+      <c r="C21" s="605"/>
+      <c r="D21" s="605"/>
+      <c r="E21" s="606"/>
+      <c r="F21" s="607"/>
+      <c r="G21" s="744" t="s">
         <v>350</v>
       </c>
-      <c r="H21" s="605"/>
-      <c r="I21" s="605"/>
-      <c r="J21" s="229"/>
-      <c r="K21" s="735"/>
-      <c r="L21" s="735"/>
-      <c r="M21" s="736"/>
-      <c r="O21" s="247"/>
-      <c r="P21" s="244"/>
-      <c r="Q21" s="244" t="s">
+      <c r="H21" s="745"/>
+      <c r="I21" s="745"/>
+      <c r="J21" s="226"/>
+      <c r="K21" s="729"/>
+      <c r="L21" s="729"/>
+      <c r="M21" s="730"/>
+      <c r="O21" s="244"/>
+      <c r="P21" s="241"/>
+      <c r="Q21" s="241" t="s">
         <v>421</v>
       </c>
-      <c r="R21" s="245"/>
-      <c r="S21" s="245"/>
-      <c r="T21" s="245"/>
-      <c r="U21" s="245"/>
-      <c r="V21" s="245"/>
-      <c r="W21" s="247"/>
+      <c r="R21" s="242"/>
+      <c r="S21" s="242"/>
+      <c r="T21" s="242"/>
+      <c r="U21" s="242"/>
+      <c r="V21" s="242"/>
+      <c r="W21" s="244"/>
     </row>
     <row r="22" spans="1:23" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="43"/>
       <c r="B22" s="44"/>
-      <c r="C22" s="633"/>
-      <c r="D22" s="633"/>
-      <c r="E22" s="633"/>
-      <c r="F22" s="634"/>
+      <c r="C22" s="608"/>
+      <c r="D22" s="608"/>
+      <c r="E22" s="608"/>
+      <c r="F22" s="609"/>
       <c r="G22" s="106" t="s">
         <v>351</v>
       </c>
-      <c r="H22" s="219"/>
-      <c r="I22" s="635"/>
-      <c r="J22" s="635"/>
-      <c r="K22" s="635"/>
+      <c r="H22" s="216"/>
+      <c r="I22" s="610"/>
+      <c r="J22" s="610"/>
+      <c r="K22" s="610"/>
       <c r="L22" s="111"/>
       <c r="M22" s="107"/>
-      <c r="O22" s="247"/>
-      <c r="P22" s="244"/>
-      <c r="Q22" s="244"/>
-      <c r="R22" s="244"/>
-      <c r="S22" s="244"/>
-      <c r="T22" s="244"/>
-      <c r="U22" s="244"/>
-      <c r="V22" s="244"/>
-      <c r="W22" s="247"/>
+      <c r="O22" s="244"/>
+      <c r="P22" s="241"/>
+      <c r="Q22" s="241"/>
+      <c r="R22" s="241"/>
+      <c r="S22" s="241"/>
+      <c r="T22" s="241"/>
+      <c r="U22" s="241"/>
+      <c r="V22" s="241"/>
+      <c r="W22" s="244"/>
     </row>
     <row r="23" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="623" t="s">
+      <c r="A23" s="598" t="s">
         <v>352</v>
       </c>
-      <c r="B23" s="624"/>
-      <c r="C23" s="636" t="s">
+      <c r="B23" s="599"/>
+      <c r="C23" s="611" t="s">
         <v>353</v>
       </c>
-      <c r="D23" s="636"/>
-      <c r="E23" s="636"/>
-      <c r="F23" s="637"/>
+      <c r="D23" s="611"/>
+      <c r="E23" s="611"/>
+      <c r="F23" s="612"/>
       <c r="G23" s="32"/>
       <c r="H23" s="32"/>
       <c r="I23" s="32"/>
@@ -18308,101 +18310,101 @@
       <c r="K23" s="32"/>
       <c r="L23" s="32"/>
       <c r="M23" s="33"/>
-      <c r="O23" s="247"/>
-      <c r="P23" s="244"/>
-      <c r="Q23" s="244"/>
-      <c r="R23" s="244"/>
-      <c r="S23" s="244"/>
-      <c r="T23" s="244"/>
-      <c r="U23" s="244"/>
-      <c r="V23" s="244"/>
-      <c r="W23" s="247"/>
+      <c r="O23" s="244"/>
+      <c r="P23" s="241"/>
+      <c r="Q23" s="241"/>
+      <c r="R23" s="241"/>
+      <c r="S23" s="241"/>
+      <c r="T23" s="241"/>
+      <c r="U23" s="241"/>
+      <c r="V23" s="241"/>
+      <c r="W23" s="244"/>
     </row>
     <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="34"/>
       <c r="B24" s="35"/>
-      <c r="C24" s="638"/>
-      <c r="D24" s="638"/>
-      <c r="E24" s="638"/>
-      <c r="F24" s="639"/>
-      <c r="G24" s="627" t="s">
+      <c r="C24" s="613"/>
+      <c r="D24" s="613"/>
+      <c r="E24" s="613"/>
+      <c r="F24" s="614"/>
+      <c r="G24" s="602" t="s">
         <v>345</v>
       </c>
-      <c r="H24" s="628"/>
-      <c r="I24" s="628"/>
-      <c r="J24" s="628"/>
-      <c r="K24" s="628"/>
-      <c r="L24" s="628"/>
+      <c r="H24" s="603"/>
+      <c r="I24" s="603"/>
+      <c r="J24" s="603"/>
+      <c r="K24" s="603"/>
+      <c r="L24" s="603"/>
       <c r="M24" s="105"/>
-      <c r="O24" s="247"/>
-      <c r="P24" s="244"/>
-      <c r="Q24" s="244"/>
-      <c r="R24" s="244"/>
-      <c r="S24" s="244"/>
-      <c r="T24" s="244"/>
-      <c r="U24" s="244"/>
-      <c r="V24" s="244"/>
-      <c r="W24" s="246"/>
+      <c r="O24" s="244"/>
+      <c r="P24" s="241"/>
+      <c r="Q24" s="241"/>
+      <c r="R24" s="241"/>
+      <c r="S24" s="241"/>
+      <c r="T24" s="241"/>
+      <c r="U24" s="241"/>
+      <c r="V24" s="241"/>
+      <c r="W24" s="243"/>
     </row>
     <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34"/>
       <c r="B25" s="35"/>
-      <c r="C25" s="638"/>
-      <c r="D25" s="638"/>
-      <c r="E25" s="638"/>
-      <c r="F25" s="639"/>
+      <c r="C25" s="613"/>
+      <c r="D25" s="613"/>
+      <c r="E25" s="613"/>
+      <c r="F25" s="614"/>
       <c r="G25" s="104"/>
-      <c r="H25" s="602"/>
-      <c r="I25" s="602"/>
-      <c r="J25" s="602"/>
-      <c r="K25" s="602"/>
-      <c r="L25" s="602"/>
+      <c r="H25" s="720"/>
+      <c r="I25" s="720"/>
+      <c r="J25" s="720"/>
+      <c r="K25" s="720"/>
+      <c r="L25" s="720"/>
       <c r="M25" s="105"/>
-      <c r="O25" s="247"/>
-      <c r="P25" s="244"/>
-      <c r="Q25" s="244"/>
-      <c r="R25" s="244"/>
-      <c r="S25" s="244"/>
-      <c r="T25" s="244"/>
-      <c r="U25" s="244"/>
-      <c r="V25" s="244"/>
-      <c r="W25" s="246"/>
+      <c r="O25" s="244"/>
+      <c r="P25" s="241"/>
+      <c r="Q25" s="241"/>
+      <c r="R25" s="241"/>
+      <c r="S25" s="241"/>
+      <c r="T25" s="241"/>
+      <c r="U25" s="241"/>
+      <c r="V25" s="241"/>
+      <c r="W25" s="243"/>
     </row>
     <row r="26" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="45"/>
       <c r="B26" s="46"/>
-      <c r="C26" s="640"/>
-      <c r="D26" s="640"/>
-      <c r="E26" s="640"/>
-      <c r="F26" s="641"/>
+      <c r="C26" s="615"/>
+      <c r="D26" s="615"/>
+      <c r="E26" s="615"/>
+      <c r="F26" s="616"/>
       <c r="G26" s="106"/>
-      <c r="H26" s="219"/>
-      <c r="I26" s="728"/>
-      <c r="J26" s="728"/>
-      <c r="K26" s="728"/>
-      <c r="L26" s="728"/>
+      <c r="H26" s="216"/>
+      <c r="I26" s="709"/>
+      <c r="J26" s="709"/>
+      <c r="K26" s="709"/>
+      <c r="L26" s="709"/>
       <c r="M26" s="107"/>
-      <c r="O26" s="247"/>
-      <c r="P26" s="244"/>
-      <c r="Q26" s="244"/>
-      <c r="R26" s="244"/>
-      <c r="S26" s="244"/>
-      <c r="T26" s="244"/>
-      <c r="U26" s="244"/>
-      <c r="V26" s="244"/>
-      <c r="W26" s="246"/>
+      <c r="O26" s="244"/>
+      <c r="P26" s="241"/>
+      <c r="Q26" s="241"/>
+      <c r="R26" s="241"/>
+      <c r="S26" s="241"/>
+      <c r="T26" s="241"/>
+      <c r="U26" s="241"/>
+      <c r="V26" s="241"/>
+      <c r="W26" s="243"/>
     </row>
     <row r="27" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="623" t="s">
+      <c r="A27" s="598" t="s">
         <v>354</v>
       </c>
-      <c r="B27" s="624"/>
-      <c r="C27" s="636" t="s">
+      <c r="B27" s="599"/>
+      <c r="C27" s="611" t="s">
         <v>355</v>
       </c>
-      <c r="D27" s="636"/>
-      <c r="E27" s="636"/>
-      <c r="F27" s="637"/>
+      <c r="D27" s="611"/>
+      <c r="E27" s="611"/>
+      <c r="F27" s="612"/>
       <c r="G27" s="32"/>
       <c r="H27" s="32"/>
       <c r="I27" s="32"/>
@@ -18410,101 +18412,101 @@
       <c r="K27" s="32"/>
       <c r="L27" s="32"/>
       <c r="M27" s="33"/>
-      <c r="O27" s="247"/>
-      <c r="P27" s="247"/>
-      <c r="Q27" s="247"/>
-      <c r="R27" s="247"/>
-      <c r="S27" s="247"/>
-      <c r="T27" s="247"/>
-      <c r="U27" s="247"/>
-      <c r="V27" s="247"/>
-      <c r="W27" s="246"/>
+      <c r="O27" s="244"/>
+      <c r="P27" s="244"/>
+      <c r="Q27" s="244"/>
+      <c r="R27" s="244"/>
+      <c r="S27" s="244"/>
+      <c r="T27" s="244"/>
+      <c r="U27" s="244"/>
+      <c r="V27" s="244"/>
+      <c r="W27" s="243"/>
     </row>
     <row r="28" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="34"/>
       <c r="B28" s="35"/>
-      <c r="C28" s="638"/>
-      <c r="D28" s="638"/>
-      <c r="E28" s="638"/>
-      <c r="F28" s="639"/>
-      <c r="G28" s="627" t="s">
+      <c r="C28" s="613"/>
+      <c r="D28" s="613"/>
+      <c r="E28" s="613"/>
+      <c r="F28" s="614"/>
+      <c r="G28" s="602" t="s">
         <v>345</v>
       </c>
-      <c r="H28" s="628"/>
-      <c r="I28" s="628"/>
-      <c r="J28" s="628"/>
-      <c r="K28" s="628"/>
-      <c r="L28" s="628"/>
+      <c r="H28" s="603"/>
+      <c r="I28" s="603"/>
+      <c r="J28" s="603"/>
+      <c r="K28" s="603"/>
+      <c r="L28" s="603"/>
       <c r="M28" s="2"/>
-      <c r="O28" s="247"/>
-      <c r="P28" s="247"/>
-      <c r="Q28" s="247"/>
-      <c r="R28" s="247"/>
-      <c r="S28" s="247"/>
-      <c r="T28" s="247"/>
-      <c r="U28" s="247"/>
-      <c r="V28" s="247"/>
-      <c r="W28" s="246"/>
+      <c r="O28" s="244"/>
+      <c r="P28" s="244"/>
+      <c r="Q28" s="244"/>
+      <c r="R28" s="244"/>
+      <c r="S28" s="244"/>
+      <c r="T28" s="244"/>
+      <c r="U28" s="244"/>
+      <c r="V28" s="244"/>
+      <c r="W28" s="243"/>
     </row>
     <row r="29" spans="1:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="34"/>
       <c r="B29" s="35"/>
-      <c r="C29" s="638"/>
-      <c r="D29" s="638"/>
-      <c r="E29" s="638"/>
-      <c r="F29" s="639"/>
-      <c r="G29" s="737"/>
-      <c r="H29" s="738"/>
-      <c r="I29" s="738"/>
-      <c r="J29" s="738"/>
-      <c r="K29" s="738"/>
-      <c r="L29" s="738"/>
-      <c r="M29" s="739"/>
-      <c r="O29" s="247"/>
-      <c r="P29" s="247"/>
-      <c r="Q29" s="247"/>
-      <c r="R29" s="247"/>
-      <c r="S29" s="247"/>
-      <c r="T29" s="247"/>
-      <c r="U29" s="247"/>
-      <c r="V29" s="247"/>
-      <c r="W29" s="246"/>
+      <c r="C29" s="613"/>
+      <c r="D29" s="613"/>
+      <c r="E29" s="613"/>
+      <c r="F29" s="614"/>
+      <c r="G29" s="731"/>
+      <c r="H29" s="732"/>
+      <c r="I29" s="732"/>
+      <c r="J29" s="732"/>
+      <c r="K29" s="732"/>
+      <c r="L29" s="732"/>
+      <c r="M29" s="733"/>
+      <c r="O29" s="244"/>
+      <c r="P29" s="244"/>
+      <c r="Q29" s="244"/>
+      <c r="R29" s="244"/>
+      <c r="S29" s="244"/>
+      <c r="T29" s="244"/>
+      <c r="U29" s="244"/>
+      <c r="V29" s="244"/>
+      <c r="W29" s="243"/>
     </row>
     <row r="30" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="45"/>
       <c r="B30" s="46"/>
-      <c r="C30" s="640"/>
-      <c r="D30" s="640"/>
-      <c r="E30" s="640"/>
-      <c r="F30" s="641"/>
+      <c r="C30" s="615"/>
+      <c r="D30" s="615"/>
+      <c r="E30" s="615"/>
+      <c r="F30" s="616"/>
       <c r="G30" s="125"/>
-      <c r="H30" s="221"/>
-      <c r="I30" s="163"/>
-      <c r="J30" s="163"/>
-      <c r="K30" s="163"/>
-      <c r="L30" s="163"/>
+      <c r="H30" s="218"/>
+      <c r="I30" s="160"/>
+      <c r="J30" s="160"/>
+      <c r="K30" s="160"/>
+      <c r="L30" s="160"/>
       <c r="M30" s="107"/>
-      <c r="O30" s="246"/>
-      <c r="P30" s="246"/>
-      <c r="Q30" s="246"/>
-      <c r="R30" s="246"/>
-      <c r="S30" s="246"/>
-      <c r="T30" s="246"/>
-      <c r="U30" s="246"/>
-      <c r="V30" s="246"/>
-      <c r="W30" s="246"/>
+      <c r="O30" s="243"/>
+      <c r="P30" s="243"/>
+      <c r="Q30" s="243"/>
+      <c r="R30" s="243"/>
+      <c r="S30" s="243"/>
+      <c r="T30" s="243"/>
+      <c r="U30" s="243"/>
+      <c r="V30" s="243"/>
+      <c r="W30" s="243"/>
     </row>
     <row r="31" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="623" t="s">
+      <c r="A31" s="598" t="s">
         <v>356</v>
       </c>
-      <c r="B31" s="624"/>
-      <c r="C31" s="636" t="s">
+      <c r="B31" s="599"/>
+      <c r="C31" s="611" t="s">
         <v>357</v>
       </c>
-      <c r="D31" s="636"/>
-      <c r="E31" s="636"/>
-      <c r="F31" s="637"/>
+      <c r="D31" s="611"/>
+      <c r="E31" s="611"/>
+      <c r="F31" s="612"/>
       <c r="G31" s="32"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
@@ -18512,98 +18514,98 @@
       <c r="K31" s="32"/>
       <c r="L31" s="32"/>
       <c r="M31" s="33"/>
-      <c r="O31" s="246"/>
-      <c r="P31" s="246"/>
-      <c r="Q31" s="246"/>
-      <c r="R31" s="246"/>
-      <c r="S31" s="246"/>
-      <c r="T31" s="246"/>
-      <c r="U31" s="246"/>
-      <c r="V31" s="246"/>
-      <c r="W31" s="246"/>
+      <c r="O31" s="243"/>
+      <c r="P31" s="243"/>
+      <c r="Q31" s="243"/>
+      <c r="R31" s="243"/>
+      <c r="S31" s="243"/>
+      <c r="T31" s="243"/>
+      <c r="U31" s="243"/>
+      <c r="V31" s="243"/>
+      <c r="W31" s="243"/>
     </row>
     <row r="32" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="34"/>
       <c r="B32" s="35"/>
-      <c r="C32" s="638"/>
-      <c r="D32" s="638"/>
-      <c r="E32" s="638"/>
-      <c r="F32" s="639"/>
-      <c r="G32" s="642" t="s">
+      <c r="C32" s="613"/>
+      <c r="D32" s="613"/>
+      <c r="E32" s="613"/>
+      <c r="F32" s="614"/>
+      <c r="G32" s="718" t="s">
         <v>358</v>
       </c>
-      <c r="H32" s="643"/>
-      <c r="I32" s="643"/>
-      <c r="J32" s="643"/>
-      <c r="K32" s="745"/>
-      <c r="L32" s="745"/>
+      <c r="H32" s="719"/>
+      <c r="I32" s="719"/>
+      <c r="J32" s="719"/>
+      <c r="K32" s="716"/>
+      <c r="L32" s="716"/>
       <c r="M32" s="105"/>
-      <c r="O32" s="246"/>
-      <c r="P32" s="246"/>
-      <c r="Q32" s="246"/>
-      <c r="R32" s="246"/>
-      <c r="S32" s="246"/>
-      <c r="T32" s="246"/>
-      <c r="U32" s="246"/>
-      <c r="V32" s="246"/>
-      <c r="W32" s="246"/>
+      <c r="O32" s="243"/>
+      <c r="P32" s="243"/>
+      <c r="Q32" s="243"/>
+      <c r="R32" s="243"/>
+      <c r="S32" s="243"/>
+      <c r="T32" s="243"/>
+      <c r="U32" s="243"/>
+      <c r="V32" s="243"/>
+      <c r="W32" s="243"/>
     </row>
     <row r="33" spans="1:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="34"/>
       <c r="B33" s="35"/>
-      <c r="C33" s="167"/>
-      <c r="D33" s="167"/>
-      <c r="E33" s="167"/>
-      <c r="F33" s="166"/>
+      <c r="C33" s="164"/>
+      <c r="D33" s="164"/>
+      <c r="E33" s="164"/>
+      <c r="F33" s="163"/>
       <c r="G33" s="108"/>
       <c r="H33" s="56"/>
       <c r="I33" s="99"/>
       <c r="J33" s="99"/>
-      <c r="K33" s="169"/>
-      <c r="L33" s="169"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="166"/>
       <c r="M33" s="105"/>
     </row>
     <row r="34" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="34"/>
       <c r="B34" s="35"/>
-      <c r="C34" s="638" t="s">
+      <c r="C34" s="613" t="s">
         <v>359</v>
       </c>
-      <c r="D34" s="638"/>
-      <c r="E34" s="638"/>
-      <c r="F34" s="639"/>
+      <c r="D34" s="613"/>
+      <c r="E34" s="613"/>
+      <c r="F34" s="614"/>
       <c r="G34" s="104"/>
-      <c r="H34" s="220"/>
-      <c r="I34" s="746"/>
-      <c r="J34" s="746"/>
-      <c r="K34" s="746"/>
-      <c r="L34" s="746"/>
+      <c r="H34" s="217"/>
+      <c r="I34" s="717"/>
+      <c r="J34" s="717"/>
+      <c r="K34" s="717"/>
+      <c r="L34" s="717"/>
       <c r="M34" s="105"/>
     </row>
     <row r="35" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="34"/>
       <c r="B35" s="35"/>
-      <c r="C35" s="638"/>
-      <c r="D35" s="638"/>
-      <c r="E35" s="638"/>
-      <c r="F35" s="639"/>
-      <c r="G35" s="642" t="s">
+      <c r="C35" s="613"/>
+      <c r="D35" s="613"/>
+      <c r="E35" s="613"/>
+      <c r="F35" s="614"/>
+      <c r="G35" s="718" t="s">
         <v>358</v>
       </c>
-      <c r="H35" s="643"/>
-      <c r="I35" s="643"/>
-      <c r="J35" s="643"/>
-      <c r="K35" s="745"/>
-      <c r="L35" s="745"/>
+      <c r="H35" s="719"/>
+      <c r="I35" s="719"/>
+      <c r="J35" s="719"/>
+      <c r="K35" s="716"/>
+      <c r="L35" s="716"/>
       <c r="M35" s="105"/>
     </row>
     <row r="36" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="45"/>
       <c r="B36" s="46"/>
-      <c r="C36" s="640"/>
-      <c r="D36" s="640"/>
-      <c r="E36" s="640"/>
-      <c r="F36" s="641"/>
+      <c r="C36" s="615"/>
+      <c r="D36" s="615"/>
+      <c r="E36" s="615"/>
+      <c r="F36" s="616"/>
       <c r="G36" s="108"/>
       <c r="H36" s="56"/>
       <c r="I36" s="99"/>
@@ -18612,16 +18614,16 @@
       <c r="M36" s="107"/>
     </row>
     <row r="37" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="623" t="s">
+      <c r="A37" s="598" t="s">
         <v>360</v>
       </c>
-      <c r="B37" s="624"/>
-      <c r="C37" s="729" t="s">
+      <c r="B37" s="599"/>
+      <c r="C37" s="710" t="s">
         <v>361</v>
       </c>
-      <c r="D37" s="729"/>
-      <c r="E37" s="729"/>
-      <c r="F37" s="730"/>
+      <c r="D37" s="710"/>
+      <c r="E37" s="710"/>
+      <c r="F37" s="711"/>
       <c r="G37" s="32"/>
       <c r="H37" s="32"/>
       <c r="I37" s="32"/>
@@ -18633,61 +18635,61 @@
     <row r="38" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="34"/>
       <c r="B38" s="35"/>
-      <c r="C38" s="731"/>
-      <c r="D38" s="731"/>
-      <c r="E38" s="731"/>
-      <c r="F38" s="732"/>
-      <c r="G38" s="627" t="s">
+      <c r="C38" s="712"/>
+      <c r="D38" s="712"/>
+      <c r="E38" s="712"/>
+      <c r="F38" s="713"/>
+      <c r="G38" s="602" t="s">
         <v>362</v>
       </c>
-      <c r="H38" s="628"/>
-      <c r="I38" s="628"/>
-      <c r="J38" s="628"/>
-      <c r="K38" s="628"/>
-      <c r="L38" s="628"/>
-      <c r="M38" s="629"/>
+      <c r="H38" s="603"/>
+      <c r="I38" s="603"/>
+      <c r="J38" s="603"/>
+      <c r="K38" s="603"/>
+      <c r="L38" s="603"/>
+      <c r="M38" s="604"/>
     </row>
     <row r="39" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="34"/>
       <c r="B39" s="35"/>
-      <c r="C39" s="731"/>
-      <c r="D39" s="731"/>
-      <c r="E39" s="731"/>
-      <c r="F39" s="732"/>
+      <c r="C39" s="712"/>
+      <c r="D39" s="712"/>
+      <c r="E39" s="712"/>
+      <c r="F39" s="713"/>
       <c r="G39" s="104"/>
-      <c r="H39" s="602"/>
-      <c r="I39" s="602"/>
-      <c r="J39" s="602"/>
-      <c r="K39" s="602"/>
-      <c r="L39" s="602"/>
+      <c r="H39" s="720"/>
+      <c r="I39" s="720"/>
+      <c r="J39" s="720"/>
+      <c r="K39" s="720"/>
+      <c r="L39" s="720"/>
       <c r="M39" s="105"/>
     </row>
     <row r="40" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="45"/>
       <c r="B40" s="46"/>
-      <c r="C40" s="733"/>
-      <c r="D40" s="733"/>
-      <c r="E40" s="733"/>
-      <c r="F40" s="734"/>
+      <c r="C40" s="714"/>
+      <c r="D40" s="714"/>
+      <c r="E40" s="714"/>
+      <c r="F40" s="715"/>
       <c r="G40" s="106"/>
-      <c r="H40" s="219"/>
-      <c r="I40" s="728"/>
-      <c r="J40" s="728"/>
-      <c r="K40" s="728"/>
-      <c r="L40" s="728"/>
+      <c r="H40" s="216"/>
+      <c r="I40" s="709"/>
+      <c r="J40" s="709"/>
+      <c r="K40" s="709"/>
+      <c r="L40" s="709"/>
       <c r="M40" s="107"/>
     </row>
     <row r="41" spans="1:14" ht="41.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="726" t="s">
+      <c r="A41" s="707" t="s">
         <v>363</v>
       </c>
-      <c r="B41" s="727"/>
-      <c r="C41" s="638" t="s">
+      <c r="B41" s="708"/>
+      <c r="C41" s="613" t="s">
         <v>364</v>
       </c>
-      <c r="D41" s="638"/>
-      <c r="E41" s="638"/>
-      <c r="F41" s="639"/>
+      <c r="D41" s="613"/>
+      <c r="E41" s="613"/>
+      <c r="F41" s="614"/>
       <c r="G41" s="32"/>
       <c r="H41" s="32"/>
       <c r="I41" s="51"/>
@@ -18699,10 +18701,10 @@
     <row r="42" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="49"/>
       <c r="B42" s="50"/>
-      <c r="C42" s="638"/>
-      <c r="D42" s="638"/>
-      <c r="E42" s="638"/>
-      <c r="F42" s="639"/>
+      <c r="C42" s="613"/>
+      <c r="D42" s="613"/>
+      <c r="E42" s="613"/>
+      <c r="F42" s="614"/>
       <c r="G42" s="54"/>
       <c r="H42" s="54"/>
       <c r="I42" s="54"/>
@@ -18716,25 +18718,25 @@
         <v>365</v>
       </c>
       <c r="B43" s="50"/>
-      <c r="C43" s="638" t="s">
+      <c r="C43" s="613" t="s">
         <v>366</v>
       </c>
-      <c r="D43" s="638"/>
-      <c r="E43" s="638"/>
-      <c r="F43" s="639"/>
+      <c r="D43" s="613"/>
+      <c r="E43" s="613"/>
+      <c r="F43" s="614"/>
       <c r="M43" s="2"/>
     </row>
     <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="49"/>
       <c r="B44" s="50"/>
-      <c r="C44" s="638"/>
-      <c r="D44" s="638"/>
-      <c r="E44" s="638"/>
-      <c r="F44" s="639"/>
-      <c r="G44" s="172" t="s">
+      <c r="C44" s="613"/>
+      <c r="D44" s="613"/>
+      <c r="E44" s="613"/>
+      <c r="F44" s="614"/>
+      <c r="G44" s="169" t="s">
         <v>367</v>
       </c>
-      <c r="H44" s="222"/>
+      <c r="H44" s="219"/>
       <c r="I44" s="99"/>
       <c r="J44" s="99"/>
       <c r="L44" s="103"/>
@@ -18746,25 +18748,25 @@
         <v>368</v>
       </c>
       <c r="B45" s="50"/>
-      <c r="C45" s="639" t="s">
+      <c r="C45" s="614" t="s">
         <v>369</v>
       </c>
-      <c r="D45" s="639"/>
-      <c r="E45" s="639"/>
-      <c r="F45" s="639"/>
+      <c r="D45" s="614"/>
+      <c r="E45" s="614"/>
+      <c r="F45" s="614"/>
       <c r="M45" s="2"/>
     </row>
     <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="49"/>
       <c r="B46" s="50"/>
-      <c r="C46" s="639"/>
-      <c r="D46" s="639"/>
-      <c r="E46" s="639"/>
-      <c r="F46" s="639"/>
-      <c r="G46" s="173" t="s">
+      <c r="C46" s="614"/>
+      <c r="D46" s="614"/>
+      <c r="E46" s="614"/>
+      <c r="F46" s="614"/>
+      <c r="G46" s="170" t="s">
         <v>370</v>
       </c>
-      <c r="H46" s="223"/>
+      <c r="H46" s="220"/>
       <c r="I46" s="99"/>
       <c r="J46" s="99"/>
       <c r="K46" s="99"/>
@@ -18777,25 +18779,25 @@
         <v>371</v>
       </c>
       <c r="B47" s="50"/>
-      <c r="C47" s="638" t="s">
+      <c r="C47" s="613" t="s">
         <v>372</v>
       </c>
-      <c r="D47" s="638"/>
+      <c r="D47" s="613"/>
       <c r="E47" s="96"/>
       <c r="F47" s="97"/>
       <c r="M47" s="2"/>
     </row>
     <row r="48" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="687"/>
-      <c r="B48" s="688"/>
-      <c r="C48" s="688"/>
-      <c r="D48" s="688"/>
-      <c r="E48" s="688"/>
-      <c r="F48" s="689"/>
-      <c r="G48" s="174" t="s">
+      <c r="A48" s="667"/>
+      <c r="B48" s="668"/>
+      <c r="C48" s="668"/>
+      <c r="D48" s="668"/>
+      <c r="E48" s="668"/>
+      <c r="F48" s="669"/>
+      <c r="G48" s="171" t="s">
         <v>370</v>
       </c>
-      <c r="H48" s="224"/>
+      <c r="H48" s="221"/>
       <c r="I48" s="101"/>
       <c r="J48" s="101"/>
       <c r="K48" s="101"/>
@@ -18804,12 +18806,12 @@
       <c r="N48" s="56"/>
     </row>
     <row r="49" spans="1:14" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="690"/>
-      <c r="B49" s="691"/>
-      <c r="C49" s="691"/>
-      <c r="D49" s="691"/>
-      <c r="E49" s="691"/>
-      <c r="F49" s="692"/>
+      <c r="A49" s="670"/>
+      <c r="B49" s="671"/>
+      <c r="C49" s="671"/>
+      <c r="D49" s="671"/>
+      <c r="E49" s="671"/>
+      <c r="F49" s="672"/>
       <c r="G49" s="98"/>
       <c r="H49" s="94"/>
       <c r="I49" s="94"/>
@@ -18820,157 +18822,157 @@
       <c r="N49" s="56"/>
     </row>
     <row r="50" spans="1:14" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="625" t="s">
+      <c r="A50" s="600" t="s">
         <v>373</v>
       </c>
-      <c r="B50" s="626"/>
-      <c r="C50" s="170" t="s">
+      <c r="B50" s="601"/>
+      <c r="C50" s="167" t="s">
         <v>374</v>
       </c>
-      <c r="D50" s="170"/>
-      <c r="E50" s="170"/>
-      <c r="F50" s="170"/>
-      <c r="G50" s="170"/>
-      <c r="H50" s="170"/>
-      <c r="I50" s="171"/>
-      <c r="J50" s="674"/>
-      <c r="K50" s="675"/>
-      <c r="L50" s="675"/>
-      <c r="M50" s="676"/>
+      <c r="D50" s="167"/>
+      <c r="E50" s="167"/>
+      <c r="F50" s="167"/>
+      <c r="G50" s="167"/>
+      <c r="H50" s="167"/>
+      <c r="I50" s="168"/>
+      <c r="J50" s="737"/>
+      <c r="K50" s="738"/>
+      <c r="L50" s="738"/>
+      <c r="M50" s="739"/>
     </row>
     <row r="51" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="684" t="s">
+      <c r="A51" s="664" t="s">
         <v>375</v>
       </c>
-      <c r="B51" s="685"/>
-      <c r="C51" s="685"/>
-      <c r="D51" s="685"/>
-      <c r="E51" s="686"/>
-      <c r="F51" s="232" t="s">
+      <c r="B51" s="665"/>
+      <c r="C51" s="665"/>
+      <c r="D51" s="665"/>
+      <c r="E51" s="666"/>
+      <c r="F51" s="229" t="s">
         <v>376</v>
       </c>
-      <c r="G51" s="463" t="s">
+      <c r="G51" s="456" t="s">
         <v>377</v>
       </c>
-      <c r="H51" s="541"/>
-      <c r="I51" s="464"/>
-      <c r="J51" s="677"/>
-      <c r="K51" s="678"/>
-      <c r="L51" s="678"/>
-      <c r="M51" s="679"/>
+      <c r="H51" s="537"/>
+      <c r="I51" s="457"/>
+      <c r="J51" s="740"/>
+      <c r="K51" s="741"/>
+      <c r="L51" s="741"/>
+      <c r="M51" s="742"/>
     </row>
     <row r="52" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="702"/>
-      <c r="B52" s="703"/>
-      <c r="C52" s="705"/>
-      <c r="D52" s="705"/>
-      <c r="E52" s="706"/>
-      <c r="F52" s="268"/>
-      <c r="G52" s="695"/>
-      <c r="H52" s="696"/>
-      <c r="I52" s="697"/>
-      <c r="J52" s="677"/>
-      <c r="K52" s="678"/>
-      <c r="L52" s="678"/>
-      <c r="M52" s="679"/>
+      <c r="A52" s="682"/>
+      <c r="B52" s="683"/>
+      <c r="C52" s="685"/>
+      <c r="D52" s="685"/>
+      <c r="E52" s="686"/>
+      <c r="F52" s="265"/>
+      <c r="G52" s="675"/>
+      <c r="H52" s="676"/>
+      <c r="I52" s="677"/>
+      <c r="J52" s="740"/>
+      <c r="K52" s="741"/>
+      <c r="L52" s="741"/>
+      <c r="M52" s="742"/>
     </row>
     <row r="53" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="702"/>
-      <c r="B53" s="703"/>
-      <c r="C53" s="703"/>
-      <c r="D53" s="703"/>
-      <c r="E53" s="704"/>
-      <c r="F53" s="268"/>
-      <c r="G53" s="695"/>
-      <c r="H53" s="696"/>
-      <c r="I53" s="697"/>
-      <c r="J53" s="677"/>
-      <c r="K53" s="678"/>
-      <c r="L53" s="678"/>
-      <c r="M53" s="679"/>
+      <c r="A53" s="682"/>
+      <c r="B53" s="683"/>
+      <c r="C53" s="683"/>
+      <c r="D53" s="683"/>
+      <c r="E53" s="684"/>
+      <c r="F53" s="265"/>
+      <c r="G53" s="675"/>
+      <c r="H53" s="676"/>
+      <c r="I53" s="677"/>
+      <c r="J53" s="740"/>
+      <c r="K53" s="741"/>
+      <c r="L53" s="741"/>
+      <c r="M53" s="742"/>
     </row>
     <row r="54" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="698"/>
-      <c r="B54" s="699"/>
-      <c r="C54" s="700"/>
-      <c r="D54" s="700"/>
-      <c r="E54" s="701"/>
-      <c r="F54" s="269"/>
-      <c r="G54" s="681"/>
-      <c r="H54" s="682"/>
-      <c r="I54" s="683"/>
-      <c r="J54" s="677"/>
-      <c r="K54" s="678"/>
-      <c r="L54" s="678"/>
-      <c r="M54" s="679"/>
+      <c r="A54" s="678"/>
+      <c r="B54" s="679"/>
+      <c r="C54" s="680"/>
+      <c r="D54" s="680"/>
+      <c r="E54" s="681"/>
+      <c r="F54" s="266"/>
+      <c r="G54" s="734"/>
+      <c r="H54" s="735"/>
+      <c r="I54" s="736"/>
+      <c r="J54" s="740"/>
+      <c r="K54" s="741"/>
+      <c r="L54" s="741"/>
+      <c r="M54" s="742"/>
     </row>
     <row r="55" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="693" t="s">
+      <c r="A55" s="673" t="s">
         <v>378</v>
       </c>
-      <c r="B55" s="694"/>
-      <c r="C55" s="707" t="s">
+      <c r="B55" s="674"/>
+      <c r="C55" s="687" t="s">
         <v>399</v>
       </c>
-      <c r="D55" s="707"/>
-      <c r="E55" s="707"/>
-      <c r="F55" s="707"/>
-      <c r="G55" s="707"/>
-      <c r="H55" s="707"/>
-      <c r="I55" s="225"/>
-      <c r="J55" s="678"/>
-      <c r="K55" s="678"/>
-      <c r="L55" s="678"/>
-      <c r="M55" s="679"/>
+      <c r="D55" s="687"/>
+      <c r="E55" s="687"/>
+      <c r="F55" s="687"/>
+      <c r="G55" s="687"/>
+      <c r="H55" s="687"/>
+      <c r="I55" s="222"/>
+      <c r="J55" s="741"/>
+      <c r="K55" s="741"/>
+      <c r="L55" s="741"/>
+      <c r="M55" s="742"/>
     </row>
     <row r="56" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="57"/>
       <c r="B56" s="58"/>
-      <c r="C56" s="708"/>
-      <c r="D56" s="708"/>
-      <c r="E56" s="708"/>
-      <c r="F56" s="708"/>
-      <c r="G56" s="708"/>
-      <c r="H56" s="708"/>
-      <c r="I56" s="226"/>
-      <c r="J56" s="177"/>
-      <c r="K56" s="680" t="s">
+      <c r="C56" s="688"/>
+      <c r="D56" s="688"/>
+      <c r="E56" s="688"/>
+      <c r="F56" s="688"/>
+      <c r="G56" s="688"/>
+      <c r="H56" s="688"/>
+      <c r="I56" s="223"/>
+      <c r="J56" s="174"/>
+      <c r="K56" s="705" t="s">
         <v>379</v>
       </c>
-      <c r="L56" s="680"/>
-      <c r="M56" s="162"/>
+      <c r="L56" s="705"/>
+      <c r="M56" s="159"/>
     </row>
     <row r="57" spans="1:14" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="57"/>
       <c r="B57" s="58"/>
-      <c r="C57" s="708"/>
-      <c r="D57" s="708"/>
-      <c r="E57" s="708"/>
-      <c r="F57" s="708"/>
-      <c r="G57" s="708"/>
-      <c r="H57" s="708"/>
-      <c r="I57" s="226"/>
-      <c r="J57" s="680"/>
-      <c r="K57" s="680"/>
-      <c r="L57" s="680"/>
-      <c r="M57" s="725"/>
+      <c r="C57" s="688"/>
+      <c r="D57" s="688"/>
+      <c r="E57" s="688"/>
+      <c r="F57" s="688"/>
+      <c r="G57" s="688"/>
+      <c r="H57" s="688"/>
+      <c r="I57" s="223"/>
+      <c r="J57" s="705"/>
+      <c r="K57" s="705"/>
+      <c r="L57" s="705"/>
+      <c r="M57" s="706"/>
     </row>
     <row r="58" spans="1:14" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="160"/>
-      <c r="B58" s="161"/>
-      <c r="C58" s="227"/>
-      <c r="D58" s="227"/>
-      <c r="E58" s="227"/>
-      <c r="F58" s="227"/>
-      <c r="G58" s="227"/>
-      <c r="H58" s="227"/>
-      <c r="I58" s="228"/>
-      <c r="K58" s="664"/>
-      <c r="L58" s="665"/>
+      <c r="A58" s="157"/>
+      <c r="B58" s="158"/>
+      <c r="C58" s="224"/>
+      <c r="D58" s="224"/>
+      <c r="E58" s="224"/>
+      <c r="F58" s="224"/>
+      <c r="G58" s="224"/>
+      <c r="H58" s="224"/>
+      <c r="I58" s="225"/>
+      <c r="K58" s="638"/>
+      <c r="L58" s="639"/>
       <c r="M58" s="2"/>
     </row>
     <row r="59" spans="1:14" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="159"/>
+      <c r="A59" s="156"/>
       <c r="C59" s="27"/>
       <c r="D59" s="27"/>
       <c r="E59" s="27"/>
@@ -18978,107 +18980,107 @@
       <c r="G59" s="27"/>
       <c r="H59" s="27"/>
       <c r="I59" s="27"/>
-      <c r="K59" s="666"/>
-      <c r="L59" s="667"/>
+      <c r="K59" s="640"/>
+      <c r="L59" s="641"/>
       <c r="M59" s="2"/>
     </row>
     <row r="60" spans="1:14" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
-      <c r="B60" s="615" t="s">
+      <c r="B60" s="657" t="s">
         <v>400</v>
       </c>
-      <c r="C60" s="616"/>
-      <c r="D60" s="617"/>
-      <c r="F60" s="606" t="s">
+      <c r="C60" s="658"/>
+      <c r="D60" s="659"/>
+      <c r="F60" s="648" t="s">
         <v>144</v>
       </c>
-      <c r="G60" s="607"/>
-      <c r="H60" s="607"/>
-      <c r="I60" s="608"/>
-      <c r="K60" s="666"/>
-      <c r="L60" s="667"/>
+      <c r="G60" s="649"/>
+      <c r="H60" s="649"/>
+      <c r="I60" s="650"/>
+      <c r="K60" s="640"/>
+      <c r="L60" s="641"/>
       <c r="M60" s="60"/>
     </row>
     <row r="61" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="59"/>
-      <c r="B61" s="670" t="s">
+      <c r="B61" s="644" t="s">
         <v>380</v>
       </c>
-      <c r="C61" s="671"/>
+      <c r="C61" s="645"/>
       <c r="D61" s="112"/>
-      <c r="F61" s="609"/>
-      <c r="G61" s="610"/>
-      <c r="H61" s="610"/>
-      <c r="I61" s="611"/>
-      <c r="K61" s="666"/>
-      <c r="L61" s="667"/>
+      <c r="F61" s="651"/>
+      <c r="G61" s="652"/>
+      <c r="H61" s="652"/>
+      <c r="I61" s="653"/>
+      <c r="K61" s="640"/>
+      <c r="L61" s="641"/>
       <c r="M61" s="60"/>
     </row>
     <row r="62" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
-      <c r="B62" s="659" t="s">
+      <c r="B62" s="632" t="s">
         <v>381</v>
       </c>
-      <c r="C62" s="660"/>
-      <c r="D62" s="618"/>
-      <c r="F62" s="612"/>
-      <c r="G62" s="613"/>
-      <c r="H62" s="613"/>
-      <c r="I62" s="614"/>
-      <c r="K62" s="666"/>
-      <c r="L62" s="667"/>
+      <c r="C62" s="633"/>
+      <c r="D62" s="636"/>
+      <c r="F62" s="654"/>
+      <c r="G62" s="655"/>
+      <c r="H62" s="655"/>
+      <c r="I62" s="656"/>
+      <c r="K62" s="640"/>
+      <c r="L62" s="641"/>
       <c r="M62" s="60"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="59"/>
-      <c r="B63" s="672"/>
-      <c r="C63" s="673"/>
-      <c r="D63" s="619"/>
-      <c r="F63" s="620" t="s">
+      <c r="B63" s="646"/>
+      <c r="C63" s="647"/>
+      <c r="D63" s="660"/>
+      <c r="F63" s="661" t="s">
         <v>382</v>
       </c>
-      <c r="G63" s="621"/>
-      <c r="H63" s="621"/>
-      <c r="I63" s="622"/>
-      <c r="K63" s="666"/>
-      <c r="L63" s="667"/>
+      <c r="G63" s="662"/>
+      <c r="H63" s="662"/>
+      <c r="I63" s="663"/>
+      <c r="K63" s="640"/>
+      <c r="L63" s="641"/>
       <c r="M63" s="60"/>
     </row>
     <row r="64" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="59"/>
-      <c r="B64" s="659" t="s">
+      <c r="B64" s="632" t="s">
         <v>383</v>
       </c>
-      <c r="C64" s="660"/>
-      <c r="D64" s="618"/>
-      <c r="F64" s="754">
+      <c r="C64" s="633"/>
+      <c r="D64" s="636"/>
+      <c r="F64" s="726">
         <f ca="1" xml:space="preserve"> NOW()</f>
-        <v>45982.693544444446</v>
-      </c>
-      <c r="G64" s="755"/>
-      <c r="H64" s="755"/>
-      <c r="I64" s="756"/>
+        <v>45982.839370949077</v>
+      </c>
+      <c r="G64" s="727"/>
+      <c r="H64" s="727"/>
+      <c r="I64" s="728"/>
       <c r="J64" s="61"/>
-      <c r="K64" s="668"/>
-      <c r="L64" s="669"/>
+      <c r="K64" s="642"/>
+      <c r="L64" s="643"/>
       <c r="M64" s="60"/>
     </row>
     <row r="65" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="59"/>
-      <c r="B65" s="661"/>
-      <c r="C65" s="662"/>
-      <c r="D65" s="663"/>
-      <c r="F65" s="656" t="s">
+      <c r="B65" s="634"/>
+      <c r="C65" s="635"/>
+      <c r="D65" s="637"/>
+      <c r="F65" s="629" t="s">
         <v>384</v>
       </c>
-      <c r="G65" s="657"/>
-      <c r="H65" s="657"/>
-      <c r="I65" s="658"/>
+      <c r="G65" s="630"/>
+      <c r="H65" s="630"/>
+      <c r="I65" s="631"/>
       <c r="J65" s="61"/>
-      <c r="K65" s="654" t="s">
+      <c r="K65" s="627" t="s">
         <v>385</v>
       </c>
-      <c r="L65" s="655"/>
+      <c r="L65" s="628"/>
       <c r="M65" s="60"/>
     </row>
     <row r="66" spans="1:13" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -19097,34 +19099,34 @@
       <c r="M66" s="67"/>
     </row>
     <row r="67" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="651" t="s">
+      <c r="A67" s="624" t="s">
         <v>386</v>
       </c>
-      <c r="B67" s="652"/>
-      <c r="C67" s="652"/>
-      <c r="D67" s="652"/>
-      <c r="E67" s="652"/>
-      <c r="F67" s="652"/>
-      <c r="G67" s="652"/>
-      <c r="H67" s="652"/>
-      <c r="I67" s="652"/>
-      <c r="J67" s="652"/>
-      <c r="K67" s="652"/>
-      <c r="L67" s="652"/>
-      <c r="M67" s="653"/>
+      <c r="B67" s="625"/>
+      <c r="C67" s="625"/>
+      <c r="D67" s="625"/>
+      <c r="E67" s="625"/>
+      <c r="F67" s="625"/>
+      <c r="G67" s="625"/>
+      <c r="H67" s="625"/>
+      <c r="I67" s="625"/>
+      <c r="J67" s="625"/>
+      <c r="K67" s="625"/>
+      <c r="L67" s="625"/>
+      <c r="M67" s="626"/>
     </row>
     <row r="68" spans="1:13" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="59"/>
       <c r="B68" s="61"/>
       <c r="C68" s="68"/>
       <c r="D68" s="68"/>
-      <c r="E68" s="648" t="s">
+      <c r="E68" s="621" t="s">
         <v>387</v>
       </c>
-      <c r="F68" s="649"/>
-      <c r="G68" s="649"/>
-      <c r="H68" s="649"/>
-      <c r="I68" s="650"/>
+      <c r="F68" s="622"/>
+      <c r="G68" s="622"/>
+      <c r="H68" s="622"/>
+      <c r="I68" s="623"/>
       <c r="J68" s="113"/>
       <c r="K68" s="113"/>
       <c r="M68" s="60"/>
@@ -19132,15 +19134,15 @@
     <row r="69" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="59"/>
       <c r="B69" s="61"/>
-      <c r="C69" s="212"/>
-      <c r="D69" s="212"/>
-      <c r="E69" s="645" t="s">
+      <c r="C69" s="209"/>
+      <c r="D69" s="209"/>
+      <c r="E69" s="618" t="s">
         <v>388</v>
       </c>
-      <c r="F69" s="646"/>
-      <c r="G69" s="646"/>
-      <c r="H69" s="646"/>
-      <c r="I69" s="647"/>
+      <c r="F69" s="619"/>
+      <c r="G69" s="619"/>
+      <c r="H69" s="619"/>
+      <c r="I69" s="620"/>
       <c r="J69" s="115"/>
       <c r="K69" s="114"/>
       <c r="L69" s="69"/>
@@ -19162,21 +19164,21 @@
       <c r="M70" s="72"/>
     </row>
     <row r="71" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="644" t="s">
+      <c r="A71" s="617" t="s">
         <v>402</v>
       </c>
-      <c r="B71" s="644"/>
-      <c r="C71" s="644"/>
-      <c r="D71" s="644"/>
-      <c r="E71" s="644"/>
-      <c r="F71" s="644"/>
-      <c r="G71" s="644"/>
-      <c r="H71" s="644"/>
-      <c r="I71" s="644"/>
-      <c r="J71" s="644"/>
-      <c r="K71" s="644"/>
-      <c r="L71" s="644"/>
-      <c r="M71" s="644"/>
+      <c r="B71" s="617"/>
+      <c r="C71" s="617"/>
+      <c r="D71" s="617"/>
+      <c r="E71" s="617"/>
+      <c r="F71" s="617"/>
+      <c r="G71" s="617"/>
+      <c r="H71" s="617"/>
+      <c r="I71" s="617"/>
+      <c r="J71" s="617"/>
+      <c r="K71" s="617"/>
+      <c r="L71" s="617"/>
+      <c r="M71" s="617"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -19189,23 +19191,24 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="88">
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="G29:M29"/>
     <mergeCell ref="H39:L39"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="J50:M55"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="H25:L25"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C13:F16"/>
     <mergeCell ref="G14:L14"/>
     <mergeCell ref="I16:L16"/>
     <mergeCell ref="G15:M15"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="C31:F32"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C34:F36"/>
-    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="G29:M29"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="I3:J3"/>
@@ -19234,7 +19237,6 @@
     <mergeCell ref="I6:L6"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="G11:M11"/>
-    <mergeCell ref="G54:I54"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A48:F49"/>
     <mergeCell ref="G51:I51"/>
@@ -19245,9 +19247,6 @@
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="C55:H57"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G35:J35"/>
     <mergeCell ref="A71:M71"/>
     <mergeCell ref="E69:I69"/>
     <mergeCell ref="E68:I68"/>
@@ -19259,15 +19258,11 @@
     <mergeCell ref="K58:L64"/>
     <mergeCell ref="B61:C61"/>
     <mergeCell ref="B62:C63"/>
-    <mergeCell ref="J50:M55"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="H25:L25"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="G21:I21"/>
     <mergeCell ref="F60:I62"/>
     <mergeCell ref="B60:D60"/>
     <mergeCell ref="D62:D63"/>
     <mergeCell ref="F63:I63"/>
+    <mergeCell ref="F64:I64"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="G38:M38"/>
@@ -19277,6 +19272,13 @@
     <mergeCell ref="I22:K22"/>
     <mergeCell ref="G19:L19"/>
     <mergeCell ref="C23:F26"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="C31:F32"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C34:F36"/>
+    <mergeCell ref="K35:L35"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -19913,16 +19915,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="61535973-5223-4bf4-bdcc-6c7df9166676">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -19931,7 +19923,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004061E9AFAF7CA04B82F43B8373745610" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3807037a0979b6ce9196f65959799221">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="61535973-5223-4bf4-bdcc-6c7df9166676" xmlns:ns3="ab5b6d4b-4285-4680-b1ee-6fe31a63f7d7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0698124c94b6a25b909cbe33b647c32f" ns2:_="" ns3:_="">
     <xsd:import namespace="61535973-5223-4bf4-bdcc-6c7df9166676"/>
@@ -20162,24 +20154,17 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CF60C-2A54-4479-8975-DF3B2608842A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="ab5b6d4b-4285-4680-b1ee-6fe31a63f7d7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="61535973-5223-4bf4-bdcc-6c7df9166676"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="61535973-5223-4bf4-bdcc-6c7df9166676">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE1AC42-07AD-4118-96D5-B1BB6CECCAA7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -20187,7 +20172,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99101B7C-E13F-4ECC-92B9-66DA7C9E1E4F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20204,4 +20189,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CF60C-2A54-4479-8975-DF3B2608842A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="ab5b6d4b-4285-4680-b1ee-6fe31a63f7d7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="61535973-5223-4bf4-bdcc-6c7df9166676"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>